--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783D8B21-28E0-B947-AA5A-29D8CDA22CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1AA5C0-11B8-B74A-A77B-B4746B60B74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ターム内容" sheetId="1" r:id="rId1"/>
@@ -16,8 +16,8 @@
     <sheet name="環境構築手順" sheetId="6" r:id="rId6"/>
     <sheet name="テストケース一覧" sheetId="7" r:id="rId7"/>
     <sheet name="API仕様書（応用）" sheetId="8" r:id="rId8"/>
-    <sheet name="基本設計書（記載済）" sheetId="11" r:id="rId9"/>
-    <sheet name="テーブル仕様書（記載済）" sheetId="12" r:id="rId10"/>
+    <sheet name="基本設計書（記載済）" sheetId="13" r:id="rId9"/>
+    <sheet name="テーブル仕様書（記載済）" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1056">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -2423,9 +2423,6 @@
   </si>
   <si>
     <t>YYYY-MM 形式の年月で絞り込み</t>
-  </si>
-  <si>
-    <t>出勤登録画面（一般ユーザー）</t>
   </si>
   <si>
     <t>★ 一般ユーザーは，自分の勤怠統計レポートを確認することができる</t>
@@ -5268,6 +5265,75 @@
   </si>
   <si>
     <t>new_break_out</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>メール認証誘導画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>redirect</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>一般ユーザーのログイン時、メール認証を誘導する画面</t>
+    <rPh sb="0" eb="2">
+      <t>イッパンユ-</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガメn</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>会員登録画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>勤怠一覧画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>勤怠詳細画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>申請一覧画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>ログイン画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>勤怠一覧画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>勤怠詳細画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>スタッフ一覧画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>スタッフ別勤怠一覧画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>申請一覧画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>修正申請承認画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>verify-email.blade.php</t>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -6939,7 +7005,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="467">
+  <cellXfs count="470">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -7966,14 +8032,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8096,22 +8155,11 @@
     <xf numFmtId="0" fontId="63" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8120,17 +8168,42 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="85" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="2" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -8237,7 +8310,7 @@
         <xdr:cNvPr id="2" name="image1.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{923D6D3B-F2F6-5C47-BDBB-9858FF278790}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{525D372D-6CD5-6C46-A440-B6292532340D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8280,7 +8353,7 @@
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8751CBEF-6415-7141-A406-F38E4A1E2AC9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D56158-9E33-E34A-AB78-6B457E2F1901}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8642,7 +8715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42EAC847-8A31-0A40-A5EE-A9CEE0F87EE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6FC7176-8099-344E-99B9-ADEDCA003754}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -8676,7 +8749,7 @@
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="303"/>
       <c r="B2" s="307" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C2" s="304"/>
       <c r="D2" s="305"/>
@@ -8690,8 +8763,8 @@
     <row r="3" spans="1:12" ht="36.75" customHeight="1">
       <c r="A3" s="303"/>
       <c r="B3" s="303"/>
-      <c r="C3" s="413" t="s">
-        <v>655</v>
+      <c r="C3" s="410" t="s">
+        <v>654</v>
       </c>
       <c r="D3" s="305"/>
       <c r="F3" s="305"/>
@@ -8705,1489 +8778,1489 @@
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
       <c r="A4" s="303"/>
       <c r="B4" s="303"/>
-      <c r="C4" s="378" t="s">
-        <v>660</v>
-      </c>
-      <c r="D4" s="414"/>
-      <c r="E4" s="415"/>
-      <c r="F4" s="415"/>
-      <c r="G4" s="415"/>
-      <c r="H4" s="415"/>
-      <c r="I4" s="415"/>
-      <c r="J4" s="415"/>
-      <c r="K4" s="415"/>
+      <c r="C4" s="375" t="s">
+        <v>659</v>
+      </c>
+      <c r="D4" s="411"/>
+      <c r="E4" s="412"/>
+      <c r="F4" s="412"/>
+      <c r="G4" s="412"/>
+      <c r="H4" s="412"/>
+      <c r="I4" s="412"/>
+      <c r="J4" s="412"/>
+      <c r="K4" s="412"/>
       <c r="L4" s="305"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="303"/>
       <c r="B5" s="303"/>
-      <c r="C5" s="416" t="s">
+      <c r="C5" s="413" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="417" t="s">
-        <v>672</v>
-      </c>
-      <c r="E5" s="418" t="s">
+      <c r="D5" s="414" t="s">
+        <v>671</v>
+      </c>
+      <c r="E5" s="415" t="s">
+        <v>675</v>
+      </c>
+      <c r="F5" s="415" t="s">
+        <v>438</v>
+      </c>
+      <c r="G5" s="415" t="s">
         <v>676</v>
       </c>
-      <c r="F5" s="418" t="s">
-        <v>438</v>
-      </c>
-      <c r="G5" s="418" t="s">
+      <c r="H5" s="415" t="s">
         <v>677</v>
       </c>
-      <c r="H5" s="418" t="s">
+      <c r="I5" s="415" t="s">
         <v>678</v>
       </c>
-      <c r="I5" s="418" t="s">
+      <c r="J5" s="415" t="s">
         <v>679</v>
       </c>
-      <c r="J5" s="418" t="s">
-        <v>680</v>
-      </c>
-      <c r="K5" s="419" t="s">
-        <v>682</v>
+      <c r="K5" s="416" t="s">
+        <v>681</v>
       </c>
       <c r="L5" s="305"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="368"/>
       <c r="B6" s="368"/>
-      <c r="C6" s="420">
+      <c r="C6" s="417">
         <v>1</v>
       </c>
-      <c r="D6" s="421" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E6" s="422"/>
-      <c r="F6" s="422"/>
-      <c r="G6" s="422"/>
-      <c r="H6" s="422"/>
-      <c r="I6" s="422"/>
-      <c r="J6" s="423"/>
-      <c r="K6" s="424"/>
+      <c r="D6" s="418" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E6" s="419"/>
+      <c r="F6" s="419"/>
+      <c r="G6" s="419"/>
+      <c r="H6" s="419"/>
+      <c r="I6" s="419"/>
+      <c r="J6" s="420"/>
+      <c r="K6" s="421"/>
       <c r="L6" s="305"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="303"/>
       <c r="B7" s="303"/>
-      <c r="C7" s="425"/>
-      <c r="E7" s="398" t="s">
-        <v>702</v>
-      </c>
-      <c r="F7" s="426" t="s">
+      <c r="C7" s="422"/>
+      <c r="E7" s="395" t="s">
+        <v>701</v>
+      </c>
+      <c r="F7" s="423" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G7" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="H7" s="395"/>
+      <c r="I7" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J7" s="424"/>
+      <c r="K7" s="421"/>
+      <c r="L7" s="305"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A8" s="376"/>
+      <c r="B8" s="376"/>
+      <c r="C8" s="425"/>
+      <c r="D8" s="304"/>
+      <c r="E8" s="395" t="s">
         <v>1009</v>
       </c>
-      <c r="G7" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="H7" s="398"/>
-      <c r="I7" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J7" s="427"/>
-      <c r="K7" s="424"/>
-      <c r="L7" s="305"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="379"/>
-      <c r="B8" s="379"/>
-      <c r="C8" s="428"/>
-      <c r="D8" s="304"/>
-      <c r="E8" s="398" t="s">
+      <c r="F8" s="395" t="s">
         <v>1010</v>
       </c>
-      <c r="F8" s="398" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G8" s="398"/>
-      <c r="H8" s="398"/>
-      <c r="I8" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J8" s="427"/>
-      <c r="K8" s="424"/>
+      <c r="G8" s="395"/>
+      <c r="H8" s="395"/>
+      <c r="I8" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J8" s="424"/>
+      <c r="K8" s="421"/>
       <c r="L8" s="305"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="368"/>
       <c r="B9" s="368"/>
-      <c r="C9" s="425"/>
-      <c r="E9" s="398" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F9" s="398" t="s">
+      <c r="C9" s="422"/>
+      <c r="E9" s="395" t="s">
         <v>1011</v>
       </c>
-      <c r="G9" s="398"/>
-      <c r="H9" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="I9" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J9" s="427"/>
-      <c r="K9" s="429" t="s">
-        <v>765</v>
+      <c r="F9" s="395" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G9" s="395"/>
+      <c r="H9" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="I9" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J9" s="424"/>
+      <c r="K9" s="426" t="s">
+        <v>764</v>
       </c>
       <c r="L9" s="305"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="A10" s="368"/>
       <c r="B10" s="368"/>
-      <c r="C10" s="425"/>
-      <c r="E10" s="398" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F10" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G10" s="398"/>
-      <c r="H10" s="398"/>
-      <c r="I10" s="426"/>
-      <c r="J10" s="427"/>
-      <c r="K10" s="424"/>
+      <c r="C10" s="422"/>
+      <c r="E10" s="395" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F10" s="395" t="s">
+        <v>731</v>
+      </c>
+      <c r="G10" s="395"/>
+      <c r="H10" s="395"/>
+      <c r="I10" s="423"/>
+      <c r="J10" s="424"/>
+      <c r="K10" s="421"/>
       <c r="L10" s="305"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="368"/>
       <c r="B11" s="368"/>
-      <c r="C11" s="425"/>
-      <c r="E11" s="398" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F11" s="398" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G11" s="398"/>
-      <c r="H11" s="398"/>
-      <c r="I11" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J11" s="427"/>
-      <c r="K11" s="424"/>
+      <c r="C11" s="422"/>
+      <c r="E11" s="395" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F11" s="395" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G11" s="395"/>
+      <c r="H11" s="395"/>
+      <c r="I11" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J11" s="424"/>
+      <c r="K11" s="421"/>
       <c r="L11" s="305"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="368"/>
       <c r="B12" s="368"/>
-      <c r="C12" s="425"/>
-      <c r="E12" s="398" t="s">
+      <c r="C12" s="422"/>
+      <c r="E12" s="395" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F12" s="395" t="s">
         <v>1015</v>
       </c>
-      <c r="F12" s="398" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G12" s="398"/>
-      <c r="H12" s="398"/>
-      <c r="I12" s="398"/>
-      <c r="J12" s="427"/>
-      <c r="K12" s="424"/>
+      <c r="G12" s="395"/>
+      <c r="H12" s="395"/>
+      <c r="I12" s="395"/>
+      <c r="J12" s="424"/>
+      <c r="K12" s="421"/>
       <c r="L12" s="305"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="368"/>
       <c r="B13" s="368"/>
-      <c r="C13" s="425"/>
-      <c r="E13" s="398" t="s">
+      <c r="C13" s="422"/>
+      <c r="E13" s="395" t="s">
+        <v>730</v>
+      </c>
+      <c r="F13" s="395" t="s">
         <v>731</v>
       </c>
-      <c r="F13" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G13" s="398"/>
-      <c r="H13" s="398"/>
-      <c r="I13" s="398"/>
-      <c r="J13" s="427"/>
-      <c r="K13" s="424"/>
+      <c r="G13" s="395"/>
+      <c r="H13" s="395"/>
+      <c r="I13" s="395"/>
+      <c r="J13" s="424"/>
+      <c r="K13" s="421"/>
       <c r="L13" s="305"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
       <c r="A14" s="368"/>
       <c r="B14" s="368"/>
-      <c r="C14" s="425"/>
-      <c r="E14" s="398" t="s">
-        <v>740</v>
-      </c>
-      <c r="F14" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G14" s="398"/>
-      <c r="H14" s="398"/>
-      <c r="I14" s="398"/>
-      <c r="J14" s="427"/>
-      <c r="K14" s="424"/>
+      <c r="C14" s="422"/>
+      <c r="E14" s="395" t="s">
+        <v>739</v>
+      </c>
+      <c r="F14" s="395" t="s">
+        <v>731</v>
+      </c>
+      <c r="G14" s="395"/>
+      <c r="H14" s="395"/>
+      <c r="I14" s="395"/>
+      <c r="J14" s="424"/>
+      <c r="K14" s="421"/>
       <c r="L14" s="305"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="368"/>
       <c r="B15" s="368"/>
-      <c r="C15" s="420">
+      <c r="C15" s="417">
         <v>2</v>
       </c>
-      <c r="D15" s="430" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E15" s="422"/>
-      <c r="F15" s="422"/>
-      <c r="G15" s="422"/>
-      <c r="H15" s="422"/>
-      <c r="I15" s="422"/>
-      <c r="J15" s="423"/>
-      <c r="K15" s="424"/>
+      <c r="D15" s="427" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E15" s="419"/>
+      <c r="F15" s="419"/>
+      <c r="G15" s="419"/>
+      <c r="H15" s="419"/>
+      <c r="I15" s="419"/>
+      <c r="J15" s="420"/>
+      <c r="K15" s="421"/>
       <c r="L15" s="305"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" customHeight="1">
       <c r="A16" s="368"/>
       <c r="B16" s="368"/>
-      <c r="C16" s="425"/>
-      <c r="E16" s="398" t="s">
-        <v>702</v>
+      <c r="C16" s="422"/>
+      <c r="E16" s="395" t="s">
+        <v>701</v>
       </c>
       <c r="F16" s="363" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G16" s="426" t="s">
-        <v>906</v>
-      </c>
-      <c r="H16" s="398"/>
-      <c r="I16" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J16" s="427"/>
-      <c r="K16" s="424"/>
+        <v>1008</v>
+      </c>
+      <c r="G16" s="423" t="s">
+        <v>905</v>
+      </c>
+      <c r="H16" s="395"/>
+      <c r="I16" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J16" s="424"/>
+      <c r="K16" s="421"/>
       <c r="L16" s="305"/>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1">
       <c r="A17" s="368"/>
       <c r="B17" s="368"/>
-      <c r="C17" s="425"/>
+      <c r="C17" s="422"/>
       <c r="D17" s="304"/>
-      <c r="E17" s="398" t="s">
+      <c r="E17" s="395" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F17" s="306" t="s">
         <v>1010</v>
       </c>
-      <c r="F17" s="306" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G17" s="398"/>
-      <c r="H17" s="398"/>
-      <c r="I17" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J17" s="427"/>
-      <c r="K17" s="424"/>
+      <c r="G17" s="395"/>
+      <c r="H17" s="395"/>
+      <c r="I17" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J17" s="424"/>
+      <c r="K17" s="421"/>
       <c r="L17" s="305"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1">
       <c r="A18" s="368"/>
       <c r="B18" s="368"/>
-      <c r="C18" s="425"/>
-      <c r="E18" s="398" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F18" s="398" t="s">
+      <c r="C18" s="422"/>
+      <c r="E18" s="395" t="s">
         <v>1011</v>
       </c>
-      <c r="G18" s="398"/>
-      <c r="H18" s="398" t="s">
-        <v>906</v>
-      </c>
-      <c r="I18" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J18" s="427"/>
-      <c r="K18" s="424"/>
+      <c r="F18" s="395" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G18" s="395"/>
+      <c r="H18" s="395" t="s">
+        <v>905</v>
+      </c>
+      <c r="I18" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J18" s="424"/>
+      <c r="K18" s="421"/>
       <c r="L18" s="305"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1">
       <c r="A19" s="368"/>
       <c r="B19" s="368"/>
-      <c r="C19" s="425"/>
-      <c r="E19" s="398" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F19" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G19" s="398"/>
-      <c r="H19" s="398"/>
-      <c r="I19" s="398"/>
-      <c r="J19" s="427"/>
-      <c r="K19" s="424"/>
+      <c r="C19" s="422"/>
+      <c r="E19" s="395" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F19" s="395" t="s">
+        <v>731</v>
+      </c>
+      <c r="G19" s="395"/>
+      <c r="H19" s="395"/>
+      <c r="I19" s="395"/>
+      <c r="J19" s="424"/>
+      <c r="K19" s="421"/>
       <c r="L19" s="305"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1">
       <c r="A20" s="368"/>
       <c r="B20" s="368"/>
-      <c r="C20" s="425"/>
-      <c r="E20" s="398" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F20" s="398" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G20" s="398"/>
-      <c r="H20" s="398"/>
-      <c r="I20" s="398" t="s">
-        <v>711</v>
-      </c>
-      <c r="J20" s="427"/>
-      <c r="K20" s="424"/>
+      <c r="C20" s="422"/>
+      <c r="E20" s="395" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F20" s="395" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G20" s="395"/>
+      <c r="H20" s="395"/>
+      <c r="I20" s="395" t="s">
+        <v>710</v>
+      </c>
+      <c r="J20" s="424"/>
+      <c r="K20" s="421"/>
       <c r="L20" s="305"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1">
       <c r="A21" s="368"/>
       <c r="B21" s="368"/>
-      <c r="C21" s="425"/>
-      <c r="E21" s="398" t="s">
+      <c r="C21" s="422"/>
+      <c r="E21" s="395" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F21" s="306" t="s">
         <v>1015</v>
       </c>
-      <c r="F21" s="306" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G21" s="398"/>
-      <c r="H21" s="398"/>
-      <c r="I21" s="398"/>
-      <c r="J21" s="427"/>
-      <c r="K21" s="431"/>
+      <c r="G21" s="395"/>
+      <c r="H21" s="395"/>
+      <c r="I21" s="395"/>
+      <c r="J21" s="424"/>
+      <c r="K21" s="428"/>
       <c r="L21" s="305"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A22" s="402"/>
-      <c r="B22" s="402"/>
-      <c r="C22" s="432"/>
-      <c r="E22" s="398" t="s">
+      <c r="A22" s="399"/>
+      <c r="B22" s="399"/>
+      <c r="C22" s="429"/>
+      <c r="E22" s="395" t="s">
+        <v>730</v>
+      </c>
+      <c r="F22" s="395" t="s">
         <v>731</v>
       </c>
-      <c r="F22" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G22" s="398"/>
-      <c r="H22" s="398"/>
-      <c r="I22" s="398"/>
-      <c r="J22" s="427"/>
+      <c r="G22" s="395"/>
+      <c r="H22" s="395"/>
+      <c r="I22" s="395"/>
+      <c r="J22" s="424"/>
       <c r="K22" s="305"/>
       <c r="L22" s="305"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A23" s="402"/>
-      <c r="B23" s="402"/>
-      <c r="C23" s="432"/>
-      <c r="E23" s="398" t="s">
-        <v>740</v>
-      </c>
-      <c r="F23" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G23" s="398"/>
-      <c r="H23" s="398"/>
-      <c r="I23" s="398"/>
-      <c r="J23" s="427"/>
+      <c r="A23" s="399"/>
+      <c r="B23" s="399"/>
+      <c r="C23" s="429"/>
+      <c r="E23" s="395" t="s">
+        <v>739</v>
+      </c>
+      <c r="F23" s="395" t="s">
+        <v>731</v>
+      </c>
+      <c r="G23" s="395"/>
+      <c r="H23" s="395"/>
+      <c r="I23" s="395"/>
+      <c r="J23" s="424"/>
       <c r="K23" s="305"/>
       <c r="L23" s="305"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A24" s="402"/>
-      <c r="B24" s="402"/>
-      <c r="C24" s="433">
+      <c r="A24" s="399"/>
+      <c r="B24" s="399"/>
+      <c r="C24" s="430">
         <v>3</v>
       </c>
-      <c r="D24" s="430" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E24" s="422"/>
-      <c r="F24" s="422"/>
-      <c r="G24" s="422"/>
-      <c r="H24" s="422"/>
-      <c r="I24" s="422"/>
-      <c r="J24" s="423"/>
+      <c r="D24" s="427" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E24" s="419"/>
+      <c r="F24" s="419"/>
+      <c r="G24" s="419"/>
+      <c r="H24" s="419"/>
+      <c r="I24" s="419"/>
+      <c r="J24" s="420"/>
       <c r="K24" s="305"/>
       <c r="L24" s="305"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A25" s="402"/>
-      <c r="B25" s="402"/>
-      <c r="C25" s="432"/>
-      <c r="E25" s="398" t="s">
-        <v>1019</v>
+      <c r="A25" s="399"/>
+      <c r="B25" s="399"/>
+      <c r="C25" s="429"/>
+      <c r="E25" s="395" t="s">
+        <v>1018</v>
       </c>
       <c r="F25" s="363" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G25" s="426" t="s">
-        <v>906</v>
-      </c>
-      <c r="H25" s="398"/>
-      <c r="I25" s="426" t="s">
-        <v>906</v>
-      </c>
-      <c r="J25" s="427"/>
+        <v>1008</v>
+      </c>
+      <c r="G25" s="423" t="s">
+        <v>905</v>
+      </c>
+      <c r="H25" s="395"/>
+      <c r="I25" s="423" t="s">
+        <v>905</v>
+      </c>
+      <c r="J25" s="424"/>
       <c r="K25" s="305"/>
       <c r="L25" s="305"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A26" s="402"/>
-      <c r="B26" s="402"/>
-      <c r="C26" s="432"/>
+      <c r="A26" s="399"/>
+      <c r="B26" s="399"/>
+      <c r="C26" s="429"/>
       <c r="D26" s="312" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E26" s="395" t="s">
+        <v>989</v>
+      </c>
+      <c r="F26" s="363" t="s">
         <v>1020</v>
       </c>
-      <c r="E26" s="398" t="s">
-        <v>990</v>
-      </c>
-      <c r="F26" s="363" t="s">
+      <c r="G26" s="423"/>
+      <c r="H26" s="395" t="s">
+        <v>905</v>
+      </c>
+      <c r="I26" s="423" t="s">
+        <v>905</v>
+      </c>
+      <c r="J26" s="424" t="s">
         <v>1021</v>
-      </c>
-      <c r="G26" s="426"/>
-      <c r="H26" s="398" t="s">
-        <v>906</v>
-      </c>
-      <c r="I26" s="426" t="s">
-        <v>906</v>
-      </c>
-      <c r="J26" s="427" t="s">
-        <v>1022</v>
       </c>
       <c r="K26" s="305"/>
       <c r="L26" s="305"/>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A27" s="402"/>
-      <c r="B27" s="402"/>
-      <c r="C27" s="432"/>
+      <c r="A27" s="399"/>
+      <c r="B27" s="399"/>
+      <c r="C27" s="429"/>
       <c r="D27" s="312"/>
-      <c r="E27" s="398" t="s">
-        <v>992</v>
+      <c r="E27" s="395" t="s">
+        <v>991</v>
       </c>
       <c r="F27" s="363" t="s">
-        <v>992</v>
-      </c>
-      <c r="G27" s="426"/>
-      <c r="H27" s="398" t="s">
-        <v>906</v>
-      </c>
-      <c r="I27" s="426"/>
-      <c r="J27" s="427"/>
+        <v>991</v>
+      </c>
+      <c r="G27" s="423"/>
+      <c r="H27" s="395" t="s">
+        <v>905</v>
+      </c>
+      <c r="I27" s="423"/>
+      <c r="J27" s="424"/>
       <c r="K27" s="305"/>
       <c r="L27" s="305"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A28" s="402"/>
-      <c r="B28" s="402"/>
-      <c r="C28" s="432"/>
+      <c r="A28" s="399"/>
+      <c r="B28" s="399"/>
+      <c r="C28" s="429"/>
       <c r="D28" s="304"/>
-      <c r="E28" s="398" t="s">
-        <v>1001</v>
+      <c r="E28" s="395" t="s">
+        <v>1000</v>
       </c>
       <c r="F28" s="363" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G28" s="398"/>
-      <c r="H28" s="398"/>
-      <c r="I28" s="426" t="s">
-        <v>906</v>
-      </c>
-      <c r="J28" s="427"/>
+        <v>1022</v>
+      </c>
+      <c r="G28" s="395"/>
+      <c r="H28" s="395"/>
+      <c r="I28" s="423" t="s">
+        <v>905</v>
+      </c>
+      <c r="J28" s="424"/>
       <c r="K28" s="305"/>
       <c r="L28" s="305"/>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A29" s="402"/>
-      <c r="B29" s="402"/>
-      <c r="C29" s="432"/>
-      <c r="E29" s="398" t="s">
-        <v>1002</v>
+      <c r="A29" s="399"/>
+      <c r="B29" s="399"/>
+      <c r="C29" s="429"/>
+      <c r="E29" s="395" t="s">
+        <v>1001</v>
       </c>
       <c r="F29" s="363" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G29" s="398"/>
-      <c r="H29" s="398"/>
-      <c r="I29" s="426"/>
-      <c r="J29" s="427"/>
+        <v>1022</v>
+      </c>
+      <c r="G29" s="395"/>
+      <c r="H29" s="395"/>
+      <c r="I29" s="423"/>
+      <c r="J29" s="424"/>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A30" s="402"/>
-      <c r="B30" s="402"/>
-      <c r="C30" s="432"/>
-      <c r="D30" s="434"/>
-      <c r="E30" s="435" t="s">
+      <c r="A30" s="399"/>
+      <c r="B30" s="399"/>
+      <c r="C30" s="429"/>
+      <c r="D30" s="431"/>
+      <c r="E30" s="432" t="s">
+        <v>730</v>
+      </c>
+      <c r="F30" s="432" t="s">
         <v>731</v>
       </c>
-      <c r="F30" s="435" t="s">
-        <v>732</v>
-      </c>
-      <c r="G30" s="435"/>
-      <c r="H30" s="435"/>
-      <c r="I30" s="435"/>
-      <c r="J30" s="436"/>
+      <c r="G30" s="432"/>
+      <c r="H30" s="432"/>
+      <c r="I30" s="432"/>
+      <c r="J30" s="433"/>
       <c r="K30" s="305"/>
       <c r="L30" s="305"/>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A31" s="402"/>
-      <c r="B31" s="402"/>
-      <c r="C31" s="432"/>
-      <c r="D31" s="437"/>
-      <c r="E31" s="435" t="s">
-        <v>740</v>
-      </c>
-      <c r="F31" s="435" t="s">
-        <v>732</v>
-      </c>
-      <c r="G31" s="435"/>
-      <c r="H31" s="435"/>
-      <c r="I31" s="435"/>
-      <c r="J31" s="436"/>
+      <c r="A31" s="399"/>
+      <c r="B31" s="399"/>
+      <c r="C31" s="429"/>
+      <c r="D31" s="434"/>
+      <c r="E31" s="432" t="s">
+        <v>739</v>
+      </c>
+      <c r="F31" s="432" t="s">
+        <v>731</v>
+      </c>
+      <c r="G31" s="432"/>
+      <c r="H31" s="432"/>
+      <c r="I31" s="432"/>
+      <c r="J31" s="433"/>
       <c r="K31" s="305"/>
       <c r="L31" s="305"/>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A32" s="402"/>
-      <c r="B32" s="402"/>
-      <c r="C32" s="432"/>
-      <c r="D32" s="438"/>
-      <c r="E32" s="439" t="s">
+      <c r="A32" s="399"/>
+      <c r="B32" s="399"/>
+      <c r="C32" s="429"/>
+      <c r="D32" s="435"/>
+      <c r="E32" s="436" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F32" s="437"/>
+      <c r="G32" s="438"/>
+      <c r="H32" s="437" t="s">
         <v>1024</v>
       </c>
-      <c r="F32" s="440"/>
-      <c r="G32" s="441"/>
-      <c r="H32" s="440" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I32" s="440"/>
-      <c r="J32" s="442"/>
+      <c r="I32" s="437"/>
+      <c r="J32" s="439"/>
       <c r="K32" s="305"/>
       <c r="L32" s="305"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A33" s="402"/>
-      <c r="B33" s="402"/>
-      <c r="C33" s="433">
+      <c r="A33" s="399"/>
+      <c r="B33" s="399"/>
+      <c r="C33" s="430">
         <v>4</v>
       </c>
-      <c r="D33" s="430" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E33" s="422"/>
-      <c r="F33" s="422"/>
-      <c r="G33" s="422"/>
-      <c r="H33" s="422"/>
-      <c r="I33" s="422"/>
-      <c r="J33" s="423"/>
+      <c r="D33" s="427" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E33" s="419"/>
+      <c r="F33" s="419"/>
+      <c r="G33" s="419"/>
+      <c r="H33" s="419"/>
+      <c r="I33" s="419"/>
+      <c r="J33" s="420"/>
       <c r="K33" s="305"/>
       <c r="L33" s="305"/>
     </row>
     <row r="34" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A34" s="402"/>
-      <c r="B34" s="402"/>
-      <c r="C34" s="432"/>
-      <c r="E34" s="398" t="s">
-        <v>702</v>
-      </c>
-      <c r="F34" s="398" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G34" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="H34" s="398"/>
-      <c r="I34" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J34" s="427"/>
+      <c r="A34" s="399"/>
+      <c r="B34" s="399"/>
+      <c r="C34" s="429"/>
+      <c r="E34" s="395" t="s">
+        <v>701</v>
+      </c>
+      <c r="F34" s="395" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G34" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="H34" s="395"/>
+      <c r="I34" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J34" s="424"/>
       <c r="K34" s="305"/>
       <c r="L34" s="305"/>
     </row>
     <row r="35" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A35" s="402"/>
-      <c r="B35" s="402"/>
-      <c r="C35" s="432"/>
+      <c r="A35" s="399"/>
+      <c r="B35" s="399"/>
+      <c r="C35" s="429"/>
       <c r="D35" s="312" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E35" s="398" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E35" s="395" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F35" s="395" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G35" s="423"/>
+      <c r="H35" s="395"/>
+      <c r="I35" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J35" s="424" t="s">
         <v>1027</v>
-      </c>
-      <c r="F35" s="398" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G35" s="426"/>
-      <c r="H35" s="398"/>
-      <c r="I35" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J35" s="427" t="s">
-        <v>1028</v>
       </c>
       <c r="K35" s="305"/>
       <c r="L35" s="305"/>
     </row>
     <row r="36" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A36" s="402"/>
-      <c r="B36" s="402"/>
-      <c r="C36" s="432"/>
+      <c r="A36" s="399"/>
+      <c r="B36" s="399"/>
+      <c r="C36" s="429"/>
       <c r="D36" s="304"/>
-      <c r="E36" s="398" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F36" s="398" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G36" s="398"/>
-      <c r="H36" s="398"/>
-      <c r="I36" s="426"/>
-      <c r="J36" s="443"/>
+      <c r="E36" s="395" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F36" s="395" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G36" s="395"/>
+      <c r="H36" s="395"/>
+      <c r="I36" s="423"/>
+      <c r="J36" s="440"/>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
     </row>
     <row r="37" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A37" s="402"/>
-      <c r="B37" s="402"/>
-      <c r="C37" s="432"/>
-      <c r="E37" s="398" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F37" s="398" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G37" s="398"/>
-      <c r="H37" s="398"/>
-      <c r="I37" s="426"/>
-      <c r="J37" s="427"/>
+      <c r="A37" s="399"/>
+      <c r="B37" s="399"/>
+      <c r="C37" s="429"/>
+      <c r="E37" s="395" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F37" s="395" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G37" s="395"/>
+      <c r="H37" s="395"/>
+      <c r="I37" s="423"/>
+      <c r="J37" s="424"/>
       <c r="K37" s="305"/>
       <c r="L37" s="305"/>
     </row>
     <row r="38" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A38" s="402"/>
-      <c r="B38" s="402"/>
-      <c r="C38" s="432"/>
-      <c r="E38" s="398" t="s">
+      <c r="A38" s="399"/>
+      <c r="B38" s="399"/>
+      <c r="C38" s="429"/>
+      <c r="E38" s="395" t="s">
+        <v>730</v>
+      </c>
+      <c r="F38" s="395" t="s">
         <v>731</v>
       </c>
-      <c r="F38" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G38" s="398"/>
-      <c r="H38" s="398"/>
-      <c r="I38" s="398"/>
-      <c r="J38" s="427"/>
+      <c r="G38" s="395"/>
+      <c r="H38" s="395"/>
+      <c r="I38" s="395"/>
+      <c r="J38" s="424"/>
       <c r="K38" s="305"/>
       <c r="L38" s="305"/>
     </row>
     <row r="39" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A39" s="402"/>
-      <c r="B39" s="402"/>
-      <c r="C39" s="432"/>
-      <c r="E39" s="398" t="s">
-        <v>740</v>
-      </c>
-      <c r="F39" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G39" s="398"/>
-      <c r="H39" s="398"/>
-      <c r="I39" s="398"/>
-      <c r="J39" s="427"/>
+      <c r="A39" s="399"/>
+      <c r="B39" s="399"/>
+      <c r="C39" s="429"/>
+      <c r="E39" s="395" t="s">
+        <v>739</v>
+      </c>
+      <c r="F39" s="395" t="s">
+        <v>731</v>
+      </c>
+      <c r="G39" s="395"/>
+      <c r="H39" s="395"/>
+      <c r="I39" s="395"/>
+      <c r="J39" s="424"/>
       <c r="K39" s="305"/>
       <c r="L39" s="305"/>
     </row>
     <row r="40" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A40" s="402"/>
-      <c r="B40" s="402"/>
-      <c r="C40" s="433">
+      <c r="A40" s="399"/>
+      <c r="B40" s="399"/>
+      <c r="C40" s="430">
         <v>5</v>
       </c>
-      <c r="D40" s="465" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E40" s="466"/>
-      <c r="F40" s="466"/>
-      <c r="G40" s="466"/>
-      <c r="H40" s="466"/>
-      <c r="I40" s="422"/>
-      <c r="J40" s="423"/>
+      <c r="D40" s="462" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
+      <c r="G40" s="463"/>
+      <c r="H40" s="463"/>
+      <c r="I40" s="419"/>
+      <c r="J40" s="420"/>
       <c r="K40" s="305"/>
       <c r="L40" s="305"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A41" s="402"/>
-      <c r="B41" s="402"/>
-      <c r="C41" s="432"/>
-      <c r="E41" s="398" t="s">
-        <v>1019</v>
+      <c r="A41" s="399"/>
+      <c r="B41" s="399"/>
+      <c r="C41" s="429"/>
+      <c r="E41" s="395" t="s">
+        <v>1018</v>
       </c>
       <c r="F41" s="363" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G41" s="426" t="s">
-        <v>906</v>
-      </c>
-      <c r="H41" s="398"/>
-      <c r="I41" s="426" t="s">
-        <v>906</v>
-      </c>
-      <c r="J41" s="427"/>
+        <v>1008</v>
+      </c>
+      <c r="G41" s="423" t="s">
+        <v>905</v>
+      </c>
+      <c r="H41" s="395"/>
+      <c r="I41" s="423" t="s">
+        <v>905</v>
+      </c>
+      <c r="J41" s="424"/>
       <c r="K41" s="305"/>
       <c r="L41" s="305"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A42" s="402"/>
-      <c r="B42" s="402"/>
-      <c r="C42" s="432"/>
+      <c r="A42" s="399"/>
+      <c r="B42" s="399"/>
+      <c r="C42" s="429"/>
       <c r="D42" s="306" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E42" s="398" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E42" s="395" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F42" s="363" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G42" s="423"/>
+      <c r="H42" s="395"/>
+      <c r="I42" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J42" s="424" t="s">
         <v>1027</v>
-      </c>
-      <c r="F42" s="363" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G42" s="426"/>
-      <c r="H42" s="398"/>
-      <c r="I42" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J42" s="427" t="s">
-        <v>1028</v>
       </c>
       <c r="K42" s="305"/>
       <c r="L42" s="305"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A43" s="402"/>
-      <c r="B43" s="402"/>
-      <c r="C43" s="432"/>
-      <c r="E43" s="398" t="s">
-        <v>973</v>
-      </c>
-      <c r="F43" s="398" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G43" s="398"/>
-      <c r="H43" s="398"/>
-      <c r="I43" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J43" s="427"/>
+      <c r="A43" s="399"/>
+      <c r="B43" s="399"/>
+      <c r="C43" s="429"/>
+      <c r="E43" s="395" t="s">
+        <v>972</v>
+      </c>
+      <c r="F43" s="395" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G43" s="395"/>
+      <c r="H43" s="395"/>
+      <c r="I43" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J43" s="424"/>
       <c r="K43" s="305"/>
       <c r="L43" s="305"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A44" s="402"/>
-      <c r="B44" s="402"/>
-      <c r="C44" s="432"/>
-      <c r="E44" s="398" t="s">
-        <v>975</v>
-      </c>
-      <c r="F44" s="444" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G44" s="398"/>
-      <c r="H44" s="398"/>
-      <c r="I44" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J44" s="427"/>
+      <c r="A44" s="399"/>
+      <c r="B44" s="399"/>
+      <c r="C44" s="429"/>
+      <c r="E44" s="395" t="s">
+        <v>974</v>
+      </c>
+      <c r="F44" s="441" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G44" s="395"/>
+      <c r="H44" s="395"/>
+      <c r="I44" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J44" s="424"/>
       <c r="K44" s="305"/>
       <c r="L44" s="305"/>
     </row>
     <row r="45" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A45" s="402"/>
-      <c r="B45" s="402"/>
-      <c r="C45" s="432"/>
-      <c r="E45" s="398" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F45" s="398" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G45" s="398"/>
-      <c r="H45" s="398"/>
-      <c r="I45" s="426" t="s">
-        <v>711</v>
-      </c>
-      <c r="J45" s="427"/>
+      <c r="A45" s="399"/>
+      <c r="B45" s="399"/>
+      <c r="C45" s="429"/>
+      <c r="E45" s="395" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F45" s="395" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G45" s="395"/>
+      <c r="H45" s="395"/>
+      <c r="I45" s="423" t="s">
+        <v>710</v>
+      </c>
+      <c r="J45" s="424"/>
       <c r="K45" s="305"/>
       <c r="L45" s="305"/>
     </row>
     <row r="46" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A46" s="402"/>
-      <c r="B46" s="402"/>
-      <c r="C46" s="432"/>
-      <c r="D46" s="445" t="s">
+      <c r="A46" s="399"/>
+      <c r="B46" s="399"/>
+      <c r="C46" s="429"/>
+      <c r="D46" s="442" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E46" s="395" t="s">
         <v>1034</v>
       </c>
-      <c r="E46" s="398" t="s">
+      <c r="F46" s="395" t="s">
         <v>1035</v>
       </c>
-      <c r="F46" s="398" t="s">
-        <v>1036</v>
-      </c>
-      <c r="G46" s="398"/>
-      <c r="H46" s="398"/>
-      <c r="I46" s="398" t="s">
-        <v>906</v>
-      </c>
-      <c r="J46" s="427"/>
+      <c r="G46" s="395"/>
+      <c r="H46" s="395"/>
+      <c r="I46" s="395" t="s">
+        <v>905</v>
+      </c>
+      <c r="J46" s="424"/>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
     </row>
     <row r="47" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A47" s="402"/>
-      <c r="B47" s="402"/>
-      <c r="C47" s="432"/>
-      <c r="D47" s="434"/>
-      <c r="E47" s="435" t="s">
+      <c r="A47" s="399"/>
+      <c r="B47" s="399"/>
+      <c r="C47" s="429"/>
+      <c r="D47" s="431"/>
+      <c r="E47" s="432" t="s">
+        <v>730</v>
+      </c>
+      <c r="F47" s="432" t="s">
         <v>731</v>
       </c>
-      <c r="F47" s="435" t="s">
-        <v>732</v>
-      </c>
-      <c r="G47" s="435"/>
-      <c r="H47" s="435"/>
-      <c r="I47" s="435"/>
-      <c r="J47" s="436"/>
+      <c r="G47" s="432"/>
+      <c r="H47" s="432"/>
+      <c r="I47" s="432"/>
+      <c r="J47" s="433"/>
       <c r="K47" s="305"/>
       <c r="L47" s="305"/>
     </row>
     <row r="48" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A48" s="402"/>
-      <c r="B48" s="402"/>
-      <c r="C48" s="446"/>
-      <c r="D48" s="438"/>
-      <c r="E48" s="435" t="s">
-        <v>740</v>
-      </c>
-      <c r="F48" s="435" t="s">
-        <v>732</v>
-      </c>
-      <c r="G48" s="435"/>
-      <c r="H48" s="435"/>
-      <c r="I48" s="435"/>
-      <c r="J48" s="436"/>
+      <c r="A48" s="399"/>
+      <c r="B48" s="399"/>
+      <c r="C48" s="443"/>
+      <c r="D48" s="435"/>
+      <c r="E48" s="432" t="s">
+        <v>739</v>
+      </c>
+      <c r="F48" s="432" t="s">
+        <v>731</v>
+      </c>
+      <c r="G48" s="432"/>
+      <c r="H48" s="432"/>
+      <c r="I48" s="432"/>
+      <c r="J48" s="433"/>
       <c r="K48" s="305"/>
       <c r="L48" s="305"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A49" s="402"/>
-      <c r="B49" s="402"/>
-      <c r="C49" s="433">
+      <c r="A49" s="399"/>
+      <c r="B49" s="399"/>
+      <c r="C49" s="430">
         <v>6</v>
       </c>
-      <c r="D49" s="421" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E49" s="422"/>
-      <c r="F49" s="422"/>
-      <c r="G49" s="422"/>
-      <c r="H49" s="422"/>
-      <c r="I49" s="422"/>
-      <c r="J49" s="423"/>
+      <c r="D49" s="418" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E49" s="419"/>
+      <c r="F49" s="419"/>
+      <c r="G49" s="419"/>
+      <c r="H49" s="419"/>
+      <c r="I49" s="419"/>
+      <c r="J49" s="420"/>
       <c r="K49" s="305"/>
       <c r="L49" s="305"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A50" s="402"/>
-      <c r="B50" s="402"/>
-      <c r="C50" s="432"/>
-      <c r="E50" s="398" t="s">
-        <v>702</v>
-      </c>
-      <c r="F50" s="398" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G50" s="398" t="s">
-        <v>711</v>
-      </c>
-      <c r="H50" s="398"/>
-      <c r="I50" s="398" t="s">
-        <v>711</v>
-      </c>
-      <c r="J50" s="427"/>
+      <c r="A50" s="399"/>
+      <c r="B50" s="399"/>
+      <c r="C50" s="429"/>
+      <c r="E50" s="395" t="s">
+        <v>701</v>
+      </c>
+      <c r="F50" s="395" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G50" s="395" t="s">
+        <v>710</v>
+      </c>
+      <c r="H50" s="395"/>
+      <c r="I50" s="395" t="s">
+        <v>710</v>
+      </c>
+      <c r="J50" s="424"/>
       <c r="K50" s="305"/>
       <c r="L50" s="305"/>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A51" s="402"/>
-      <c r="B51" s="402"/>
-      <c r="C51" s="432"/>
+      <c r="A51" s="399"/>
+      <c r="B51" s="399"/>
+      <c r="C51" s="429"/>
       <c r="D51" s="312" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E51" s="398" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E51" s="395" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F51" s="395" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G51" s="395"/>
+      <c r="H51" s="395"/>
+      <c r="I51" s="395" t="s">
+        <v>905</v>
+      </c>
+      <c r="J51" s="424" t="s">
         <v>1038</v>
-      </c>
-      <c r="F51" s="398" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G51" s="398"/>
-      <c r="H51" s="398"/>
-      <c r="I51" s="398" t="s">
-        <v>906</v>
-      </c>
-      <c r="J51" s="427" t="s">
-        <v>1039</v>
       </c>
       <c r="K51" s="305"/>
       <c r="L51" s="305"/>
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A52" s="402"/>
-      <c r="B52" s="402"/>
-      <c r="C52" s="432"/>
-      <c r="E52" s="398" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F52" s="398" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G52" s="398"/>
-      <c r="H52" s="398"/>
-      <c r="I52" s="398"/>
-      <c r="J52" s="427"/>
+      <c r="A52" s="399"/>
+      <c r="B52" s="399"/>
+      <c r="C52" s="429"/>
+      <c r="E52" s="395" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F52" s="395" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G52" s="395"/>
+      <c r="H52" s="395"/>
+      <c r="I52" s="395"/>
+      <c r="J52" s="424"/>
       <c r="K52" s="305"/>
       <c r="L52" s="305"/>
     </row>
     <row r="53" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A53" s="402"/>
-      <c r="B53" s="402"/>
-      <c r="C53" s="432"/>
-      <c r="E53" s="398" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F53" s="398" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G53" s="398"/>
-      <c r="H53" s="398"/>
-      <c r="I53" s="398"/>
-      <c r="J53" s="427"/>
+      <c r="A53" s="399"/>
+      <c r="B53" s="399"/>
+      <c r="C53" s="429"/>
+      <c r="E53" s="395" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F53" s="395" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G53" s="395"/>
+      <c r="H53" s="395"/>
+      <c r="I53" s="395"/>
+      <c r="J53" s="424"/>
       <c r="K53" s="305"/>
       <c r="L53" s="305"/>
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A54" s="402"/>
-      <c r="B54" s="402"/>
-      <c r="C54" s="432"/>
-      <c r="E54" s="398" t="s">
+      <c r="A54" s="399"/>
+      <c r="B54" s="399"/>
+      <c r="C54" s="429"/>
+      <c r="E54" s="395" t="s">
+        <v>730</v>
+      </c>
+      <c r="F54" s="395" t="s">
         <v>731</v>
       </c>
-      <c r="F54" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G54" s="398"/>
-      <c r="H54" s="398"/>
-      <c r="I54" s="398"/>
-      <c r="J54" s="427"/>
+      <c r="G54" s="395"/>
+      <c r="H54" s="395"/>
+      <c r="I54" s="395"/>
+      <c r="J54" s="424"/>
       <c r="K54" s="305"/>
       <c r="L54" s="305"/>
     </row>
     <row r="55" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A55" s="402"/>
-      <c r="B55" s="402"/>
-      <c r="C55" s="432"/>
-      <c r="E55" s="398" t="s">
-        <v>740</v>
-      </c>
-      <c r="F55" s="398" t="s">
-        <v>732</v>
-      </c>
-      <c r="G55" s="398"/>
-      <c r="H55" s="398"/>
-      <c r="I55" s="398"/>
-      <c r="J55" s="427"/>
+      <c r="A55" s="399"/>
+      <c r="B55" s="399"/>
+      <c r="C55" s="429"/>
+      <c r="E55" s="395" t="s">
+        <v>739</v>
+      </c>
+      <c r="F55" s="395" t="s">
+        <v>731</v>
+      </c>
+      <c r="G55" s="395"/>
+      <c r="H55" s="395"/>
+      <c r="I55" s="395"/>
+      <c r="J55" s="424"/>
       <c r="K55" s="305"/>
       <c r="L55" s="305"/>
     </row>
     <row r="56" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A56" s="402"/>
-      <c r="B56" s="402"/>
-      <c r="C56" s="433">
+      <c r="A56" s="399"/>
+      <c r="B56" s="399"/>
+      <c r="C56" s="430">
         <v>7</v>
       </c>
-      <c r="D56" s="421" t="s">
-        <v>749</v>
-      </c>
-      <c r="E56" s="422"/>
-      <c r="F56" s="422"/>
-      <c r="G56" s="422"/>
-      <c r="H56" s="422"/>
-      <c r="I56" s="422"/>
-      <c r="J56" s="423"/>
+      <c r="D56" s="418" t="s">
+        <v>748</v>
+      </c>
+      <c r="E56" s="419"/>
+      <c r="F56" s="419"/>
+      <c r="G56" s="419"/>
+      <c r="H56" s="419"/>
+      <c r="I56" s="419"/>
+      <c r="J56" s="420"/>
       <c r="K56" s="305"/>
       <c r="L56" s="305"/>
     </row>
     <row r="57" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A57" s="402"/>
-      <c r="B57" s="402"/>
-      <c r="C57" s="432"/>
-      <c r="E57" s="398"/>
+      <c r="A57" s="399"/>
+      <c r="B57" s="399"/>
+      <c r="C57" s="429"/>
+      <c r="E57" s="395"/>
       <c r="F57" s="363"/>
-      <c r="G57" s="426"/>
-      <c r="H57" s="398"/>
-      <c r="I57" s="426"/>
-      <c r="J57" s="427"/>
+      <c r="G57" s="423"/>
+      <c r="H57" s="395"/>
+      <c r="I57" s="423"/>
+      <c r="J57" s="424"/>
       <c r="K57" s="305"/>
       <c r="L57" s="305"/>
     </row>
     <row r="58" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A58" s="402"/>
-      <c r="B58" s="402"/>
-      <c r="C58" s="432"/>
-      <c r="E58" s="398"/>
+      <c r="A58" s="399"/>
+      <c r="B58" s="399"/>
+      <c r="C58" s="429"/>
+      <c r="E58" s="395"/>
       <c r="F58" s="363"/>
-      <c r="G58" s="398"/>
-      <c r="H58" s="398"/>
-      <c r="I58" s="426"/>
-      <c r="J58" s="427"/>
+      <c r="G58" s="395"/>
+      <c r="H58" s="395"/>
+      <c r="I58" s="423"/>
+      <c r="J58" s="424"/>
       <c r="K58" s="305"/>
       <c r="L58" s="305"/>
     </row>
     <row r="59" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A59" s="402"/>
-      <c r="B59" s="402"/>
-      <c r="C59" s="432"/>
+      <c r="A59" s="399"/>
+      <c r="B59" s="399"/>
+      <c r="C59" s="429"/>
       <c r="D59" s="312"/>
-      <c r="E59" s="398"/>
+      <c r="E59" s="395"/>
       <c r="F59" s="363"/>
-      <c r="G59" s="398"/>
-      <c r="H59" s="426"/>
-      <c r="I59" s="426"/>
-      <c r="J59" s="427"/>
+      <c r="G59" s="395"/>
+      <c r="H59" s="423"/>
+      <c r="I59" s="423"/>
+      <c r="J59" s="424"/>
       <c r="K59" s="305"/>
       <c r="L59" s="305"/>
     </row>
     <row r="60" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A60" s="402"/>
-      <c r="B60" s="402"/>
-      <c r="C60" s="432"/>
-      <c r="E60" s="398"/>
-      <c r="F60" s="398"/>
-      <c r="G60" s="398"/>
-      <c r="H60" s="398"/>
-      <c r="I60" s="398"/>
-      <c r="J60" s="427"/>
+      <c r="A60" s="399"/>
+      <c r="B60" s="399"/>
+      <c r="C60" s="429"/>
+      <c r="E60" s="395"/>
+      <c r="F60" s="395"/>
+      <c r="G60" s="395"/>
+      <c r="H60" s="395"/>
+      <c r="I60" s="395"/>
+      <c r="J60" s="424"/>
       <c r="K60" s="305"/>
       <c r="L60" s="305"/>
     </row>
     <row r="61" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A61" s="402"/>
-      <c r="B61" s="402"/>
-      <c r="C61" s="432"/>
-      <c r="E61" s="398"/>
-      <c r="F61" s="398"/>
-      <c r="G61" s="398"/>
-      <c r="H61" s="398"/>
-      <c r="I61" s="398"/>
-      <c r="J61" s="427"/>
+      <c r="A61" s="399"/>
+      <c r="B61" s="399"/>
+      <c r="C61" s="429"/>
+      <c r="E61" s="395"/>
+      <c r="F61" s="395"/>
+      <c r="G61" s="395"/>
+      <c r="H61" s="395"/>
+      <c r="I61" s="395"/>
+      <c r="J61" s="424"/>
       <c r="K61" s="305"/>
       <c r="L61" s="305"/>
     </row>
     <row r="62" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A62" s="402"/>
-      <c r="B62" s="402"/>
-      <c r="C62" s="432"/>
+      <c r="A62" s="399"/>
+      <c r="B62" s="399"/>
+      <c r="C62" s="429"/>
       <c r="E62" s="364"/>
-      <c r="F62" s="398"/>
-      <c r="G62" s="398"/>
-      <c r="H62" s="398"/>
-      <c r="I62" s="398"/>
-      <c r="J62" s="427"/>
+      <c r="F62" s="395"/>
+      <c r="G62" s="395"/>
+      <c r="H62" s="395"/>
+      <c r="I62" s="395"/>
+      <c r="J62" s="424"/>
       <c r="K62" s="305"/>
       <c r="L62" s="305"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A63" s="402"/>
-      <c r="B63" s="402"/>
-      <c r="C63" s="433">
+      <c r="A63" s="399"/>
+      <c r="B63" s="399"/>
+      <c r="C63" s="430">
         <v>8</v>
       </c>
-      <c r="D63" s="421" t="s">
-        <v>749</v>
-      </c>
-      <c r="E63" s="422"/>
-      <c r="F63" s="422"/>
-      <c r="G63" s="422"/>
-      <c r="H63" s="422"/>
-      <c r="I63" s="422"/>
-      <c r="J63" s="423"/>
+      <c r="D63" s="418" t="s">
+        <v>748</v>
+      </c>
+      <c r="E63" s="419"/>
+      <c r="F63" s="419"/>
+      <c r="G63" s="419"/>
+      <c r="H63" s="419"/>
+      <c r="I63" s="419"/>
+      <c r="J63" s="420"/>
       <c r="K63" s="305"/>
       <c r="L63" s="305"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A64" s="402"/>
-      <c r="B64" s="402"/>
-      <c r="C64" s="432"/>
-      <c r="E64" s="398"/>
-      <c r="F64" s="398"/>
-      <c r="G64" s="398"/>
-      <c r="H64" s="398"/>
-      <c r="I64" s="398"/>
-      <c r="J64" s="427"/>
+      <c r="A64" s="399"/>
+      <c r="B64" s="399"/>
+      <c r="C64" s="429"/>
+      <c r="E64" s="395"/>
+      <c r="F64" s="395"/>
+      <c r="G64" s="395"/>
+      <c r="H64" s="395"/>
+      <c r="I64" s="395"/>
+      <c r="J64" s="424"/>
       <c r="K64" s="305"/>
       <c r="L64" s="305"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A65" s="402"/>
-      <c r="B65" s="402"/>
-      <c r="C65" s="432"/>
+      <c r="A65" s="399"/>
+      <c r="B65" s="399"/>
+      <c r="C65" s="429"/>
       <c r="D65" s="304"/>
-      <c r="E65" s="398"/>
-      <c r="F65" s="398"/>
-      <c r="G65" s="398"/>
-      <c r="H65" s="398"/>
-      <c r="I65" s="398"/>
-      <c r="J65" s="427"/>
+      <c r="E65" s="395"/>
+      <c r="F65" s="395"/>
+      <c r="G65" s="395"/>
+      <c r="H65" s="395"/>
+      <c r="I65" s="395"/>
+      <c r="J65" s="424"/>
       <c r="K65" s="305"/>
       <c r="L65" s="305"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A66" s="402"/>
-      <c r="B66" s="402"/>
-      <c r="C66" s="432"/>
-      <c r="E66" s="398"/>
-      <c r="F66" s="398"/>
-      <c r="G66" s="398"/>
-      <c r="H66" s="398"/>
-      <c r="I66" s="398"/>
-      <c r="J66" s="427"/>
+      <c r="A66" s="399"/>
+      <c r="B66" s="399"/>
+      <c r="C66" s="429"/>
+      <c r="E66" s="395"/>
+      <c r="F66" s="395"/>
+      <c r="G66" s="395"/>
+      <c r="H66" s="395"/>
+      <c r="I66" s="395"/>
+      <c r="J66" s="424"/>
       <c r="K66" s="305"/>
       <c r="L66" s="305"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A67" s="402"/>
-      <c r="B67" s="402"/>
-      <c r="C67" s="432"/>
-      <c r="E67" s="398"/>
-      <c r="F67" s="398"/>
-      <c r="G67" s="398"/>
-      <c r="H67" s="398"/>
-      <c r="I67" s="398"/>
-      <c r="J67" s="427"/>
+      <c r="A67" s="399"/>
+      <c r="B67" s="399"/>
+      <c r="C67" s="429"/>
+      <c r="E67" s="395"/>
+      <c r="F67" s="395"/>
+      <c r="G67" s="395"/>
+      <c r="H67" s="395"/>
+      <c r="I67" s="395"/>
+      <c r="J67" s="424"/>
       <c r="K67" s="305"/>
       <c r="L67" s="305"/>
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A68" s="402"/>
-      <c r="B68" s="402"/>
-      <c r="C68" s="432"/>
-      <c r="E68" s="398"/>
-      <c r="F68" s="398"/>
-      <c r="G68" s="398"/>
-      <c r="H68" s="398"/>
-      <c r="I68" s="398"/>
-      <c r="J68" s="427"/>
+      <c r="A68" s="399"/>
+      <c r="B68" s="399"/>
+      <c r="C68" s="429"/>
+      <c r="E68" s="395"/>
+      <c r="F68" s="395"/>
+      <c r="G68" s="395"/>
+      <c r="H68" s="395"/>
+      <c r="I68" s="395"/>
+      <c r="J68" s="424"/>
       <c r="K68" s="305"/>
       <c r="L68" s="305"/>
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A69" s="402"/>
-      <c r="B69" s="402"/>
-      <c r="C69" s="432"/>
-      <c r="E69" s="398"/>
-      <c r="F69" s="398"/>
-      <c r="G69" s="398"/>
-      <c r="H69" s="398"/>
-      <c r="I69" s="398"/>
-      <c r="J69" s="427"/>
+      <c r="A69" s="399"/>
+      <c r="B69" s="399"/>
+      <c r="C69" s="429"/>
+      <c r="E69" s="395"/>
+      <c r="F69" s="395"/>
+      <c r="G69" s="395"/>
+      <c r="H69" s="395"/>
+      <c r="I69" s="395"/>
+      <c r="J69" s="424"/>
       <c r="K69" s="305"/>
       <c r="L69" s="305"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A70" s="402"/>
-      <c r="B70" s="402"/>
-      <c r="C70" s="432"/>
-      <c r="E70" s="398"/>
-      <c r="F70" s="398"/>
-      <c r="G70" s="398"/>
-      <c r="H70" s="398"/>
-      <c r="I70" s="398"/>
-      <c r="J70" s="427"/>
+      <c r="A70" s="399"/>
+      <c r="B70" s="399"/>
+      <c r="C70" s="429"/>
+      <c r="E70" s="395"/>
+      <c r="F70" s="395"/>
+      <c r="G70" s="395"/>
+      <c r="H70" s="395"/>
+      <c r="I70" s="395"/>
+      <c r="J70" s="424"/>
       <c r="K70" s="305"/>
       <c r="L70" s="305"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A71" s="402"/>
-      <c r="B71" s="402"/>
-      <c r="C71" s="432"/>
-      <c r="E71" s="398"/>
-      <c r="F71" s="398"/>
-      <c r="G71" s="398"/>
-      <c r="H71" s="398"/>
-      <c r="I71" s="398"/>
-      <c r="J71" s="427"/>
+      <c r="A71" s="399"/>
+      <c r="B71" s="399"/>
+      <c r="C71" s="429"/>
+      <c r="E71" s="395"/>
+      <c r="F71" s="395"/>
+      <c r="G71" s="395"/>
+      <c r="H71" s="395"/>
+      <c r="I71" s="395"/>
+      <c r="J71" s="424"/>
       <c r="K71" s="305"/>
       <c r="L71" s="305"/>
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A72" s="402"/>
-      <c r="B72" s="402"/>
-      <c r="C72" s="432"/>
-      <c r="E72" s="398"/>
-      <c r="F72" s="398"/>
-      <c r="G72" s="398"/>
-      <c r="H72" s="398"/>
-      <c r="I72" s="398"/>
-      <c r="J72" s="427"/>
+      <c r="A72" s="399"/>
+      <c r="B72" s="399"/>
+      <c r="C72" s="429"/>
+      <c r="E72" s="395"/>
+      <c r="F72" s="395"/>
+      <c r="G72" s="395"/>
+      <c r="H72" s="395"/>
+      <c r="I72" s="395"/>
+      <c r="J72" s="424"/>
       <c r="K72" s="305"/>
       <c r="L72" s="305"/>
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A73" s="402"/>
-      <c r="B73" s="402"/>
-      <c r="C73" s="432"/>
+      <c r="A73" s="399"/>
+      <c r="B73" s="399"/>
+      <c r="C73" s="429"/>
       <c r="D73" s="303"/>
-      <c r="E73" s="398"/>
-      <c r="F73" s="398"/>
-      <c r="G73" s="398"/>
-      <c r="H73" s="398"/>
-      <c r="I73" s="398"/>
-      <c r="J73" s="427"/>
+      <c r="E73" s="395"/>
+      <c r="F73" s="395"/>
+      <c r="G73" s="395"/>
+      <c r="H73" s="395"/>
+      <c r="I73" s="395"/>
+      <c r="J73" s="424"/>
       <c r="K73" s="305"/>
       <c r="L73" s="305"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A74" s="402"/>
-      <c r="B74" s="402"/>
-      <c r="C74" s="432"/>
-      <c r="D74" s="434"/>
-      <c r="E74" s="447"/>
-      <c r="F74" s="447"/>
-      <c r="G74" s="447"/>
-      <c r="H74" s="447"/>
-      <c r="I74" s="447"/>
-      <c r="J74" s="448"/>
+      <c r="A74" s="399"/>
+      <c r="B74" s="399"/>
+      <c r="C74" s="429"/>
+      <c r="D74" s="431"/>
+      <c r="E74" s="444"/>
+      <c r="F74" s="444"/>
+      <c r="G74" s="444"/>
+      <c r="H74" s="444"/>
+      <c r="I74" s="444"/>
+      <c r="J74" s="445"/>
       <c r="K74" s="305"/>
       <c r="L74" s="305"/>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A75" s="402"/>
-      <c r="B75" s="402"/>
-      <c r="C75" s="432"/>
-      <c r="D75" s="434"/>
-      <c r="E75" s="435"/>
-      <c r="F75" s="435"/>
-      <c r="G75" s="435"/>
-      <c r="H75" s="435"/>
-      <c r="I75" s="435"/>
-      <c r="J75" s="436"/>
+      <c r="A75" s="399"/>
+      <c r="B75" s="399"/>
+      <c r="C75" s="429"/>
+      <c r="D75" s="431"/>
+      <c r="E75" s="432"/>
+      <c r="F75" s="432"/>
+      <c r="G75" s="432"/>
+      <c r="H75" s="432"/>
+      <c r="I75" s="432"/>
+      <c r="J75" s="433"/>
       <c r="K75" s="305"/>
       <c r="L75" s="305"/>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A76" s="402"/>
-      <c r="B76" s="402"/>
-      <c r="C76" s="446"/>
-      <c r="D76" s="438"/>
-      <c r="E76" s="435"/>
-      <c r="F76" s="435"/>
-      <c r="G76" s="435"/>
-      <c r="H76" s="435"/>
-      <c r="I76" s="435"/>
-      <c r="J76" s="436"/>
+      <c r="A76" s="399"/>
+      <c r="B76" s="399"/>
+      <c r="C76" s="443"/>
+      <c r="D76" s="435"/>
+      <c r="E76" s="432"/>
+      <c r="F76" s="432"/>
+      <c r="G76" s="432"/>
+      <c r="H76" s="432"/>
+      <c r="I76" s="432"/>
+      <c r="J76" s="433"/>
       <c r="K76" s="305"/>
       <c r="L76" s="305"/>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A77" s="402"/>
-      <c r="B77" s="402"/>
-      <c r="C77" s="433">
+      <c r="A77" s="399"/>
+      <c r="B77" s="399"/>
+      <c r="C77" s="430">
         <v>9</v>
       </c>
-      <c r="D77" s="421" t="s">
-        <v>749</v>
-      </c>
-      <c r="E77" s="422"/>
-      <c r="F77" s="422"/>
-      <c r="G77" s="422"/>
-      <c r="H77" s="422"/>
-      <c r="I77" s="422"/>
-      <c r="J77" s="423"/>
+      <c r="D77" s="418" t="s">
+        <v>748</v>
+      </c>
+      <c r="E77" s="419"/>
+      <c r="F77" s="419"/>
+      <c r="G77" s="419"/>
+      <c r="H77" s="419"/>
+      <c r="I77" s="419"/>
+      <c r="J77" s="420"/>
       <c r="K77" s="305"/>
       <c r="L77" s="305"/>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A78" s="402"/>
-      <c r="B78" s="402"/>
-      <c r="C78" s="432"/>
-      <c r="E78" s="398"/>
-      <c r="F78" s="398"/>
-      <c r="G78" s="398"/>
-      <c r="H78" s="398"/>
-      <c r="I78" s="398"/>
-      <c r="J78" s="427"/>
+      <c r="A78" s="399"/>
+      <c r="B78" s="399"/>
+      <c r="C78" s="429"/>
+      <c r="E78" s="395"/>
+      <c r="F78" s="395"/>
+      <c r="G78" s="395"/>
+      <c r="H78" s="395"/>
+      <c r="I78" s="395"/>
+      <c r="J78" s="424"/>
       <c r="K78" s="305"/>
       <c r="L78" s="305"/>
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A79" s="402"/>
-      <c r="B79" s="402"/>
-      <c r="C79" s="432"/>
+      <c r="A79" s="399"/>
+      <c r="B79" s="399"/>
+      <c r="C79" s="429"/>
       <c r="D79" s="304"/>
-      <c r="E79" s="398"/>
-      <c r="F79" s="398"/>
-      <c r="G79" s="398"/>
-      <c r="H79" s="398"/>
-      <c r="I79" s="398"/>
-      <c r="J79" s="427"/>
+      <c r="E79" s="395"/>
+      <c r="F79" s="395"/>
+      <c r="G79" s="395"/>
+      <c r="H79" s="395"/>
+      <c r="I79" s="395"/>
+      <c r="J79" s="424"/>
       <c r="K79" s="305"/>
       <c r="L79" s="305"/>
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A80" s="402"/>
-      <c r="B80" s="402"/>
-      <c r="C80" s="432"/>
-      <c r="E80" s="398"/>
-      <c r="F80" s="398"/>
-      <c r="G80" s="398"/>
-      <c r="H80" s="398"/>
-      <c r="I80" s="398"/>
-      <c r="J80" s="427"/>
+      <c r="A80" s="399"/>
+      <c r="B80" s="399"/>
+      <c r="C80" s="429"/>
+      <c r="E80" s="395"/>
+      <c r="F80" s="395"/>
+      <c r="G80" s="395"/>
+      <c r="H80" s="395"/>
+      <c r="I80" s="395"/>
+      <c r="J80" s="424"/>
       <c r="K80" s="305"/>
       <c r="L80" s="305"/>
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A81" s="402"/>
-      <c r="B81" s="402"/>
-      <c r="C81" s="432"/>
-      <c r="E81" s="398"/>
-      <c r="F81" s="398"/>
-      <c r="G81" s="398"/>
-      <c r="H81" s="398"/>
-      <c r="I81" s="398"/>
-      <c r="J81" s="427"/>
+      <c r="A81" s="399"/>
+      <c r="B81" s="399"/>
+      <c r="C81" s="429"/>
+      <c r="E81" s="395"/>
+      <c r="F81" s="395"/>
+      <c r="G81" s="395"/>
+      <c r="H81" s="395"/>
+      <c r="I81" s="395"/>
+      <c r="J81" s="424"/>
       <c r="K81" s="305"/>
       <c r="L81" s="305"/>
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A82" s="402"/>
-      <c r="B82" s="402"/>
-      <c r="C82" s="432"/>
-      <c r="E82" s="398"/>
-      <c r="F82" s="398"/>
-      <c r="G82" s="398"/>
-      <c r="H82" s="398"/>
-      <c r="I82" s="398"/>
-      <c r="J82" s="427"/>
+      <c r="A82" s="399"/>
+      <c r="B82" s="399"/>
+      <c r="C82" s="429"/>
+      <c r="E82" s="395"/>
+      <c r="F82" s="395"/>
+      <c r="G82" s="395"/>
+      <c r="H82" s="395"/>
+      <c r="I82" s="395"/>
+      <c r="J82" s="424"/>
       <c r="K82" s="305"/>
       <c r="L82" s="305"/>
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A83" s="402"/>
-      <c r="B83" s="402"/>
-      <c r="C83" s="432"/>
-      <c r="E83" s="398"/>
-      <c r="F83" s="398"/>
-      <c r="G83" s="398"/>
-      <c r="H83" s="398"/>
-      <c r="I83" s="398"/>
-      <c r="J83" s="427"/>
+      <c r="A83" s="399"/>
+      <c r="B83" s="399"/>
+      <c r="C83" s="429"/>
+      <c r="E83" s="395"/>
+      <c r="F83" s="395"/>
+      <c r="G83" s="395"/>
+      <c r="H83" s="395"/>
+      <c r="I83" s="395"/>
+      <c r="J83" s="424"/>
       <c r="K83" s="305"/>
       <c r="L83" s="305"/>
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A84" s="402"/>
-      <c r="B84" s="402"/>
-      <c r="C84" s="432"/>
-      <c r="E84" s="398"/>
-      <c r="F84" s="398"/>
-      <c r="G84" s="398"/>
-      <c r="H84" s="398"/>
-      <c r="I84" s="398"/>
-      <c r="J84" s="427"/>
+      <c r="A84" s="399"/>
+      <c r="B84" s="399"/>
+      <c r="C84" s="429"/>
+      <c r="E84" s="395"/>
+      <c r="F84" s="395"/>
+      <c r="G84" s="395"/>
+      <c r="H84" s="395"/>
+      <c r="I84" s="395"/>
+      <c r="J84" s="424"/>
       <c r="K84" s="305"/>
       <c r="L84" s="305"/>
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A85" s="402"/>
-      <c r="B85" s="402"/>
-      <c r="C85" s="432"/>
-      <c r="E85" s="398"/>
-      <c r="F85" s="398"/>
-      <c r="G85" s="398"/>
-      <c r="H85" s="398"/>
-      <c r="I85" s="398"/>
-      <c r="J85" s="427"/>
+      <c r="A85" s="399"/>
+      <c r="B85" s="399"/>
+      <c r="C85" s="429"/>
+      <c r="E85" s="395"/>
+      <c r="F85" s="395"/>
+      <c r="G85" s="395"/>
+      <c r="H85" s="395"/>
+      <c r="I85" s="395"/>
+      <c r="J85" s="424"/>
       <c r="K85" s="305"/>
       <c r="L85" s="305"/>
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A86" s="402"/>
-      <c r="B86" s="402"/>
-      <c r="C86" s="432"/>
-      <c r="E86" s="398"/>
-      <c r="F86" s="398"/>
-      <c r="G86" s="398"/>
-      <c r="H86" s="398"/>
-      <c r="I86" s="398"/>
-      <c r="J86" s="427"/>
+      <c r="A86" s="399"/>
+      <c r="B86" s="399"/>
+      <c r="C86" s="429"/>
+      <c r="E86" s="395"/>
+      <c r="F86" s="395"/>
+      <c r="G86" s="395"/>
+      <c r="H86" s="395"/>
+      <c r="I86" s="395"/>
+      <c r="J86" s="424"/>
       <c r="K86" s="305"/>
       <c r="L86" s="305"/>
     </row>
     <row r="87" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A87" s="402"/>
-      <c r="B87" s="402"/>
-      <c r="C87" s="432"/>
+      <c r="A87" s="399"/>
+      <c r="B87" s="399"/>
+      <c r="C87" s="429"/>
       <c r="D87" s="303"/>
-      <c r="E87" s="398"/>
-      <c r="F87" s="398"/>
-      <c r="G87" s="398"/>
-      <c r="H87" s="398"/>
-      <c r="I87" s="398"/>
-      <c r="J87" s="427"/>
+      <c r="E87" s="395"/>
+      <c r="F87" s="395"/>
+      <c r="G87" s="395"/>
+      <c r="H87" s="395"/>
+      <c r="I87" s="395"/>
+      <c r="J87" s="424"/>
       <c r="K87" s="305"/>
       <c r="L87" s="305"/>
     </row>
     <row r="88" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A88" s="402"/>
-      <c r="B88" s="402"/>
-      <c r="C88" s="432"/>
-      <c r="D88" s="434"/>
-      <c r="E88" s="447"/>
-      <c r="F88" s="447"/>
-      <c r="G88" s="447"/>
-      <c r="H88" s="447"/>
-      <c r="I88" s="447"/>
-      <c r="J88" s="448"/>
+      <c r="A88" s="399"/>
+      <c r="B88" s="399"/>
+      <c r="C88" s="429"/>
+      <c r="D88" s="431"/>
+      <c r="E88" s="444"/>
+      <c r="F88" s="444"/>
+      <c r="G88" s="444"/>
+      <c r="H88" s="444"/>
+      <c r="I88" s="444"/>
+      <c r="J88" s="445"/>
       <c r="K88" s="305"/>
       <c r="L88" s="305"/>
     </row>
     <row r="89" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A89" s="402"/>
-      <c r="B89" s="402"/>
-      <c r="C89" s="432"/>
-      <c r="D89" s="434"/>
-      <c r="E89" s="435"/>
-      <c r="F89" s="435"/>
-      <c r="G89" s="435"/>
-      <c r="H89" s="435"/>
-      <c r="I89" s="435"/>
-      <c r="J89" s="436"/>
+      <c r="A89" s="399"/>
+      <c r="B89" s="399"/>
+      <c r="C89" s="429"/>
+      <c r="D89" s="431"/>
+      <c r="E89" s="432"/>
+      <c r="F89" s="432"/>
+      <c r="G89" s="432"/>
+      <c r="H89" s="432"/>
+      <c r="I89" s="432"/>
+      <c r="J89" s="433"/>
       <c r="K89" s="305"/>
       <c r="L89" s="305"/>
     </row>
     <row r="90" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A90" s="402"/>
-      <c r="B90" s="402"/>
-      <c r="C90" s="446"/>
-      <c r="D90" s="438"/>
-      <c r="E90" s="435"/>
-      <c r="F90" s="435"/>
-      <c r="G90" s="435"/>
-      <c r="H90" s="435"/>
-      <c r="I90" s="435"/>
-      <c r="J90" s="436"/>
+      <c r="A90" s="399"/>
+      <c r="B90" s="399"/>
+      <c r="C90" s="443"/>
+      <c r="D90" s="435"/>
+      <c r="E90" s="432"/>
+      <c r="F90" s="432"/>
+      <c r="G90" s="432"/>
+      <c r="H90" s="432"/>
+      <c r="I90" s="432"/>
+      <c r="J90" s="433"/>
       <c r="K90" s="305"/>
       <c r="L90" s="305"/>
     </row>
     <row r="91" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A91" s="402"/>
-      <c r="B91" s="402"/>
-      <c r="C91" s="449"/>
+      <c r="A91" s="399"/>
+      <c r="B91" s="399"/>
+      <c r="C91" s="446"/>
       <c r="D91" s="305"/>
       <c r="E91" s="305"/>
       <c r="F91" s="305"/>
@@ -10256,11 +10329,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="458" t="s">
+      <c r="C4" s="450" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="459"/>
-      <c r="E4" s="459"/>
+      <c r="D4" s="451"/>
+      <c r="E4" s="451"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10269,13 +10342,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="462" t="s">
+      <c r="C5" s="456" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="460" t="s">
+      <c r="D5" s="452" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="461"/>
+      <c r="E5" s="453"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10284,11 +10357,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="455"/>
-      <c r="D6" s="450" t="s">
+      <c r="C6" s="449"/>
+      <c r="D6" s="454" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="451"/>
+      <c r="E6" s="455"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10297,11 +10370,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="455"/>
-      <c r="D7" s="450" t="s">
+      <c r="C7" s="449"/>
+      <c r="D7" s="454" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="451"/>
+      <c r="E7" s="455"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10310,11 +10383,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="455"/>
-      <c r="D8" s="450" t="s">
+      <c r="C8" s="449"/>
+      <c r="D8" s="454" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="451"/>
+      <c r="E8" s="455"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10323,11 +10396,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="455"/>
-      <c r="D9" s="450" t="s">
+      <c r="C9" s="449"/>
+      <c r="D9" s="454" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="451"/>
+      <c r="E9" s="455"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10336,11 +10409,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="456"/>
-      <c r="D10" s="450" t="s">
+      <c r="C10" s="448"/>
+      <c r="D10" s="454" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="451"/>
+      <c r="E10" s="455"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10349,13 +10422,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="463" t="s">
+      <c r="C11" s="447" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="450" t="s">
+      <c r="D11" s="454" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="451"/>
+      <c r="E11" s="455"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10364,11 +10437,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="456"/>
-      <c r="D12" s="450" t="s">
+      <c r="C12" s="448"/>
+      <c r="D12" s="454" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="451"/>
+      <c r="E12" s="455"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10377,13 +10450,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="463" t="s">
+      <c r="C13" s="447" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="450" t="s">
+      <c r="D13" s="454" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="451"/>
+      <c r="E13" s="455"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10392,11 +10465,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="455"/>
-      <c r="D14" s="450" t="s">
+      <c r="C14" s="449"/>
+      <c r="D14" s="454" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="451"/>
+      <c r="E14" s="455"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10405,11 +10478,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="456"/>
-      <c r="D15" s="450" t="s">
+      <c r="C15" s="448"/>
+      <c r="D15" s="454" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="451"/>
+      <c r="E15" s="455"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -10418,13 +10491,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="463" t="s">
+      <c r="C16" s="447" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="452" t="s">
+      <c r="D16" s="459" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="453"/>
+      <c r="E16" s="460"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -10433,8 +10506,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="455"/>
-      <c r="D17" s="454" t="s">
+      <c r="C17" s="449"/>
+      <c r="D17" s="458" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -10448,8 +10521,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="455"/>
-      <c r="D18" s="455"/>
+      <c r="C18" s="449"/>
+      <c r="D18" s="449"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -10461,8 +10534,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="455"/>
-      <c r="D19" s="455"/>
+      <c r="C19" s="449"/>
+      <c r="D19" s="449"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -10474,8 +10547,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="455"/>
-      <c r="D20" s="455"/>
+      <c r="C20" s="449"/>
+      <c r="D20" s="449"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -10487,8 +10560,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="455"/>
-      <c r="D21" s="456"/>
+      <c r="C21" s="449"/>
+      <c r="D21" s="448"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -10500,7 +10573,7 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="455"/>
+      <c r="C22" s="449"/>
       <c r="D22" s="457" t="s">
         <v>165</v>
       </c>
@@ -10515,8 +10588,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="455"/>
-      <c r="D23" s="455"/>
+      <c r="C23" s="449"/>
+      <c r="D23" s="449"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -10528,8 +10601,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="455"/>
-      <c r="D24" s="455"/>
+      <c r="C24" s="449"/>
+      <c r="D24" s="449"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -10541,8 +10614,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="455"/>
-      <c r="D25" s="455"/>
+      <c r="C25" s="449"/>
+      <c r="D25" s="449"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -10554,8 +10627,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="455"/>
-      <c r="D26" s="456"/>
+      <c r="C26" s="449"/>
+      <c r="D26" s="448"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -10567,7 +10640,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="455"/>
+      <c r="C27" s="449"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -10582,7 +10655,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="455"/>
+      <c r="C28" s="449"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -10597,8 +10670,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="455"/>
-      <c r="D29" s="454" t="s">
+      <c r="C29" s="449"/>
+      <c r="D29" s="458" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -10612,8 +10685,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="455"/>
-      <c r="D30" s="455"/>
+      <c r="C30" s="449"/>
+      <c r="D30" s="449"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -10625,8 +10698,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="456"/>
-      <c r="D31" s="456"/>
+      <c r="C31" s="448"/>
+      <c r="D31" s="448"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -10638,13 +10711,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="463" t="s">
+      <c r="C32" s="447" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="450" t="s">
+      <c r="D32" s="454" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="451"/>
+      <c r="E32" s="455"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -10652,11 +10725,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="455"/>
-      <c r="D33" s="450" t="s">
+      <c r="C33" s="449"/>
+      <c r="D33" s="454" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="451"/>
+      <c r="E33" s="455"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -10665,11 +10738,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="456"/>
-      <c r="D34" s="450" t="s">
+      <c r="C34" s="448"/>
+      <c r="D34" s="454" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="451"/>
+      <c r="E34" s="455"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -10686,6 +10759,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -10702,14 +10783,6 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -11715,16 +11788,16 @@
         <v>462</v>
       </c>
       <c r="E57" s="243" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F57" s="244" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G57" s="245" t="s">
+        <v>470</v>
+      </c>
+      <c r="H57" s="247" t="s">
         <v>471</v>
-      </c>
-      <c r="H57" s="247" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="52">
@@ -11734,13 +11807,13 @@
       <c r="D58" s="248"/>
       <c r="E58" s="249"/>
       <c r="F58" s="244" t="s">
+        <v>476</v>
+      </c>
+      <c r="G58" s="245" t="s">
         <v>477</v>
       </c>
-      <c r="G58" s="245" t="s">
+      <c r="H58" s="247" t="s">
         <v>478</v>
-      </c>
-      <c r="H58" s="247" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="26">
@@ -11750,13 +11823,13 @@
       <c r="D59" s="248"/>
       <c r="E59" s="249"/>
       <c r="F59" s="244" t="s">
+        <v>480</v>
+      </c>
+      <c r="G59" s="245" t="s">
         <v>481</v>
       </c>
-      <c r="G59" s="245" t="s">
-        <v>482</v>
-      </c>
       <c r="H59" s="247" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="52">
@@ -11766,13 +11839,13 @@
       <c r="D60" s="251"/>
       <c r="E60" s="252"/>
       <c r="F60" s="244" t="s">
+        <v>492</v>
+      </c>
+      <c r="G60" s="245" t="s">
         <v>493</v>
       </c>
-      <c r="G60" s="245" t="s">
+      <c r="H60" s="247" t="s">
         <v>494</v>
-      </c>
-      <c r="H60" s="247" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="78">
@@ -11782,19 +11855,19 @@
         <v>17</v>
       </c>
       <c r="D61" s="241" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E61" s="243" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F61" s="244" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G61" s="245" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H61" s="231" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="39">
@@ -11804,13 +11877,13 @@
       <c r="D62" s="248"/>
       <c r="E62" s="249"/>
       <c r="F62" s="244" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G62" s="245" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H62" s="231" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="26">
@@ -11820,13 +11893,13 @@
       <c r="D63" s="248"/>
       <c r="E63" s="249"/>
       <c r="F63" s="244" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G63" s="245" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H63" s="231" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="195">
@@ -11836,13 +11909,13 @@
       <c r="D64" s="248"/>
       <c r="E64" s="249"/>
       <c r="F64" s="244" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G64" s="245" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H64" s="231" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="78">
@@ -11852,13 +11925,13 @@
       <c r="D65" s="248"/>
       <c r="E65" s="249"/>
       <c r="F65" s="244" t="s">
+        <v>532</v>
+      </c>
+      <c r="G65" s="245" t="s">
         <v>533</v>
       </c>
-      <c r="G65" s="245" t="s">
+      <c r="H65" s="231" t="s">
         <v>534</v>
-      </c>
-      <c r="H65" s="231" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="39">
@@ -11868,13 +11941,13 @@
       <c r="D66" s="248"/>
       <c r="E66" s="249"/>
       <c r="F66" s="244" t="s">
+        <v>537</v>
+      </c>
+      <c r="G66" s="245" t="s">
         <v>538</v>
       </c>
-      <c r="G66" s="245" t="s">
+      <c r="H66" s="231" t="s">
         <v>539</v>
-      </c>
-      <c r="H66" s="231" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="26">
@@ -11884,13 +11957,13 @@
       <c r="D67" s="248"/>
       <c r="E67" s="249"/>
       <c r="F67" s="244" t="s">
+        <v>542</v>
+      </c>
+      <c r="G67" s="245" t="s">
         <v>543</v>
       </c>
-      <c r="G67" s="245" t="s">
-        <v>544</v>
-      </c>
       <c r="H67" s="231" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="26">
@@ -11900,13 +11973,13 @@
       <c r="D68" s="248"/>
       <c r="E68" s="249"/>
       <c r="F68" s="244" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G68" s="245" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H68" s="231" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="26">
@@ -11916,13 +11989,13 @@
       <c r="D69" s="248"/>
       <c r="E69" s="249"/>
       <c r="F69" s="244" t="s">
+        <v>556</v>
+      </c>
+      <c r="G69" s="245" t="s">
         <v>557</v>
       </c>
-      <c r="G69" s="245" t="s">
-        <v>558</v>
-      </c>
       <c r="H69" s="231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="26">
@@ -11932,13 +12005,13 @@
       <c r="D70" s="248"/>
       <c r="E70" s="249"/>
       <c r="F70" s="244" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G70" s="245" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H70" s="231" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="39">
@@ -11948,13 +12021,13 @@
       <c r="D71" s="248"/>
       <c r="E71" s="249"/>
       <c r="F71" s="244" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G71" s="245" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H71" s="231" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="26">
@@ -11964,13 +12037,13 @@
       <c r="D72" s="251"/>
       <c r="E72" s="252"/>
       <c r="F72" s="244" t="s">
+        <v>577</v>
+      </c>
+      <c r="G72" s="245" t="s">
         <v>578</v>
       </c>
-      <c r="G72" s="245" t="s">
-        <v>579</v>
-      </c>
       <c r="H72" s="231" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -13209,7 +13282,7 @@
         <v>423</v>
       </c>
       <c r="F12" s="220" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G12" s="221" t="s">
         <v>426</v>
@@ -13219,13 +13292,13 @@
       <c r="C13" s="228"/>
       <c r="D13" s="224"/>
       <c r="E13" s="239" t="s">
+        <v>467</v>
+      </c>
+      <c r="F13" s="220" t="s">
         <v>468</v>
       </c>
-      <c r="F13" s="220" t="s">
+      <c r="G13" s="221" t="s">
         <v>469</v>
-      </c>
-      <c r="G13" s="221" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
@@ -13252,7 +13325,7 @@
         <v>423</v>
       </c>
       <c r="F15" s="220" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G15" s="221" t="s">
         <v>426</v>
@@ -13262,13 +13335,13 @@
       <c r="C16" s="228"/>
       <c r="D16" s="250"/>
       <c r="E16" s="239" t="s">
+        <v>467</v>
+      </c>
+      <c r="F16" s="220" t="s">
         <v>468</v>
       </c>
-      <c r="F16" s="220" t="s">
+      <c r="G16" s="221" t="s">
         <v>469</v>
-      </c>
-      <c r="G16" s="221" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="17" spans="3:7" ht="15" customHeight="1">
@@ -13276,16 +13349,16 @@
         <v>4</v>
       </c>
       <c r="D17" s="224" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E17" s="239" t="s">
+        <v>489</v>
+      </c>
+      <c r="F17" s="220" t="s">
         <v>490</v>
       </c>
-      <c r="F17" s="220" t="s">
+      <c r="G17" s="221" t="s">
         <v>491</v>
-      </c>
-      <c r="G17" s="221" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="18" spans="3:7" ht="15" customHeight="1">
@@ -13296,52 +13369,52 @@
         <v>234</v>
       </c>
       <c r="E18" s="239" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F18" s="220" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G18" s="221" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="19" spans="3:7" ht="15" customHeight="1">
       <c r="C19" s="222"/>
       <c r="D19" s="224"/>
       <c r="E19" s="239" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F19" s="220" t="s">
+        <v>505</v>
+      </c>
+      <c r="G19" s="221" t="s">
         <v>506</v>
-      </c>
-      <c r="G19" s="221" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="20" spans="3:7" ht="15" customHeight="1">
       <c r="C20" s="222"/>
       <c r="D20" s="224"/>
       <c r="E20" s="239" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F20" s="220" t="s">
+        <v>511</v>
+      </c>
+      <c r="G20" s="221" t="s">
         <v>512</v>
-      </c>
-      <c r="G20" s="221" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="21" spans="3:7" ht="15" customHeight="1">
       <c r="C21" s="228"/>
       <c r="D21" s="224"/>
       <c r="E21" s="239" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F21" s="220" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G21" s="221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="22" spans="3:7" ht="15" customHeight="1">
@@ -13352,39 +13425,39 @@
         <v>247</v>
       </c>
       <c r="E22" s="239" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F22" s="220" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G22" s="221" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="3:7" ht="15" customHeight="1">
       <c r="C23" s="222"/>
       <c r="D23" s="224"/>
       <c r="E23" s="239" t="s">
+        <v>528</v>
+      </c>
+      <c r="F23" s="220" t="s">
         <v>529</v>
       </c>
-      <c r="F23" s="220" t="s">
-        <v>530</v>
-      </c>
       <c r="G23" s="221" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="24" spans="3:7" ht="15" customHeight="1">
       <c r="C24" s="228"/>
       <c r="D24" s="250"/>
       <c r="E24" s="254" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F24" s="220" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G24" s="221" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="25" spans="3:7" ht="15" customHeight="1">
@@ -13395,65 +13468,65 @@
         <v>254</v>
       </c>
       <c r="E25" s="239" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F25" s="220" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G25" s="221" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" spans="3:7" ht="15" customHeight="1">
       <c r="C26" s="222"/>
       <c r="D26" s="224"/>
       <c r="E26" s="239" t="s">
+        <v>552</v>
+      </c>
+      <c r="F26" s="220" t="s">
         <v>553</v>
       </c>
-      <c r="F26" s="220" t="s">
-        <v>554</v>
-      </c>
       <c r="G26" s="221" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="27" spans="3:7" ht="15" customHeight="1">
       <c r="C27" s="222"/>
       <c r="D27" s="224"/>
       <c r="E27" s="254" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F27" s="220" t="s">
+        <v>560</v>
+      </c>
+      <c r="G27" s="221" t="s">
         <v>561</v>
-      </c>
-      <c r="G27" s="221" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="28" spans="3:7" ht="15" customHeight="1">
       <c r="C28" s="222"/>
       <c r="D28" s="224"/>
       <c r="E28" s="239" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F28" s="220" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G28" s="221" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="29" spans="3:7" ht="15" customHeight="1">
       <c r="C29" s="228"/>
       <c r="D29" s="250"/>
       <c r="E29" s="254" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F29" s="220" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G29" s="221" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="30" spans="3:7" ht="15" customHeight="1">
@@ -13464,26 +13537,26 @@
         <v>262</v>
       </c>
       <c r="E30" s="239" t="s">
+        <v>574</v>
+      </c>
+      <c r="F30" s="220" t="s">
         <v>575</v>
       </c>
-      <c r="F30" s="220" t="s">
+      <c r="G30" s="221" t="s">
         <v>576</v>
-      </c>
-      <c r="G30" s="221" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="31" spans="3:7" ht="15" customHeight="1">
       <c r="C31" s="228"/>
       <c r="D31" s="250"/>
       <c r="E31" s="254" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F31" s="220" t="s">
+        <v>581</v>
+      </c>
+      <c r="G31" s="221" t="s">
         <v>582</v>
-      </c>
-      <c r="G31" s="221" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="32" spans="3:7" ht="15" customHeight="1">
@@ -13491,68 +13564,68 @@
         <v>9</v>
       </c>
       <c r="D32" s="224" t="s">
+        <v>583</v>
+      </c>
+      <c r="E32" s="239" t="s">
         <v>584</v>
       </c>
-      <c r="E32" s="239" t="s">
+      <c r="F32" s="220" t="s">
         <v>585</v>
       </c>
-      <c r="F32" s="220" t="s">
+      <c r="G32" s="221" t="s">
         <v>586</v>
-      </c>
-      <c r="G32" s="221" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="33" spans="3:7" ht="15" customHeight="1">
       <c r="C33" s="222"/>
       <c r="D33" s="224"/>
       <c r="E33" s="239" t="s">
+        <v>587</v>
+      </c>
+      <c r="F33" s="220" t="s">
         <v>588</v>
       </c>
-      <c r="F33" s="220" t="s">
+      <c r="G33" s="221" t="s">
         <v>589</v>
-      </c>
-      <c r="G33" s="221" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="34" spans="3:7" ht="15" customHeight="1">
       <c r="C34" s="222"/>
       <c r="D34" s="224"/>
       <c r="E34" s="239" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F34" s="220" t="s">
+        <v>592</v>
+      </c>
+      <c r="G34" s="221" t="s">
         <v>593</v>
-      </c>
-      <c r="G34" s="221" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="35" spans="3:7" ht="15" customHeight="1">
       <c r="C35" s="222"/>
       <c r="D35" s="224"/>
       <c r="E35" s="239" t="s">
+        <v>594</v>
+      </c>
+      <c r="F35" s="220" t="s">
         <v>595</v>
       </c>
-      <c r="F35" s="220" t="s">
+      <c r="G35" s="221" t="s">
         <v>596</v>
-      </c>
-      <c r="G35" s="221" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="36" spans="3:7" ht="15" customHeight="1">
       <c r="C36" s="228"/>
       <c r="D36" s="224"/>
       <c r="E36" s="239" t="s">
+        <v>597</v>
+      </c>
+      <c r="F36" s="220" t="s">
         <v>598</v>
       </c>
-      <c r="F36" s="220" t="s">
+      <c r="G36" s="221" t="s">
         <v>599</v>
-      </c>
-      <c r="G36" s="221" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="37" spans="3:7" ht="15" customHeight="1">
@@ -13560,55 +13633,55 @@
         <v>10</v>
       </c>
       <c r="D37" s="255" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E37" s="239" t="s">
+        <v>603</v>
+      </c>
+      <c r="F37" s="220" t="s">
         <v>604</v>
       </c>
-      <c r="F37" s="220" t="s">
+      <c r="G37" s="221" t="s">
         <v>605</v>
-      </c>
-      <c r="G37" s="221" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="38" spans="3:7" ht="15" customHeight="1">
       <c r="C38" s="222"/>
       <c r="D38" s="224"/>
       <c r="E38" s="239" t="s">
+        <v>606</v>
+      </c>
+      <c r="F38" s="220" t="s">
         <v>607</v>
       </c>
-      <c r="F38" s="220" t="s">
+      <c r="G38" s="221" t="s">
         <v>608</v>
-      </c>
-      <c r="G38" s="221" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="39" spans="3:7" ht="15" customHeight="1">
       <c r="C39" s="222"/>
       <c r="D39" s="224"/>
       <c r="E39" s="239" t="s">
+        <v>609</v>
+      </c>
+      <c r="F39" s="220" t="s">
         <v>610</v>
       </c>
-      <c r="F39" s="220" t="s">
-        <v>611</v>
-      </c>
       <c r="G39" s="221" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="40" spans="3:7" ht="15" customHeight="1">
       <c r="C40" s="256"/>
       <c r="D40" s="250"/>
       <c r="E40" s="239" t="s">
+        <v>611</v>
+      </c>
+      <c r="F40" s="220" t="s">
         <v>612</v>
       </c>
-      <c r="F40" s="220" t="s">
-        <v>613</v>
-      </c>
       <c r="G40" s="221" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="41" spans="3:7" ht="15" customHeight="1">
@@ -13616,107 +13689,107 @@
         <v>11</v>
       </c>
       <c r="D41" s="255" t="s">
+        <v>613</v>
+      </c>
+      <c r="E41" s="239" t="s">
         <v>614</v>
       </c>
-      <c r="E41" s="239" t="s">
+      <c r="F41" s="220" t="s">
         <v>615</v>
       </c>
-      <c r="F41" s="220" t="s">
+      <c r="G41" s="221" t="s">
         <v>616</v>
-      </c>
-      <c r="G41" s="221" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="42" spans="3:7" ht="15" customHeight="1">
       <c r="C42" s="222"/>
       <c r="D42" s="224"/>
       <c r="E42" s="239" t="s">
+        <v>617</v>
+      </c>
+      <c r="F42" s="220" t="s">
         <v>618</v>
       </c>
-      <c r="F42" s="220" t="s">
+      <c r="G42" s="221" t="s">
         <v>619</v>
-      </c>
-      <c r="G42" s="221" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="43" spans="3:7" ht="15" customHeight="1">
       <c r="C43" s="222"/>
       <c r="D43" s="224"/>
       <c r="E43" s="239" t="s">
+        <v>620</v>
+      </c>
+      <c r="F43" s="220" t="s">
         <v>621</v>
       </c>
-      <c r="F43" s="220" t="s">
+      <c r="G43" s="221" t="s">
         <v>622</v>
-      </c>
-      <c r="G43" s="221" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="44" spans="3:7" ht="15" customHeight="1">
       <c r="C44" s="222"/>
       <c r="D44" s="224"/>
       <c r="E44" s="239" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F44" s="220" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G44" s="221" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="45" spans="3:7" ht="15" customHeight="1">
       <c r="C45" s="222"/>
       <c r="D45" s="224"/>
       <c r="E45" s="239" t="s">
+        <v>630</v>
+      </c>
+      <c r="F45" s="220" t="s">
         <v>631</v>
       </c>
-      <c r="F45" s="220" t="s">
+      <c r="G45" s="221" t="s">
         <v>632</v>
-      </c>
-      <c r="G45" s="221" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="46" spans="3:7" ht="15" customHeight="1">
       <c r="C46" s="222"/>
       <c r="D46" s="224"/>
       <c r="E46" s="239" t="s">
+        <v>633</v>
+      </c>
+      <c r="F46" s="220" t="s">
         <v>634</v>
       </c>
-      <c r="F46" s="220" t="s">
+      <c r="G46" s="221" t="s">
         <v>635</v>
-      </c>
-      <c r="G46" s="221" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="47" spans="3:7" ht="15" customHeight="1">
       <c r="C47" s="222"/>
       <c r="D47" s="224"/>
       <c r="E47" s="239" t="s">
+        <v>636</v>
+      </c>
+      <c r="F47" s="220" t="s">
         <v>637</v>
       </c>
-      <c r="F47" s="220" t="s">
+      <c r="G47" s="221" t="s">
         <v>638</v>
-      </c>
-      <c r="G47" s="221" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="48" spans="3:7" ht="15" customHeight="1">
       <c r="C48" s="228"/>
       <c r="D48" s="250"/>
       <c r="E48" s="239" t="s">
+        <v>639</v>
+      </c>
+      <c r="F48" s="220" t="s">
         <v>640</v>
       </c>
-      <c r="F48" s="220" t="s">
+      <c r="G48" s="221" t="s">
         <v>641</v>
-      </c>
-      <c r="G48" s="221" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="49" spans="3:7" ht="15" customHeight="1">
@@ -13724,55 +13797,55 @@
         <v>12</v>
       </c>
       <c r="D49" s="224" t="s">
+        <v>643</v>
+      </c>
+      <c r="E49" s="239" t="s">
         <v>644</v>
       </c>
-      <c r="E49" s="239" t="s">
+      <c r="F49" s="220" t="s">
         <v>645</v>
       </c>
-      <c r="F49" s="220" t="s">
+      <c r="G49" s="221" t="s">
         <v>646</v>
-      </c>
-      <c r="G49" s="221" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="50" spans="3:7" ht="15" customHeight="1">
       <c r="C50" s="222"/>
       <c r="D50" s="224"/>
       <c r="E50" s="239" t="s">
+        <v>647</v>
+      </c>
+      <c r="F50" s="220" t="s">
+        <v>645</v>
+      </c>
+      <c r="G50" s="221" t="s">
         <v>648</v>
-      </c>
-      <c r="F50" s="220" t="s">
-        <v>646</v>
-      </c>
-      <c r="G50" s="221" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="51" spans="3:7" ht="15" customHeight="1">
       <c r="C51" s="222"/>
       <c r="D51" s="224"/>
       <c r="E51" s="239" t="s">
+        <v>649</v>
+      </c>
+      <c r="F51" s="220" t="s">
         <v>650</v>
       </c>
-      <c r="F51" s="220" t="s">
+      <c r="G51" s="221" t="s">
         <v>651</v>
-      </c>
-      <c r="G51" s="221" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="52" spans="3:7" ht="15" customHeight="1">
       <c r="C52" s="228"/>
       <c r="D52" s="224"/>
       <c r="E52" s="239" t="s">
+        <v>652</v>
+      </c>
+      <c r="F52" s="220" t="s">
         <v>653</v>
       </c>
-      <c r="F52" s="220" t="s">
-        <v>654</v>
-      </c>
       <c r="G52" s="221" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="53" spans="3:7" ht="15" customHeight="1">
@@ -13780,68 +13853,68 @@
         <v>13</v>
       </c>
       <c r="D53" s="259" t="s">
+        <v>656</v>
+      </c>
+      <c r="E53" s="260" t="s">
         <v>657</v>
       </c>
-      <c r="E53" s="260" t="s">
-        <v>658</v>
-      </c>
       <c r="F53" s="261" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G53" s="262" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="54" spans="3:7" ht="15" customHeight="1">
       <c r="C54" s="222"/>
       <c r="D54" s="263"/>
       <c r="E54" s="260" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F54" s="261" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G54" s="262" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="55" spans="3:7" ht="15" customHeight="1">
       <c r="C55" s="222"/>
       <c r="D55" s="263"/>
       <c r="E55" s="260" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F55" s="261" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G55" s="262" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="56" spans="3:7" ht="56">
       <c r="C56" s="222"/>
       <c r="D56" s="263"/>
       <c r="E56" s="260" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F56" s="261" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G56" s="262" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="57" spans="3:7" ht="42">
       <c r="C57" s="228"/>
       <c r="D57" s="264"/>
       <c r="E57" s="260" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F57" s="261" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G57" s="262" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="58" spans="3:7" ht="28">
@@ -13849,68 +13922,68 @@
         <v>14</v>
       </c>
       <c r="D58" s="265" t="s">
+        <v>684</v>
+      </c>
+      <c r="E58" s="260" t="s">
         <v>685</v>
       </c>
-      <c r="E58" s="260" t="s">
+      <c r="F58" s="261" t="s">
         <v>686</v>
       </c>
-      <c r="F58" s="261" t="s">
+      <c r="G58" s="262" t="s">
         <v>687</v>
-      </c>
-      <c r="G58" s="262" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="59" spans="3:7" ht="28">
       <c r="C59" s="222"/>
       <c r="D59" s="263"/>
       <c r="E59" s="260" t="s">
+        <v>689</v>
+      </c>
+      <c r="F59" s="261" t="s">
         <v>690</v>
       </c>
-      <c r="F59" s="261" t="s">
+      <c r="G59" s="262" t="s">
         <v>691</v>
-      </c>
-      <c r="G59" s="262" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="60" spans="3:7" ht="42">
       <c r="C60" s="222"/>
       <c r="D60" s="263"/>
       <c r="E60" s="239" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F60" s="220" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G60" s="221" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="61" spans="3:7" ht="42">
       <c r="C61" s="222"/>
       <c r="D61" s="263"/>
       <c r="E61" s="239" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F61" s="220" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G61" s="221" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="62" spans="3:7" ht="42">
       <c r="C62" s="228"/>
       <c r="D62" s="263"/>
       <c r="E62" s="239" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F62" s="220" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G62" s="221" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="63" spans="3:7" ht="28">
@@ -13918,55 +13991,55 @@
         <v>15</v>
       </c>
       <c r="D63" s="268" t="s">
+        <v>695</v>
+      </c>
+      <c r="E63" s="260" t="s">
         <v>696</v>
       </c>
-      <c r="E63" s="260" t="s">
+      <c r="F63" s="220" t="s">
         <v>697</v>
       </c>
-      <c r="F63" s="220" t="s">
+      <c r="G63" s="262" t="s">
         <v>698</v>
-      </c>
-      <c r="G63" s="262" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="64" spans="3:7" ht="28">
       <c r="C64" s="222"/>
       <c r="D64" s="263"/>
       <c r="E64" s="260" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F64" s="220" t="s">
+        <v>702</v>
+      </c>
+      <c r="G64" s="262" t="s">
         <v>703</v>
-      </c>
-      <c r="G64" s="262" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="28">
       <c r="C65" s="222"/>
       <c r="D65" s="263"/>
       <c r="E65" s="239" t="s">
+        <v>704</v>
+      </c>
+      <c r="F65" s="220" t="s">
         <v>705</v>
       </c>
-      <c r="F65" s="220" t="s">
+      <c r="G65" s="221" t="s">
         <v>706</v>
-      </c>
-      <c r="G65" s="221" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="28">
       <c r="C66" s="228"/>
       <c r="D66" s="264"/>
       <c r="E66" s="239" t="s">
+        <v>707</v>
+      </c>
+      <c r="F66" s="220" t="s">
         <v>708</v>
       </c>
-      <c r="F66" s="220" t="s">
+      <c r="G66" s="221" t="s">
         <v>709</v>
-      </c>
-      <c r="G66" s="221" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="13">
@@ -13978,7 +14051,7 @@
     <row r="68" spans="1:8" ht="19">
       <c r="A68" s="45"/>
       <c r="B68" s="273" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C68" s="45"/>
       <c r="D68" s="45"/>
@@ -13991,7 +14064,7 @@
       <c r="A69" s="45"/>
       <c r="B69" s="45"/>
       <c r="C69" s="274" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D69" s="45"/>
       <c r="E69" s="203"/>
@@ -14022,52 +14095,52 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="464">
+      <c r="C71" s="461">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E71" s="281" t="s">
+        <v>737</v>
+      </c>
+      <c r="F71" s="282" t="s">
         <v>738</v>
       </c>
-      <c r="F71" s="282" t="s">
-        <v>739</v>
-      </c>
       <c r="G71" s="281" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H71" s="279"/>
     </row>
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="455"/>
+      <c r="C72" s="449"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
+        <v>742</v>
+      </c>
+      <c r="F72" s="282" t="s">
         <v>743</v>
       </c>
-      <c r="F72" s="282" t="s">
+      <c r="G72" s="281" t="s">
         <v>744</v>
-      </c>
-      <c r="G72" s="281" t="s">
-        <v>745</v>
       </c>
       <c r="H72" s="279"/>
     </row>
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="456"/>
+      <c r="C73" s="448"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
+        <v>745</v>
+      </c>
+      <c r="F73" s="282" t="s">
         <v>746</v>
       </c>
-      <c r="F73" s="282" t="s">
+      <c r="G73" s="281" t="s">
         <v>747</v>
-      </c>
-      <c r="G73" s="281" t="s">
-        <v>748</v>
       </c>
       <c r="H73" s="279"/>
     </row>
@@ -14078,16 +14151,16 @@
         <v>17</v>
       </c>
       <c r="D74" s="280" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E74" s="281" t="s">
+        <v>754</v>
+      </c>
+      <c r="F74" s="282" t="s">
         <v>755</v>
       </c>
-      <c r="F74" s="282" t="s">
+      <c r="G74" s="281" t="s">
         <v>756</v>
-      </c>
-      <c r="G74" s="281" t="s">
-        <v>757</v>
       </c>
       <c r="H74" s="279"/>
     </row>
@@ -14097,13 +14170,13 @@
       <c r="C75" s="286"/>
       <c r="D75" s="283"/>
       <c r="E75" s="281" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F75" s="282" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G75" s="281" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H75" s="279"/>
     </row>
@@ -14113,13 +14186,13 @@
       <c r="C76" s="287"/>
       <c r="D76" s="284"/>
       <c r="E76" s="281" t="s">
+        <v>771</v>
+      </c>
+      <c r="F76" s="282" t="s">
         <v>772</v>
       </c>
-      <c r="F76" s="282" t="s">
+      <c r="G76" s="281" t="s">
         <v>773</v>
-      </c>
-      <c r="G76" s="281" t="s">
-        <v>774</v>
       </c>
       <c r="H76" s="279"/>
     </row>
@@ -14130,16 +14203,16 @@
         <v>18</v>
       </c>
       <c r="D77" s="280" t="s">
+        <v>774</v>
+      </c>
+      <c r="E77" s="281" t="s">
         <v>775</v>
       </c>
-      <c r="E77" s="281" t="s">
-        <v>776</v>
-      </c>
       <c r="F77" s="282" t="s">
+        <v>777</v>
+      </c>
+      <c r="G77" s="281" t="s">
         <v>778</v>
-      </c>
-      <c r="G77" s="281" t="s">
-        <v>779</v>
       </c>
       <c r="H77" s="279"/>
     </row>
@@ -14149,13 +14222,13 @@
       <c r="C78" s="286"/>
       <c r="D78" s="283"/>
       <c r="E78" s="281" t="s">
+        <v>780</v>
+      </c>
+      <c r="F78" s="282" t="s">
         <v>781</v>
       </c>
-      <c r="F78" s="282" t="s">
+      <c r="G78" s="281" t="s">
         <v>782</v>
-      </c>
-      <c r="G78" s="281" t="s">
-        <v>783</v>
       </c>
       <c r="H78" s="279"/>
     </row>
@@ -14165,13 +14238,13 @@
       <c r="C79" s="286"/>
       <c r="D79" s="283"/>
       <c r="E79" s="281" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F79" s="282" t="s">
+        <v>786</v>
+      </c>
+      <c r="G79" s="281" t="s">
         <v>787</v>
-      </c>
-      <c r="G79" s="281" t="s">
-        <v>788</v>
       </c>
       <c r="H79" s="279"/>
     </row>
@@ -14181,13 +14254,13 @@
       <c r="C80" s="287"/>
       <c r="D80" s="284"/>
       <c r="E80" s="281" t="s">
+        <v>789</v>
+      </c>
+      <c r="F80" s="282" t="s">
         <v>790</v>
       </c>
-      <c r="F80" s="282" t="s">
+      <c r="G80" s="281" t="s">
         <v>791</v>
-      </c>
-      <c r="G80" s="281" t="s">
-        <v>792</v>
       </c>
       <c r="H80" s="279"/>
     </row>
@@ -14198,16 +14271,16 @@
         <v>19</v>
       </c>
       <c r="D81" s="280" t="s">
+        <v>792</v>
+      </c>
+      <c r="E81" s="281" t="s">
         <v>793</v>
       </c>
-      <c r="E81" s="281" t="s">
+      <c r="F81" s="282" t="s">
         <v>794</v>
       </c>
-      <c r="F81" s="282" t="s">
+      <c r="G81" s="281" t="s">
         <v>795</v>
-      </c>
-      <c r="G81" s="281" t="s">
-        <v>796</v>
       </c>
       <c r="H81" s="279"/>
     </row>
@@ -14217,13 +14290,13 @@
       <c r="C82" s="286"/>
       <c r="D82" s="283"/>
       <c r="E82" s="281" t="s">
+        <v>796</v>
+      </c>
+      <c r="F82" s="282" t="s">
         <v>797</v>
       </c>
-      <c r="F82" s="282" t="s">
+      <c r="G82" s="281" t="s">
         <v>798</v>
-      </c>
-      <c r="G82" s="281" t="s">
-        <v>799</v>
       </c>
       <c r="H82" s="279"/>
     </row>
@@ -14233,13 +14306,13 @@
       <c r="C83" s="287"/>
       <c r="D83" s="284"/>
       <c r="E83" s="281" t="s">
+        <v>800</v>
+      </c>
+      <c r="F83" s="282" t="s">
         <v>801</v>
       </c>
-      <c r="F83" s="282" t="s">
+      <c r="G83" s="281" t="s">
         <v>802</v>
-      </c>
-      <c r="G83" s="281" t="s">
-        <v>803</v>
       </c>
       <c r="H83" s="279"/>
     </row>
@@ -14250,16 +14323,16 @@
         <v>20</v>
       </c>
       <c r="D84" s="280" t="s">
+        <v>803</v>
+      </c>
+      <c r="E84" s="281" t="s">
         <v>804</v>
       </c>
-      <c r="E84" s="281" t="s">
+      <c r="F84" s="282" t="s">
         <v>805</v>
       </c>
-      <c r="F84" s="282" t="s">
+      <c r="G84" s="281" t="s">
         <v>806</v>
-      </c>
-      <c r="G84" s="281" t="s">
-        <v>807</v>
       </c>
       <c r="H84" s="279"/>
     </row>
@@ -14269,13 +14342,13 @@
       <c r="C85" s="286"/>
       <c r="D85" s="283"/>
       <c r="E85" s="281" t="s">
+        <v>807</v>
+      </c>
+      <c r="F85" s="282" t="s">
         <v>808</v>
       </c>
-      <c r="F85" s="282" t="s">
+      <c r="G85" s="281" t="s">
         <v>809</v>
-      </c>
-      <c r="G85" s="281" t="s">
-        <v>810</v>
       </c>
       <c r="H85" s="279"/>
     </row>
@@ -14285,13 +14358,13 @@
       <c r="C86" s="287"/>
       <c r="D86" s="284"/>
       <c r="E86" s="281" t="s">
+        <v>811</v>
+      </c>
+      <c r="F86" s="282" t="s">
         <v>812</v>
       </c>
-      <c r="F86" s="282" t="s">
+      <c r="G86" s="281" t="s">
         <v>813</v>
-      </c>
-      <c r="G86" s="281" t="s">
-        <v>814</v>
       </c>
       <c r="H86" s="279"/>
     </row>
@@ -14717,7 +14790,7 @@
       <c r="B25" s="203"/>
       <c r="C25" s="203"/>
       <c r="D25" s="211" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E25" s="211" t="s">
         <v>444</v>
@@ -14726,7 +14799,7 @@
         <v>447</v>
       </c>
       <c r="G25" s="211" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H25" s="235">
         <v>2</v>
@@ -14737,7 +14810,7 @@
       <c r="B26" s="203"/>
       <c r="C26" s="203"/>
       <c r="D26" s="211" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E26" s="211" t="s">
         <v>444</v>
@@ -14746,7 +14819,7 @@
         <v>447</v>
       </c>
       <c r="G26" s="211" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H26" s="235">
         <v>20</v>
@@ -14768,7 +14841,7 @@
       <c r="B28" s="203"/>
       <c r="C28" s="203"/>
       <c r="D28" s="229" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E28" s="203"/>
       <c r="F28" s="203"/>
@@ -14781,13 +14854,13 @@
       <c r="B29" s="203"/>
       <c r="C29" s="203"/>
       <c r="D29" s="232" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E29" s="232" t="s">
         <v>349</v>
       </c>
       <c r="F29" s="232" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G29" s="203"/>
       <c r="H29" s="203"/>
@@ -14798,13 +14871,13 @@
       <c r="B30" s="203"/>
       <c r="C30" s="203"/>
       <c r="D30" s="212" t="s">
+        <v>486</v>
+      </c>
+      <c r="E30" s="212" t="s">
         <v>487</v>
       </c>
-      <c r="E30" s="212" t="s">
+      <c r="F30" s="212" t="s">
         <v>488</v>
-      </c>
-      <c r="F30" s="212" t="s">
-        <v>489</v>
       </c>
       <c r="G30" s="203"/>
       <c r="H30" s="203"/>
@@ -14825,7 +14898,7 @@
       <c r="A32" s="201"/>
       <c r="C32" s="203"/>
       <c r="D32" s="229" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E32" s="203"/>
       <c r="F32" s="203"/>
@@ -14838,7 +14911,7 @@
       <c r="B33" s="203"/>
       <c r="C33" s="203"/>
       <c r="D33" s="81" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E33" s="203"/>
       <c r="F33" s="203"/>
@@ -14851,7 +14924,7 @@
       <c r="B34" s="203"/>
       <c r="C34" s="203"/>
       <c r="D34" s="81" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E34" s="203"/>
       <c r="F34" s="203"/>
@@ -14864,7 +14937,7 @@
       <c r="B35" s="203"/>
       <c r="C35" s="203"/>
       <c r="D35" s="81" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E35" s="203"/>
       <c r="F35" s="203"/>
@@ -14877,7 +14950,7 @@
       <c r="B36" s="203"/>
       <c r="C36" s="203"/>
       <c r="D36" s="81" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E36" s="203"/>
       <c r="F36" s="203"/>
@@ -14890,7 +14963,7 @@
       <c r="B37" s="203"/>
       <c r="C37" s="203"/>
       <c r="D37" s="81" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E37" s="203"/>
       <c r="F37" s="203"/>
@@ -14903,7 +14976,7 @@
       <c r="B38" s="203"/>
       <c r="C38" s="203"/>
       <c r="D38" s="81" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E38" s="203"/>
       <c r="F38" s="203"/>
@@ -14926,7 +14999,7 @@
       <c r="A40" s="201"/>
       <c r="B40" s="203"/>
       <c r="C40" s="205" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D40" s="203"/>
       <c r="E40" s="203"/>
@@ -15018,7 +15091,7 @@
         <v>349</v>
       </c>
       <c r="E46" s="211" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F46" s="227"/>
       <c r="G46" s="203"/>
@@ -15075,16 +15148,16 @@
       <c r="B50" s="203"/>
       <c r="C50" s="203"/>
       <c r="D50" s="211" t="s">
+        <v>623</v>
+      </c>
+      <c r="E50" s="211" t="s">
         <v>624</v>
       </c>
-      <c r="E50" s="211" t="s">
-        <v>625</v>
-      </c>
       <c r="F50" s="211" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G50" s="211" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H50" s="235">
         <v>5</v>
@@ -15107,7 +15180,7 @@
       <c r="B52" s="203"/>
       <c r="C52" s="203"/>
       <c r="D52" s="229" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E52" s="203"/>
       <c r="F52" s="203"/>
@@ -15120,13 +15193,13 @@
       <c r="B53" s="203"/>
       <c r="C53" s="203"/>
       <c r="D53" s="232" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E53" s="232" t="s">
         <v>349</v>
       </c>
       <c r="F53" s="232" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G53" s="203"/>
       <c r="H53" s="203"/>
@@ -15137,13 +15210,13 @@
       <c r="B54" s="203"/>
       <c r="C54" s="203"/>
       <c r="D54" s="212" t="s">
+        <v>486</v>
+      </c>
+      <c r="E54" s="212" t="s">
         <v>487</v>
       </c>
-      <c r="E54" s="212" t="s">
-        <v>488</v>
-      </c>
       <c r="F54" s="212" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G54" s="203"/>
       <c r="H54" s="203"/>
@@ -15154,13 +15227,13 @@
       <c r="B55" s="203"/>
       <c r="C55" s="203"/>
       <c r="D55" s="212" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E55" s="212" t="s">
+        <v>662</v>
+      </c>
+      <c r="F55" s="212" t="s">
         <v>663</v>
-      </c>
-      <c r="F55" s="212" t="s">
-        <v>664</v>
       </c>
       <c r="G55" s="203"/>
       <c r="H55" s="203"/>
@@ -15181,7 +15254,7 @@
       <c r="A57" s="201"/>
       <c r="C57" s="203"/>
       <c r="D57" s="229" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E57" s="203"/>
       <c r="F57" s="203"/>
@@ -15194,7 +15267,7 @@
       <c r="B58" s="203"/>
       <c r="C58" s="203"/>
       <c r="D58" s="81" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E58" s="203"/>
       <c r="F58" s="203"/>
@@ -15207,7 +15280,7 @@
       <c r="B59" s="203"/>
       <c r="C59" s="203"/>
       <c r="D59" s="81" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E59" s="203"/>
       <c r="F59" s="203"/>
@@ -15220,7 +15293,7 @@
       <c r="B60" s="203"/>
       <c r="C60" s="203"/>
       <c r="D60" s="81" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E60" s="203"/>
       <c r="F60" s="203"/>
@@ -15233,7 +15306,7 @@
       <c r="B61" s="203"/>
       <c r="C61" s="203"/>
       <c r="D61" s="81" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E61" s="203"/>
       <c r="F61" s="203"/>
@@ -15256,7 +15329,7 @@
       <c r="A63" s="201"/>
       <c r="B63" s="203"/>
       <c r="C63" s="205" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D63" s="203"/>
       <c r="E63" s="203"/>
@@ -15371,7 +15444,7 @@
       <c r="B71" s="203"/>
       <c r="C71" s="203"/>
       <c r="D71" s="229" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E71" s="203"/>
       <c r="F71" s="203"/>
@@ -15412,7 +15485,7 @@
         <v>439</v>
       </c>
       <c r="G73" s="269" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H73" s="270">
         <v>5</v>
@@ -15424,16 +15497,16 @@
       <c r="B74" s="203"/>
       <c r="C74" s="203"/>
       <c r="D74" s="211" t="s">
+        <v>711</v>
+      </c>
+      <c r="E74" s="211" t="s">
         <v>712</v>
-      </c>
-      <c r="E74" s="211" t="s">
-        <v>713</v>
       </c>
       <c r="F74" s="211" t="s">
         <v>439</v>
       </c>
       <c r="G74" s="269" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H74" s="270">
         <v>5</v>
@@ -15445,16 +15518,16 @@
       <c r="B75" s="203"/>
       <c r="C75" s="203"/>
       <c r="D75" s="211" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E75" s="211" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F75" s="211" t="s">
         <v>447</v>
       </c>
       <c r="G75" s="269" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H75" s="270">
         <v>5</v>
@@ -15466,7 +15539,7 @@
       <c r="B76" s="203"/>
       <c r="C76" s="203"/>
       <c r="D76" s="211" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E76" s="211" t="s">
         <v>461</v>
@@ -15475,7 +15548,7 @@
         <v>447</v>
       </c>
       <c r="G76" s="269" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H76" s="270">
         <v>5</v>
@@ -15498,7 +15571,7 @@
       <c r="B78" s="203"/>
       <c r="C78" s="203"/>
       <c r="D78" s="229" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E78" s="203"/>
       <c r="F78" s="203"/>
@@ -15511,13 +15584,13 @@
       <c r="B79" s="203"/>
       <c r="C79" s="203"/>
       <c r="D79" s="232" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E79" s="232" t="s">
         <v>349</v>
       </c>
       <c r="F79" s="232" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G79" s="203"/>
       <c r="H79" s="203"/>
@@ -15528,13 +15601,13 @@
       <c r="B80" s="203"/>
       <c r="C80" s="203"/>
       <c r="D80" s="212" t="s">
+        <v>719</v>
+      </c>
+      <c r="E80" s="212" t="s">
         <v>720</v>
       </c>
-      <c r="E80" s="212" t="s">
+      <c r="F80" s="212" t="s">
         <v>721</v>
-      </c>
-      <c r="F80" s="212" t="s">
-        <v>722</v>
       </c>
       <c r="G80" s="203"/>
       <c r="H80" s="203"/>
@@ -15545,13 +15618,13 @@
       <c r="B81" s="203"/>
       <c r="C81" s="203"/>
       <c r="D81" s="212" t="s">
+        <v>722</v>
+      </c>
+      <c r="E81" s="212" t="s">
         <v>723</v>
       </c>
-      <c r="E81" s="212" t="s">
+      <c r="F81" s="212" t="s">
         <v>724</v>
-      </c>
-      <c r="F81" s="212" t="s">
-        <v>725</v>
       </c>
       <c r="G81" s="203"/>
       <c r="H81" s="203"/>
@@ -15562,13 +15635,13 @@
       <c r="B82" s="203"/>
       <c r="C82" s="203"/>
       <c r="D82" s="212" t="s">
+        <v>725</v>
+      </c>
+      <c r="E82" s="212" t="s">
         <v>726</v>
       </c>
-      <c r="E82" s="212" t="s">
+      <c r="F82" s="212" t="s">
         <v>727</v>
-      </c>
-      <c r="F82" s="212" t="s">
-        <v>728</v>
       </c>
       <c r="G82" s="203"/>
       <c r="H82" s="203"/>
@@ -15579,7 +15652,7 @@
       <c r="B83" s="203"/>
       <c r="C83" s="203"/>
       <c r="D83" s="203" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E83" s="203"/>
       <c r="F83" s="203"/>
@@ -15603,7 +15676,7 @@
       <c r="B85" s="203"/>
       <c r="C85" s="203"/>
       <c r="D85" s="229" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E85" s="203"/>
       <c r="F85" s="203"/>
@@ -15616,13 +15689,13 @@
       <c r="B86" s="203"/>
       <c r="C86" s="203"/>
       <c r="D86" s="232" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E86" s="232" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F86" s="266" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G86" s="285"/>
       <c r="H86" s="201"/>
@@ -15636,10 +15709,10 @@
         <v>455</v>
       </c>
       <c r="E87" s="211" t="s">
+        <v>749</v>
+      </c>
+      <c r="F87" s="269" t="s">
         <v>750</v>
-      </c>
-      <c r="F87" s="269" t="s">
-        <v>751</v>
       </c>
       <c r="G87" s="285"/>
       <c r="H87" s="201"/>
@@ -15653,10 +15726,10 @@
         <v>455</v>
       </c>
       <c r="E88" s="211" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F88" s="269" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G88" s="285"/>
       <c r="H88" s="201"/>
@@ -15670,10 +15743,10 @@
         <v>455</v>
       </c>
       <c r="E89" s="211" t="s">
+        <v>757</v>
+      </c>
+      <c r="F89" s="269" t="s">
         <v>758</v>
-      </c>
-      <c r="F89" s="269" t="s">
-        <v>759</v>
       </c>
       <c r="G89" s="285"/>
       <c r="H89" s="201"/>
@@ -15684,13 +15757,13 @@
       <c r="B90" s="203"/>
       <c r="C90" s="203"/>
       <c r="D90" s="211" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E90" s="211" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F90" s="269" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G90" s="285"/>
       <c r="H90" s="201"/>
@@ -15701,13 +15774,13 @@
       <c r="B91" s="203"/>
       <c r="C91" s="203"/>
       <c r="D91" s="211" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E91" s="211" t="s">
+        <v>760</v>
+      </c>
+      <c r="F91" s="269" t="s">
         <v>761</v>
-      </c>
-      <c r="F91" s="269" t="s">
-        <v>762</v>
       </c>
       <c r="G91" s="285"/>
       <c r="H91" s="201"/>
@@ -15718,13 +15791,13 @@
       <c r="B92" s="203"/>
       <c r="C92" s="203"/>
       <c r="D92" s="211" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E92" s="211" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F92" s="269" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G92" s="285"/>
       <c r="H92" s="201"/>
@@ -15735,13 +15808,13 @@
       <c r="B93" s="203"/>
       <c r="C93" s="203"/>
       <c r="D93" s="211" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E93" s="211" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F93" s="269" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G93" s="285"/>
       <c r="H93" s="201"/>
@@ -15752,13 +15825,13 @@
       <c r="B94" s="203"/>
       <c r="C94" s="203"/>
       <c r="D94" s="211" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E94" s="211" t="s">
+        <v>769</v>
+      </c>
+      <c r="F94" s="269" t="s">
         <v>770</v>
-      </c>
-      <c r="F94" s="269" t="s">
-        <v>771</v>
       </c>
       <c r="G94" s="285"/>
       <c r="H94" s="201"/>
@@ -15779,7 +15852,7 @@
       <c r="A96" s="201"/>
       <c r="C96" s="203"/>
       <c r="D96" s="229" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E96" s="203"/>
       <c r="F96" s="203"/>
@@ -15792,7 +15865,7 @@
       <c r="B97" s="203"/>
       <c r="C97" s="203"/>
       <c r="D97" s="81" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E97" s="203"/>
       <c r="F97" s="203"/>
@@ -15805,7 +15878,7 @@
       <c r="B98" s="203"/>
       <c r="C98" s="203"/>
       <c r="D98" s="81" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E98" s="203"/>
       <c r="F98" s="203"/>
@@ -15818,7 +15891,7 @@
       <c r="B99" s="203"/>
       <c r="C99" s="203"/>
       <c r="D99" s="81" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E99" s="203"/>
       <c r="F99" s="203"/>
@@ -15831,7 +15904,7 @@
       <c r="B100" s="203"/>
       <c r="C100" s="203"/>
       <c r="D100" s="81" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E100" s="203"/>
       <c r="F100" s="203"/>
@@ -15844,7 +15917,7 @@
       <c r="B101" s="203"/>
       <c r="C101" s="203"/>
       <c r="D101" s="81" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E101" s="203"/>
       <c r="F101" s="203"/>
@@ -15878,7 +15951,7 @@
       <c r="A104" s="201"/>
       <c r="B104" s="203"/>
       <c r="C104" s="205" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D104" s="203"/>
       <c r="E104" s="203"/>
@@ -15925,7 +15998,7 @@
         <v>409</v>
       </c>
       <c r="E107" s="212" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F107" s="203"/>
       <c r="G107" s="203"/>
@@ -15955,7 +16028,7 @@
         <v>416</v>
       </c>
       <c r="E109" s="212" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F109" s="203"/>
       <c r="G109" s="203"/>
@@ -15970,7 +16043,7 @@
         <v>349</v>
       </c>
       <c r="E110" s="211" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F110" s="227"/>
       <c r="G110" s="203"/>
@@ -15982,7 +16055,7 @@
       <c r="B111" s="203"/>
       <c r="C111" s="203"/>
       <c r="D111" s="203" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E111" s="203"/>
       <c r="F111" s="203"/>
@@ -16006,7 +16079,7 @@
       <c r="B113" s="203"/>
       <c r="C113" s="203"/>
       <c r="D113" s="229" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E113" s="203"/>
       <c r="F113" s="203"/>
@@ -16036,13 +16109,13 @@
       <c r="B115" s="203"/>
       <c r="C115" s="203"/>
       <c r="D115" s="211" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E115" s="211" t="s">
+        <v>818</v>
+      </c>
+      <c r="F115" s="269" t="s">
         <v>819</v>
-      </c>
-      <c r="F115" s="269" t="s">
-        <v>820</v>
       </c>
       <c r="G115" s="289"/>
       <c r="H115" s="290"/>
@@ -16053,13 +16126,13 @@
       <c r="B116" s="203"/>
       <c r="C116" s="203"/>
       <c r="D116" s="211" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E116" s="211" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F116" s="269" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G116" s="289"/>
       <c r="H116" s="290"/>
@@ -16070,13 +16143,13 @@
       <c r="B117" s="203"/>
       <c r="C117" s="203"/>
       <c r="D117" s="211" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E117" s="211" t="s">
+        <v>821</v>
+      </c>
+      <c r="F117" s="269" t="s">
         <v>822</v>
-      </c>
-      <c r="F117" s="269" t="s">
-        <v>823</v>
       </c>
       <c r="G117" s="289"/>
       <c r="H117" s="290"/>
@@ -16087,13 +16160,13 @@
       <c r="B118" s="203"/>
       <c r="C118" s="203"/>
       <c r="D118" s="211" t="s">
+        <v>725</v>
+      </c>
+      <c r="E118" s="211" t="s">
         <v>726</v>
       </c>
-      <c r="E118" s="211" t="s">
+      <c r="F118" s="269" t="s">
         <v>727</v>
-      </c>
-      <c r="F118" s="269" t="s">
-        <v>728</v>
       </c>
       <c r="G118" s="289"/>
       <c r="H118" s="290"/>
@@ -16104,13 +16177,13 @@
       <c r="B119" s="203"/>
       <c r="C119" s="203"/>
       <c r="D119" s="211" t="s">
+        <v>823</v>
+      </c>
+      <c r="E119" s="211" t="s">
         <v>824</v>
       </c>
-      <c r="E119" s="211" t="s">
+      <c r="F119" s="269" t="s">
         <v>825</v>
-      </c>
-      <c r="F119" s="269" t="s">
-        <v>826</v>
       </c>
       <c r="G119" s="289"/>
       <c r="H119" s="290"/>
@@ -16131,7 +16204,7 @@
       <c r="A121" s="201"/>
       <c r="C121" s="203"/>
       <c r="D121" s="229" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E121" s="203"/>
       <c r="F121" s="203"/>
@@ -16144,7 +16217,7 @@
       <c r="B122" s="203"/>
       <c r="C122" s="203"/>
       <c r="D122" s="81" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E122" s="203"/>
       <c r="F122" s="203"/>
@@ -16157,7 +16230,7 @@
       <c r="B123" s="203"/>
       <c r="C123" s="203"/>
       <c r="D123" s="81" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E123" s="203"/>
       <c r="F123" s="203"/>
@@ -16170,7 +16243,7 @@
       <c r="B124" s="203"/>
       <c r="C124" s="203"/>
       <c r="D124" s="81" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E124" s="203"/>
       <c r="F124" s="203"/>
@@ -16183,7 +16256,7 @@
       <c r="B125" s="203"/>
       <c r="C125" s="203"/>
       <c r="D125" s="81" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E125" s="203"/>
       <c r="F125" s="203"/>
@@ -16196,7 +16269,7 @@
       <c r="B126" s="203"/>
       <c r="C126" s="203"/>
       <c r="D126" s="81" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E126" s="203"/>
       <c r="F126" s="203"/>
@@ -16219,7 +16292,7 @@
       <c r="A128" s="201"/>
       <c r="B128" s="203"/>
       <c r="C128" s="205" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D128" s="203"/>
       <c r="E128" s="203"/>
@@ -16296,7 +16369,7 @@
         <v>416</v>
       </c>
       <c r="E133" s="212" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F133" s="203"/>
       <c r="G133" s="203"/>
@@ -16311,7 +16384,7 @@
         <v>349</v>
       </c>
       <c r="E134" s="211" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F134" s="227"/>
       <c r="G134" s="203"/>
@@ -16334,7 +16407,7 @@
       <c r="B136" s="203"/>
       <c r="C136" s="203"/>
       <c r="D136" s="229" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E136" s="203"/>
       <c r="F136" s="203"/>
@@ -16347,13 +16420,13 @@
       <c r="B137" s="203"/>
       <c r="C137" s="203"/>
       <c r="D137" s="232" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E137" s="232" t="s">
         <v>349</v>
       </c>
       <c r="F137" s="232" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G137" s="203"/>
       <c r="H137" s="203"/>
@@ -16364,13 +16437,13 @@
       <c r="B138" s="203"/>
       <c r="C138" s="203"/>
       <c r="D138" s="212" t="s">
+        <v>834</v>
+      </c>
+      <c r="E138" s="212" t="s">
         <v>835</v>
       </c>
-      <c r="E138" s="212" t="s">
+      <c r="F138" s="212" t="s">
         <v>836</v>
-      </c>
-      <c r="F138" s="212" t="s">
-        <v>837</v>
       </c>
       <c r="G138" s="203"/>
       <c r="H138" s="203"/>
@@ -16381,13 +16454,13 @@
       <c r="B139" s="203"/>
       <c r="C139" s="203"/>
       <c r="D139" s="212" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E139" s="212" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F139" s="212" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G139" s="203"/>
       <c r="H139" s="203"/>
@@ -16398,13 +16471,13 @@
       <c r="B140" s="203"/>
       <c r="C140" s="203"/>
       <c r="D140" s="212" t="s">
+        <v>725</v>
+      </c>
+      <c r="E140" s="212" t="s">
         <v>726</v>
       </c>
-      <c r="E140" s="212" t="s">
+      <c r="F140" s="212" t="s">
         <v>727</v>
-      </c>
-      <c r="F140" s="212" t="s">
-        <v>728</v>
       </c>
       <c r="G140" s="203"/>
       <c r="H140" s="203"/>
@@ -16415,13 +16488,13 @@
       <c r="B141" s="203"/>
       <c r="C141" s="203"/>
       <c r="D141" s="291" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E141" s="291" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F141" s="291" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G141" s="203"/>
       <c r="H141" s="203"/>
@@ -16442,7 +16515,7 @@
       <c r="A143" s="201"/>
       <c r="C143" s="203"/>
       <c r="D143" s="229" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E143" s="203"/>
       <c r="F143" s="203"/>
@@ -16455,7 +16528,7 @@
       <c r="B144" s="203"/>
       <c r="C144" s="203"/>
       <c r="D144" s="81" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E144" s="203"/>
       <c r="F144" s="203"/>
@@ -16468,7 +16541,7 @@
       <c r="B145" s="203"/>
       <c r="C145" s="203"/>
       <c r="D145" s="81" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E145" s="203"/>
       <c r="F145" s="203"/>
@@ -16481,7 +16554,7 @@
       <c r="B146" s="203"/>
       <c r="C146" s="203"/>
       <c r="D146" s="81" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E146" s="203"/>
       <c r="F146" s="203"/>
@@ -16504,7 +16577,7 @@
       <c r="A148" s="201"/>
       <c r="B148" s="203"/>
       <c r="C148" s="205" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D148" s="203"/>
       <c r="E148" s="203"/>
@@ -16518,7 +16591,7 @@
       <c r="B149" s="203"/>
       <c r="C149" s="203"/>
       <c r="D149" s="81" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E149" s="203"/>
       <c r="F149" s="203"/>
@@ -16546,10 +16619,10 @@
       <c r="B151" s="203"/>
       <c r="C151" s="203"/>
       <c r="D151" s="211" t="s">
+        <v>843</v>
+      </c>
+      <c r="E151" s="211" t="s">
         <v>844</v>
-      </c>
-      <c r="E151" s="211" t="s">
-        <v>845</v>
       </c>
       <c r="F151" s="203"/>
       <c r="G151" s="203"/>
@@ -16561,10 +16634,10 @@
       <c r="B152" s="203"/>
       <c r="C152" s="203"/>
       <c r="D152" s="212" t="s">
+        <v>845</v>
+      </c>
+      <c r="E152" s="212" t="s">
         <v>846</v>
-      </c>
-      <c r="E152" s="212" t="s">
-        <v>847</v>
       </c>
       <c r="F152" s="203"/>
       <c r="G152" s="203"/>
@@ -16576,10 +16649,10 @@
       <c r="B153" s="203"/>
       <c r="C153" s="203"/>
       <c r="D153" s="211" t="s">
+        <v>847</v>
+      </c>
+      <c r="E153" s="211" t="s">
         <v>848</v>
-      </c>
-      <c r="E153" s="211" t="s">
-        <v>849</v>
       </c>
       <c r="F153" s="203"/>
       <c r="G153" s="203"/>
@@ -16602,7 +16675,7 @@
       <c r="B155" s="203"/>
       <c r="C155" s="203"/>
       <c r="D155" s="229" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E155" s="203"/>
       <c r="F155" s="203"/>
@@ -16630,10 +16703,10 @@
       <c r="B157" s="203"/>
       <c r="C157" s="203"/>
       <c r="D157" s="211" t="s">
+        <v>850</v>
+      </c>
+      <c r="E157" s="269" t="s">
         <v>851</v>
-      </c>
-      <c r="E157" s="269" t="s">
-        <v>852</v>
       </c>
       <c r="F157" s="289"/>
       <c r="G157" s="258"/>
@@ -16645,10 +16718,10 @@
       <c r="B158" s="203"/>
       <c r="C158" s="203"/>
       <c r="D158" s="211" t="s">
+        <v>852</v>
+      </c>
+      <c r="E158" s="269" t="s">
         <v>853</v>
-      </c>
-      <c r="E158" s="269" t="s">
-        <v>854</v>
       </c>
       <c r="F158" s="289"/>
       <c r="G158" s="258"/>
@@ -16660,10 +16733,10 @@
       <c r="B159" s="203"/>
       <c r="C159" s="203"/>
       <c r="D159" s="211" t="s">
+        <v>854</v>
+      </c>
+      <c r="E159" s="269" t="s">
         <v>855</v>
-      </c>
-      <c r="E159" s="269" t="s">
-        <v>856</v>
       </c>
       <c r="F159" s="289"/>
       <c r="G159" s="258"/>
@@ -16675,10 +16748,10 @@
       <c r="B160" s="203"/>
       <c r="C160" s="203"/>
       <c r="D160" s="211" t="s">
+        <v>856</v>
+      </c>
+      <c r="E160" s="269" t="s">
         <v>857</v>
-      </c>
-      <c r="E160" s="269" t="s">
-        <v>858</v>
       </c>
       <c r="F160" s="289"/>
       <c r="G160" s="258"/>
@@ -16690,10 +16763,10 @@
       <c r="B161" s="203"/>
       <c r="C161" s="203"/>
       <c r="D161" s="211" t="s">
+        <v>858</v>
+      </c>
+      <c r="E161" s="269" t="s">
         <v>859</v>
-      </c>
-      <c r="E161" s="269" t="s">
-        <v>860</v>
       </c>
       <c r="F161" s="289"/>
       <c r="G161" s="258"/>
@@ -16705,10 +16778,10 @@
       <c r="B162" s="203"/>
       <c r="C162" s="203"/>
       <c r="D162" s="211" t="s">
+        <v>860</v>
+      </c>
+      <c r="E162" s="269" t="s">
         <v>861</v>
-      </c>
-      <c r="E162" s="269" t="s">
-        <v>862</v>
       </c>
       <c r="F162" s="289"/>
       <c r="G162" s="258"/>
@@ -16720,10 +16793,10 @@
       <c r="B163" s="203"/>
       <c r="C163" s="203"/>
       <c r="D163" s="211" t="s">
+        <v>862</v>
+      </c>
+      <c r="E163" s="269" t="s">
         <v>863</v>
-      </c>
-      <c r="E163" s="269" t="s">
-        <v>864</v>
       </c>
       <c r="F163" s="289"/>
       <c r="G163" s="258"/>
@@ -16745,7 +16818,7 @@
       <c r="A165" s="201"/>
       <c r="B165" s="203"/>
       <c r="C165" s="205" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D165" s="203"/>
       <c r="E165" s="203"/>
@@ -16758,7 +16831,7 @@
       <c r="A166" s="201"/>
       <c r="B166" s="203"/>
       <c r="C166" s="203" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D166" s="271"/>
       <c r="E166" s="271"/>
@@ -16772,13 +16845,13 @@
       <c r="B167" s="203"/>
       <c r="C167" s="203"/>
       <c r="D167" s="208" t="s">
+        <v>866</v>
+      </c>
+      <c r="E167" s="208" t="s">
         <v>867</v>
       </c>
-      <c r="E167" s="208" t="s">
+      <c r="F167" s="208" t="s">
         <v>868</v>
-      </c>
-      <c r="F167" s="208" t="s">
-        <v>869</v>
       </c>
       <c r="G167" s="203"/>
       <c r="H167" s="203"/>
@@ -16789,13 +16862,13 @@
       <c r="B168" s="203"/>
       <c r="C168" s="203"/>
       <c r="D168" s="212" t="s">
+        <v>869</v>
+      </c>
+      <c r="E168" s="212" t="s">
+        <v>701</v>
+      </c>
+      <c r="F168" s="212" t="s">
         <v>870</v>
-      </c>
-      <c r="E168" s="212" t="s">
-        <v>702</v>
-      </c>
-      <c r="F168" s="212" t="s">
-        <v>871</v>
       </c>
       <c r="G168" s="203"/>
       <c r="H168" s="203"/>
@@ -16810,7 +16883,7 @@
         <v>442</v>
       </c>
       <c r="F169" s="211" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G169" s="203"/>
       <c r="H169" s="203"/>
@@ -16822,10 +16895,10 @@
       <c r="C170" s="203"/>
       <c r="D170" s="212"/>
       <c r="E170" s="212" t="s">
+        <v>872</v>
+      </c>
+      <c r="F170" s="212" t="s">
         <v>873</v>
-      </c>
-      <c r="F170" s="212" t="s">
-        <v>874</v>
       </c>
       <c r="G170" s="203"/>
       <c r="H170" s="203"/>
@@ -16840,7 +16913,7 @@
         <v>455</v>
       </c>
       <c r="F171" s="211" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G171" s="203"/>
       <c r="H171" s="203"/>
@@ -16852,10 +16925,10 @@
       <c r="C172" s="203"/>
       <c r="D172" s="212"/>
       <c r="E172" s="212" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F172" s="212" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G172" s="203"/>
       <c r="H172" s="203"/>
@@ -16867,10 +16940,10 @@
       <c r="C173" s="203"/>
       <c r="D173" s="292"/>
       <c r="E173" s="292" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F173" s="292" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G173" s="203"/>
       <c r="H173" s="203"/>
@@ -16882,10 +16955,10 @@
       <c r="C174" s="203"/>
       <c r="D174" s="293"/>
       <c r="E174" s="294" t="s">
+        <v>877</v>
+      </c>
+      <c r="F174" s="294" t="s">
         <v>878</v>
-      </c>
-      <c r="F174" s="294" t="s">
-        <v>879</v>
       </c>
       <c r="G174" s="203"/>
       <c r="H174" s="203"/>
@@ -16897,10 +16970,10 @@
       <c r="C175" s="203"/>
       <c r="D175" s="295"/>
       <c r="E175" s="292" t="s">
+        <v>879</v>
+      </c>
+      <c r="F175" s="292" t="s">
         <v>880</v>
-      </c>
-      <c r="F175" s="292" t="s">
-        <v>881</v>
       </c>
       <c r="G175" s="203"/>
       <c r="H175" s="203"/>
@@ -16912,10 +16985,10 @@
       <c r="C176" s="203"/>
       <c r="D176" s="296"/>
       <c r="E176" s="294" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F176" s="297" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G176" s="203"/>
       <c r="H176" s="203"/>
@@ -16927,10 +17000,10 @@
       <c r="C177" s="203"/>
       <c r="D177" s="295"/>
       <c r="E177" s="292" t="s">
+        <v>882</v>
+      </c>
+      <c r="F177" s="292" t="s">
         <v>883</v>
-      </c>
-      <c r="F177" s="292" t="s">
-        <v>884</v>
       </c>
       <c r="G177" s="203"/>
       <c r="H177" s="203"/>
@@ -16942,10 +17015,10 @@
       <c r="C178" s="203"/>
       <c r="D178" s="293"/>
       <c r="E178" s="294" t="s">
+        <v>884</v>
+      </c>
+      <c r="F178" s="297" t="s">
         <v>885</v>
-      </c>
-      <c r="F178" s="297" t="s">
-        <v>886</v>
       </c>
       <c r="G178" s="203"/>
       <c r="H178" s="203"/>
@@ -16966,7 +17039,7 @@
       <c r="A180" s="201"/>
       <c r="B180" s="203"/>
       <c r="C180" s="205" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D180" s="203"/>
       <c r="E180" s="203"/>
@@ -16980,7 +17053,7 @@
       <c r="B181" s="203"/>
       <c r="C181" s="203"/>
       <c r="D181" s="229" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E181" s="203"/>
       <c r="F181" s="203"/>
@@ -16993,13 +17066,13 @@
       <c r="B182" s="203"/>
       <c r="C182" s="203"/>
       <c r="D182" s="232" t="s">
+        <v>887</v>
+      </c>
+      <c r="E182" s="232" t="s">
         <v>888</v>
       </c>
-      <c r="E182" s="232" t="s">
+      <c r="F182" s="232" t="s">
         <v>889</v>
-      </c>
-      <c r="F182" s="232" t="s">
-        <v>890</v>
       </c>
       <c r="G182" s="203"/>
       <c r="H182" s="203"/>
@@ -17010,13 +17083,13 @@
       <c r="B183" s="203"/>
       <c r="C183" s="203"/>
       <c r="D183" s="212" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E183" s="301">
         <v>404</v>
       </c>
       <c r="F183" s="212" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G183" s="203"/>
       <c r="H183" s="203"/>
@@ -17027,13 +17100,13 @@
       <c r="B184" s="203"/>
       <c r="C184" s="203"/>
       <c r="D184" s="212" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E184" s="301">
         <v>422</v>
       </c>
       <c r="F184" s="212" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G184" s="203"/>
       <c r="H184" s="203"/>
@@ -17044,13 +17117,13 @@
       <c r="B185" s="203"/>
       <c r="C185" s="203"/>
       <c r="D185" s="212" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E185" s="301">
         <v>401</v>
       </c>
       <c r="F185" s="212" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G185" s="203"/>
       <c r="H185" s="203"/>
@@ -17061,13 +17134,13 @@
       <c r="B186" s="203"/>
       <c r="C186" s="203"/>
       <c r="D186" s="291" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E186" s="302">
         <v>403</v>
       </c>
       <c r="F186" s="291" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G186" s="203"/>
       <c r="H186" s="203"/>
@@ -17081,11 +17154,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{670B653A-538B-1F49-B095-95AC213C8895}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CE4CA6A-E328-0141-BEB6-738B34DAA966}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="2.6640625" style="306" customWidth="1"/>
@@ -17188,19 +17261,19 @@
         <v>36</v>
       </c>
       <c r="E6" s="318" t="s">
+        <v>895</v>
+      </c>
+      <c r="F6" s="319" t="s">
         <v>896</v>
       </c>
-      <c r="F6" s="319" t="s">
+      <c r="G6" s="320" t="s">
         <v>897</v>
       </c>
-      <c r="G6" s="320" t="s">
+      <c r="H6" s="321" t="s">
+        <v>897</v>
+      </c>
+      <c r="I6" s="322" t="s">
         <v>898</v>
-      </c>
-      <c r="H6" s="321" t="s">
-        <v>898</v>
-      </c>
-      <c r="I6" s="322" t="s">
-        <v>899</v>
       </c>
       <c r="J6" s="305"/>
     </row>
@@ -17214,19 +17287,19 @@
         <v>42</v>
       </c>
       <c r="E7" s="325" t="s">
+        <v>899</v>
+      </c>
+      <c r="F7" s="326" t="s">
+        <v>896</v>
+      </c>
+      <c r="G7" s="327" t="s">
+        <v>897</v>
+      </c>
+      <c r="H7" s="328" t="s">
+        <v>897</v>
+      </c>
+      <c r="I7" s="329" t="s">
         <v>900</v>
-      </c>
-      <c r="F7" s="326" t="s">
-        <v>897</v>
-      </c>
-      <c r="G7" s="327" t="s">
-        <v>898</v>
-      </c>
-      <c r="H7" s="328" t="s">
-        <v>898</v>
-      </c>
-      <c r="I7" s="329" t="s">
-        <v>901</v>
       </c>
       <c r="J7" s="305"/>
     </row>
@@ -17234,25 +17307,25 @@
       <c r="A8" s="312"/>
       <c r="B8" s="304"/>
       <c r="C8" s="330" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D8" s="324" t="s">
         <v>52</v>
       </c>
       <c r="E8" s="325" t="s">
+        <v>902</v>
+      </c>
+      <c r="F8" s="331" t="s">
         <v>903</v>
       </c>
-      <c r="F8" s="331" t="s">
+      <c r="G8" s="332" t="s">
         <v>904</v>
       </c>
-      <c r="G8" s="332" t="s">
+      <c r="H8" s="333" t="s">
         <v>905</v>
       </c>
-      <c r="H8" s="333" t="s">
+      <c r="I8" s="334" t="s">
         <v>906</v>
-      </c>
-      <c r="I8" s="334" t="s">
-        <v>907</v>
       </c>
       <c r="J8" s="305"/>
     </row>
@@ -17266,19 +17339,19 @@
         <v>56</v>
       </c>
       <c r="E9" s="325" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F9" s="331" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G9" s="335" t="s">
+        <v>907</v>
+      </c>
+      <c r="H9" s="333" t="s">
+        <v>905</v>
+      </c>
+      <c r="I9" s="336" t="s">
         <v>908</v>
-      </c>
-      <c r="H9" s="333" t="s">
-        <v>906</v>
-      </c>
-      <c r="I9" s="336" t="s">
-        <v>909</v>
       </c>
       <c r="J9" s="305"/>
     </row>
@@ -17292,19 +17365,19 @@
         <v>60</v>
       </c>
       <c r="E10" s="325" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F10" s="331" t="s">
+        <v>909</v>
+      </c>
+      <c r="G10" s="335" t="s">
         <v>910</v>
       </c>
-      <c r="G10" s="335" t="s">
+      <c r="H10" s="333" t="s">
+        <v>905</v>
+      </c>
+      <c r="I10" s="336" t="s">
         <v>911</v>
-      </c>
-      <c r="H10" s="333" t="s">
-        <v>906</v>
-      </c>
-      <c r="I10" s="336" t="s">
-        <v>912</v>
       </c>
       <c r="J10" s="305"/>
     </row>
@@ -17318,19 +17391,19 @@
         <v>67</v>
       </c>
       <c r="E11" s="325" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F11" s="331" t="s">
+        <v>912</v>
+      </c>
+      <c r="G11" s="335" t="s">
+        <v>907</v>
+      </c>
+      <c r="H11" s="333" t="s">
+        <v>905</v>
+      </c>
+      <c r="I11" s="336" t="s">
         <v>913</v>
-      </c>
-      <c r="G11" s="335" t="s">
-        <v>908</v>
-      </c>
-      <c r="H11" s="333" t="s">
-        <v>906</v>
-      </c>
-      <c r="I11" s="336" t="s">
-        <v>914</v>
       </c>
       <c r="J11" s="305"/>
     </row>
@@ -17344,19 +17417,19 @@
         <v>70</v>
       </c>
       <c r="E12" s="338" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F12" s="331" t="s">
+        <v>896</v>
+      </c>
+      <c r="G12" s="339" t="s">
         <v>897</v>
       </c>
-      <c r="G12" s="339" t="s">
-        <v>898</v>
-      </c>
       <c r="H12" s="333" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I12" s="340" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="J12" s="305"/>
     </row>
@@ -17370,19 +17443,19 @@
         <v>78</v>
       </c>
       <c r="E13" s="342" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F13" s="326" t="s">
+        <v>915</v>
+      </c>
+      <c r="G13" s="335" t="s">
+        <v>907</v>
+      </c>
+      <c r="H13" s="333" t="s">
+        <v>905</v>
+      </c>
+      <c r="I13" s="334" t="s">
         <v>916</v>
-      </c>
-      <c r="G13" s="335" t="s">
-        <v>908</v>
-      </c>
-      <c r="H13" s="333" t="s">
-        <v>906</v>
-      </c>
-      <c r="I13" s="334" t="s">
-        <v>917</v>
       </c>
       <c r="J13" s="305"/>
     </row>
@@ -17393,22 +17466,22 @@
         <v>80</v>
       </c>
       <c r="D14" s="337" t="s">
+        <v>917</v>
+      </c>
+      <c r="E14" s="343" t="s">
+        <v>899</v>
+      </c>
+      <c r="F14" s="326" t="s">
+        <v>915</v>
+      </c>
+      <c r="G14" s="335" t="s">
         <v>918</v>
       </c>
-      <c r="E14" s="343" t="s">
-        <v>900</v>
-      </c>
-      <c r="F14" s="326" t="s">
-        <v>916</v>
-      </c>
-      <c r="G14" s="335" t="s">
+      <c r="H14" s="333" t="s">
+        <v>905</v>
+      </c>
+      <c r="I14" s="334" t="s">
         <v>919</v>
-      </c>
-      <c r="H14" s="333" t="s">
-        <v>906</v>
-      </c>
-      <c r="I14" s="334" t="s">
-        <v>920</v>
       </c>
       <c r="J14" s="305"/>
     </row>
@@ -17422,19 +17495,19 @@
         <v>85</v>
       </c>
       <c r="E15" s="344" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F15" s="331" t="s">
+        <v>920</v>
+      </c>
+      <c r="G15" s="335" t="s">
+        <v>907</v>
+      </c>
+      <c r="H15" s="333" t="s">
+        <v>905</v>
+      </c>
+      <c r="I15" s="334" t="s">
         <v>921</v>
-      </c>
-      <c r="G15" s="335" t="s">
-        <v>908</v>
-      </c>
-      <c r="H15" s="333" t="s">
-        <v>906</v>
-      </c>
-      <c r="I15" s="334" t="s">
-        <v>922</v>
       </c>
       <c r="J15" s="305"/>
     </row>
@@ -17448,19 +17521,19 @@
         <v>99</v>
       </c>
       <c r="E16" s="346" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F16" s="331" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G16" s="335" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H16" s="333" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I16" s="334" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="J16" s="305"/>
     </row>
@@ -17471,22 +17544,22 @@
         <v>102</v>
       </c>
       <c r="D17" s="324" t="s">
+        <v>923</v>
+      </c>
+      <c r="E17" s="346" t="s">
+        <v>899</v>
+      </c>
+      <c r="F17" s="331" t="s">
         <v>924</v>
       </c>
-      <c r="E17" s="346" t="s">
-        <v>900</v>
-      </c>
-      <c r="F17" s="331" t="s">
+      <c r="G17" s="335" t="s">
+        <v>907</v>
+      </c>
+      <c r="H17" s="333" t="s">
+        <v>905</v>
+      </c>
+      <c r="I17" s="336" t="s">
         <v>925</v>
-      </c>
-      <c r="G17" s="335" t="s">
-        <v>908</v>
-      </c>
-      <c r="H17" s="333" t="s">
-        <v>906</v>
-      </c>
-      <c r="I17" s="336" t="s">
-        <v>926</v>
       </c>
       <c r="J17" s="305"/>
     </row>
@@ -17500,19 +17573,19 @@
         <v>108</v>
       </c>
       <c r="E18" s="349" t="s">
+        <v>926</v>
+      </c>
+      <c r="F18" s="350" t="s">
+        <v>924</v>
+      </c>
+      <c r="G18" s="351" t="s">
         <v>927</v>
       </c>
-      <c r="F18" s="350" t="s">
-        <v>925</v>
-      </c>
-      <c r="G18" s="351" t="s">
+      <c r="H18" s="352" t="s">
+        <v>905</v>
+      </c>
+      <c r="I18" s="353" t="s">
         <v>928</v>
-      </c>
-      <c r="H18" s="352" t="s">
-        <v>906</v>
-      </c>
-      <c r="I18" s="353" t="s">
-        <v>929</v>
       </c>
       <c r="J18" s="305"/>
     </row>
@@ -17520,45 +17593,57 @@
       <c r="A19" s="312"/>
       <c r="B19" s="304"/>
       <c r="C19" s="354" t="s">
+        <v>929</v>
+      </c>
+      <c r="D19" s="355" t="s">
         <v>930</v>
       </c>
-      <c r="D19" s="355" t="s">
+      <c r="E19" s="356" t="s">
+        <v>899</v>
+      </c>
+      <c r="F19" s="357" t="s">
+        <v>903</v>
+      </c>
+      <c r="G19" s="358" t="s">
         <v>931</v>
       </c>
-      <c r="E19" s="356" t="s">
-        <v>900</v>
-      </c>
-      <c r="F19" s="357" t="s">
-        <v>904</v>
-      </c>
-      <c r="G19" s="358" t="s">
+      <c r="H19" s="359" t="s">
+        <v>905</v>
+      </c>
+      <c r="I19" s="360" t="s">
         <v>932</v>
       </c>
-      <c r="H19" s="359" t="s">
-        <v>906</v>
-      </c>
-      <c r="I19" s="360" t="s">
-        <v>933</v>
-      </c>
       <c r="J19" s="305"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1">
+    <row r="20" spans="1:10" ht="45">
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
-      <c r="C20" s="312"/>
-      <c r="D20" s="312"/>
-      <c r="E20" s="312"/>
-      <c r="F20" s="312"/>
-      <c r="G20" s="312"/>
-      <c r="H20" s="312"/>
-      <c r="I20" s="305"/>
+      <c r="C20" s="354" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D20" s="355" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E20" s="356" t="s">
+        <v>897</v>
+      </c>
+      <c r="F20" s="357" t="s">
+        <v>897</v>
+      </c>
+      <c r="G20" s="358" t="s">
+        <v>897</v>
+      </c>
+      <c r="H20" s="359" t="s">
+        <v>905</v>
+      </c>
+      <c r="I20" s="360" t="s">
+        <v>1043</v>
+      </c>
       <c r="J20" s="305"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="312"/>
-      <c r="B21" s="313" t="s">
-        <v>592</v>
-      </c>
+      <c r="B21" s="304"/>
       <c r="C21" s="312"/>
       <c r="D21" s="312"/>
       <c r="E21" s="312"/>
@@ -17570,13 +17655,11 @@
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="312"/>
-      <c r="B22" s="304"/>
-      <c r="C22" s="361" t="s">
-        <v>601</v>
-      </c>
-      <c r="D22" s="362" t="s">
-        <v>349</v>
-      </c>
+      <c r="B22" s="313" t="s">
+        <v>591</v>
+      </c>
+      <c r="C22" s="312"/>
+      <c r="D22" s="312"/>
       <c r="E22" s="312"/>
       <c r="F22" s="312"/>
       <c r="G22" s="312"/>
@@ -17587,11 +17670,11 @@
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="312"/>
       <c r="B23" s="304"/>
-      <c r="C23" s="363" t="s">
-        <v>934</v>
-      </c>
-      <c r="D23" s="364" t="s">
-        <v>935</v>
+      <c r="C23" s="361" t="s">
+        <v>600</v>
+      </c>
+      <c r="D23" s="362" t="s">
+        <v>349</v>
       </c>
       <c r="E23" s="312"/>
       <c r="F23" s="312"/>
@@ -17600,14 +17683,14 @@
       <c r="I23" s="305"/>
       <c r="J23" s="305"/>
     </row>
-    <row r="24" spans="1:10" ht="16.5" customHeight="1">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="312"/>
       <c r="B24" s="304"/>
-      <c r="C24" s="365" t="s">
-        <v>936</v>
-      </c>
-      <c r="D24" s="366" t="s">
-        <v>937</v>
+      <c r="C24" s="363" t="s">
+        <v>933</v>
+      </c>
+      <c r="D24" s="364" t="s">
+        <v>934</v>
       </c>
       <c r="E24" s="312"/>
       <c r="F24" s="312"/>
@@ -17616,14 +17699,14 @@
       <c r="I24" s="305"/>
       <c r="J24" s="305"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1">
+    <row r="25" spans="1:10" ht="16.5" customHeight="1">
       <c r="A25" s="312"/>
       <c r="B25" s="304"/>
-      <c r="C25" s="367" t="s">
-        <v>938</v>
-      </c>
-      <c r="D25" s="364" t="s">
-        <v>939</v>
+      <c r="C25" s="365" t="s">
+        <v>935</v>
+      </c>
+      <c r="D25" s="366" t="s">
+        <v>936</v>
       </c>
       <c r="E25" s="312"/>
       <c r="F25" s="312"/>
@@ -17632,14 +17715,14 @@
       <c r="I25" s="305"/>
       <c r="J25" s="305"/>
     </row>
-    <row r="26" spans="1:10" ht="16.5" customHeight="1">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
       <c r="C26" s="367" t="s">
-        <v>940</v>
-      </c>
-      <c r="D26" s="366" t="s">
-        <v>941</v>
+        <v>937</v>
+      </c>
+      <c r="D26" s="364" t="s">
+        <v>938</v>
       </c>
       <c r="E26" s="312"/>
       <c r="F26" s="312"/>
@@ -17648,14 +17731,14 @@
       <c r="I26" s="305"/>
       <c r="J26" s="305"/>
     </row>
-    <row r="27" spans="1:10" ht="17.25" customHeight="1">
+    <row r="27" spans="1:10" ht="16.5" customHeight="1">
       <c r="A27" s="312"/>
       <c r="B27" s="304"/>
       <c r="C27" s="367" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="D27" s="366" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E27" s="312"/>
       <c r="F27" s="312"/>
@@ -17664,14 +17747,14 @@
       <c r="I27" s="305"/>
       <c r="J27" s="305"/>
     </row>
-    <row r="28" spans="1:10" ht="14.25" customHeight="1">
+    <row r="28" spans="1:10" ht="17.25" customHeight="1">
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
       <c r="C28" s="367" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="D28" s="366" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="E28" s="312"/>
       <c r="F28" s="312"/>
@@ -17680,11 +17763,15 @@
       <c r="I28" s="305"/>
       <c r="J28" s="305"/>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1">
+    <row r="29" spans="1:10" ht="14.25" customHeight="1">
       <c r="A29" s="312"/>
       <c r="B29" s="304"/>
-      <c r="C29" s="312"/>
-      <c r="D29" s="312"/>
+      <c r="C29" s="367" t="s">
+        <v>943</v>
+      </c>
+      <c r="D29" s="366" t="s">
+        <v>944</v>
+      </c>
       <c r="E29" s="312"/>
       <c r="F29" s="312"/>
       <c r="G29" s="312"/>
@@ -17694,11 +17781,9 @@
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="312"/>
-      <c r="B30" s="304" t="s">
-        <v>671</v>
-      </c>
+      <c r="B30" s="304"/>
       <c r="C30" s="312"/>
-      <c r="D30" s="368"/>
+      <c r="D30" s="312"/>
       <c r="E30" s="312"/>
       <c r="F30" s="312"/>
       <c r="G30" s="312"/>
@@ -17708,13 +17793,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="312"/>
-      <c r="B31" s="304"/>
-      <c r="C31" s="369" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="370" t="s">
-        <v>683</v>
-      </c>
+      <c r="B31" s="304" t="s">
+        <v>670</v>
+      </c>
+      <c r="C31" s="312"/>
+      <c r="D31" s="368"/>
       <c r="E31" s="312"/>
       <c r="F31" s="312"/>
       <c r="G31" s="312"/>
@@ -17725,11 +17808,11 @@
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
-      <c r="C32" s="363" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="371" t="s">
-        <v>946</v>
+      <c r="C32" s="369" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="370" t="s">
+        <v>682</v>
       </c>
       <c r="E32" s="312"/>
       <c r="F32" s="312"/>
@@ -17741,11 +17824,11 @@
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="312"/>
       <c r="B33" s="304"/>
-      <c r="C33" s="372" t="s">
-        <v>947</v>
+      <c r="C33" s="464" t="s">
+        <v>1044</v>
       </c>
       <c r="D33" s="371" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="E33" s="312"/>
       <c r="F33" s="312"/>
@@ -17757,11 +17840,11 @@
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="312"/>
       <c r="B34" s="304"/>
-      <c r="C34" s="371" t="s">
-        <v>464</v>
+      <c r="C34" s="372" t="s">
+        <v>946</v>
       </c>
       <c r="D34" s="371" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="E34" s="312"/>
       <c r="F34" s="312"/>
@@ -17773,11 +17856,11 @@
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
-      <c r="C35" s="371" t="s">
-        <v>55</v>
+      <c r="C35" s="372" t="s">
+        <v>901</v>
       </c>
       <c r="D35" s="371" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="E35" s="312"/>
       <c r="F35" s="312"/>
@@ -17789,11 +17872,11 @@
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
-      <c r="C36" s="371" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="373" t="s">
-        <v>951</v>
+      <c r="C36" s="372" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D36" s="371" t="s">
+        <v>949</v>
       </c>
       <c r="E36" s="312"/>
       <c r="F36" s="312"/>
@@ -17805,11 +17888,11 @@
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
-      <c r="C37" s="371" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="371" t="s">
-        <v>952</v>
+      <c r="C37" s="372" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D37" s="373" t="s">
+        <v>950</v>
       </c>
       <c r="E37" s="312"/>
       <c r="F37" s="312"/>
@@ -17821,11 +17904,11 @@
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
-      <c r="C38" s="371" t="s">
-        <v>69</v>
+      <c r="C38" s="372" t="s">
+        <v>1047</v>
       </c>
       <c r="D38" s="371" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E38" s="312"/>
       <c r="F38" s="312"/>
@@ -17837,11 +17920,11 @@
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
-      <c r="C39" s="374" t="s">
-        <v>73</v>
+      <c r="C39" s="372" t="s">
+        <v>1048</v>
       </c>
       <c r="D39" s="371" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="E39" s="312"/>
       <c r="F39" s="312"/>
@@ -17853,11 +17936,11 @@
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
-      <c r="C40" s="371" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="373" t="s">
-        <v>955</v>
+      <c r="C40" s="465" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D40" s="371" t="s">
+        <v>953</v>
       </c>
       <c r="E40" s="312"/>
       <c r="F40" s="312"/>
@@ -17869,11 +17952,11 @@
     <row r="41" spans="1:10" ht="15.75" customHeight="1">
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
-      <c r="C41" s="371" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="371" t="s">
-        <v>956</v>
+      <c r="C41" s="372" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D41" s="373" t="s">
+        <v>954</v>
       </c>
       <c r="E41" s="312"/>
       <c r="F41" s="312"/>
@@ -17885,11 +17968,11 @@
     <row r="42" spans="1:10" ht="15.75" customHeight="1">
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
-      <c r="C42" s="374" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" s="375" t="s">
-        <v>957</v>
+      <c r="C42" s="372" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D42" s="371" t="s">
+        <v>955</v>
       </c>
       <c r="E42" s="312"/>
       <c r="F42" s="312"/>
@@ -17901,11 +17984,11 @@
     <row r="43" spans="1:10" ht="15.75" customHeight="1">
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
-      <c r="C43" s="371" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="371" t="s">
-        <v>958</v>
+      <c r="C43" s="465" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D43" s="374" t="s">
+        <v>956</v>
       </c>
       <c r="E43" s="312"/>
       <c r="F43" s="312"/>
@@ -17917,11 +18000,11 @@
     <row r="44" spans="1:10" ht="15.75" customHeight="1">
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
-      <c r="C44" s="371" t="s">
-        <v>107</v>
+      <c r="C44" s="372" t="s">
+        <v>1053</v>
       </c>
       <c r="D44" s="371" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E44" s="312"/>
       <c r="F44" s="312"/>
@@ -17933,11 +18016,11 @@
     <row r="45" spans="1:10" ht="15.75" customHeight="1">
       <c r="A45" s="312"/>
       <c r="B45" s="304"/>
-      <c r="C45" s="376" t="s">
-        <v>930</v>
-      </c>
-      <c r="D45" s="377" t="s">
-        <v>960</v>
+      <c r="C45" s="372" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D45" s="371" t="s">
+        <v>958</v>
       </c>
       <c r="E45" s="312"/>
       <c r="F45" s="312"/>
@@ -17949,10 +18032,14 @@
     <row r="46" spans="1:10" ht="15.75" customHeight="1">
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
-      <c r="C46" s="312"/>
-      <c r="D46" s="312"/>
+      <c r="C46" s="466" t="s">
+        <v>929</v>
+      </c>
+      <c r="D46" s="467" t="s">
+        <v>959</v>
+      </c>
       <c r="E46" s="312"/>
-      <c r="F46" s="368"/>
+      <c r="F46" s="312"/>
       <c r="G46" s="312"/>
       <c r="H46" s="312"/>
       <c r="I46" s="305"/>
@@ -17960,13 +18047,15 @@
     </row>
     <row r="47" spans="1:10" ht="15.75" customHeight="1">
       <c r="A47" s="312"/>
-      <c r="B47" s="304" t="s">
-        <v>113</v>
-      </c>
-      <c r="C47" s="312"/>
-      <c r="D47" s="312"/>
+      <c r="B47" s="304"/>
+      <c r="C47" s="468" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D47" s="469" t="s">
+        <v>1055</v>
+      </c>
       <c r="E47" s="312"/>
-      <c r="F47" s="368"/>
+      <c r="F47" s="312"/>
       <c r="G47" s="312"/>
       <c r="H47" s="312"/>
       <c r="I47" s="305"/>
@@ -17975,33 +18064,25 @@
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
       <c r="A48" s="312"/>
       <c r="B48" s="304"/>
-      <c r="C48" s="378" t="s">
-        <v>733</v>
-      </c>
-      <c r="D48" s="369" t="s">
-        <v>735</v>
-      </c>
-      <c r="E48" s="369" t="s">
-        <v>737</v>
-      </c>
-      <c r="F48" s="379"/>
+      <c r="C48" s="312"/>
+      <c r="D48" s="312"/>
+      <c r="E48" s="312"/>
+      <c r="F48" s="368"/>
+      <c r="G48" s="312"/>
       <c r="H48" s="312"/>
       <c r="I48" s="305"/>
       <c r="J48" s="305"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1">
       <c r="A49" s="312"/>
-      <c r="B49" s="304"/>
-      <c r="C49" s="380" t="s">
-        <v>961</v>
-      </c>
-      <c r="D49" s="381" t="s">
-        <v>962</v>
-      </c>
-      <c r="E49" s="382" t="s">
-        <v>963</v>
-      </c>
-      <c r="F49" s="383"/>
+      <c r="B49" s="304" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="312"/>
+      <c r="D49" s="312"/>
+      <c r="E49" s="312"/>
+      <c r="F49" s="368"/>
+      <c r="G49" s="312"/>
       <c r="H49" s="312"/>
       <c r="I49" s="305"/>
       <c r="J49" s="305"/>
@@ -18009,14 +18090,16 @@
     <row r="50" spans="1:10" ht="15.75" customHeight="1">
       <c r="A50" s="312"/>
       <c r="B50" s="304"/>
-      <c r="C50" s="384"/>
-      <c r="D50" s="385" t="s">
-        <v>964</v>
-      </c>
-      <c r="E50" s="386" t="s">
-        <v>965</v>
-      </c>
-      <c r="F50" s="387"/>
+      <c r="C50" s="375" t="s">
+        <v>732</v>
+      </c>
+      <c r="D50" s="369" t="s">
+        <v>734</v>
+      </c>
+      <c r="E50" s="369" t="s">
+        <v>736</v>
+      </c>
+      <c r="F50" s="376"/>
       <c r="H50" s="312"/>
       <c r="I50" s="305"/>
       <c r="J50" s="305"/>
@@ -18024,16 +18107,16 @@
     <row r="51" spans="1:10" ht="15.75" customHeight="1">
       <c r="A51" s="312"/>
       <c r="B51" s="304"/>
-      <c r="C51" s="380" t="s">
-        <v>966</v>
-      </c>
-      <c r="D51" s="381" t="s">
+      <c r="C51" s="377" t="s">
+        <v>960</v>
+      </c>
+      <c r="D51" s="378" t="s">
+        <v>961</v>
+      </c>
+      <c r="E51" s="379" t="s">
         <v>962</v>
       </c>
-      <c r="E51" s="382" t="s">
-        <v>963</v>
-      </c>
-      <c r="F51" s="383"/>
+      <c r="F51" s="380"/>
       <c r="H51" s="312"/>
       <c r="I51" s="305"/>
       <c r="J51" s="305"/>
@@ -18041,14 +18124,14 @@
     <row r="52" spans="1:10" ht="15.75" customHeight="1">
       <c r="A52" s="312"/>
       <c r="B52" s="304"/>
-      <c r="C52" s="384"/>
-      <c r="D52" s="385" t="s">
+      <c r="C52" s="381"/>
+      <c r="D52" s="382" t="s">
+        <v>963</v>
+      </c>
+      <c r="E52" s="383" t="s">
         <v>964</v>
       </c>
-      <c r="E52" s="386" t="s">
-        <v>965</v>
-      </c>
-      <c r="F52" s="387"/>
+      <c r="F52" s="384"/>
       <c r="H52" s="312"/>
       <c r="I52" s="305"/>
       <c r="J52" s="305"/>
@@ -18056,16 +18139,16 @@
     <row r="53" spans="1:10" ht="15.75" customHeight="1">
       <c r="A53" s="312"/>
       <c r="B53" s="304"/>
-      <c r="C53" s="388" t="s">
-        <v>967</v>
-      </c>
-      <c r="D53" s="385" t="s">
-        <v>968</v>
-      </c>
-      <c r="E53" s="389" t="s">
-        <v>969</v>
-      </c>
-      <c r="F53" s="387"/>
+      <c r="C53" s="377" t="s">
+        <v>965</v>
+      </c>
+      <c r="D53" s="378" t="s">
+        <v>961</v>
+      </c>
+      <c r="E53" s="379" t="s">
+        <v>962</v>
+      </c>
+      <c r="F53" s="380"/>
       <c r="H53" s="312"/>
       <c r="I53" s="305"/>
       <c r="J53" s="305"/>
@@ -18073,14 +18156,14 @@
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
       <c r="A54" s="312"/>
       <c r="B54" s="304"/>
-      <c r="C54" s="380"/>
-      <c r="D54" s="390" t="s">
-        <v>962</v>
-      </c>
-      <c r="E54" s="389" t="s">
-        <v>970</v>
-      </c>
-      <c r="F54" s="387"/>
+      <c r="C54" s="381"/>
+      <c r="D54" s="382" t="s">
+        <v>963</v>
+      </c>
+      <c r="E54" s="383" t="s">
+        <v>964</v>
+      </c>
+      <c r="F54" s="384"/>
       <c r="H54" s="312"/>
       <c r="I54" s="305"/>
       <c r="J54" s="305"/>
@@ -18088,14 +18171,16 @@
     <row r="55" spans="1:10" ht="15.75" customHeight="1">
       <c r="A55" s="312"/>
       <c r="B55" s="304"/>
-      <c r="C55" s="391"/>
-      <c r="D55" s="385" t="s">
-        <v>964</v>
-      </c>
-      <c r="E55" s="392" t="s">
-        <v>971</v>
-      </c>
-      <c r="F55" s="387"/>
+      <c r="C55" s="385" t="s">
+        <v>966</v>
+      </c>
+      <c r="D55" s="382" t="s">
+        <v>967</v>
+      </c>
+      <c r="E55" s="386" t="s">
+        <v>968</v>
+      </c>
+      <c r="F55" s="384"/>
       <c r="H55" s="312"/>
       <c r="I55" s="305"/>
       <c r="J55" s="305"/>
@@ -18103,16 +18188,14 @@
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
       <c r="A56" s="312"/>
       <c r="B56" s="304"/>
-      <c r="C56" s="388" t="s">
-        <v>972</v>
-      </c>
-      <c r="D56" s="381" t="s">
-        <v>973</v>
-      </c>
-      <c r="E56" s="389" t="s">
-        <v>974</v>
-      </c>
-      <c r="F56" s="387"/>
+      <c r="C56" s="377"/>
+      <c r="D56" s="387" t="s">
+        <v>961</v>
+      </c>
+      <c r="E56" s="386" t="s">
+        <v>969</v>
+      </c>
+      <c r="F56" s="384"/>
       <c r="H56" s="312"/>
       <c r="I56" s="305"/>
       <c r="J56" s="305"/>
@@ -18120,14 +18203,14 @@
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
       <c r="A57" s="312"/>
       <c r="B57" s="304"/>
-      <c r="C57" s="380"/>
-      <c r="D57" s="390" t="s">
-        <v>975</v>
-      </c>
-      <c r="E57" s="392" t="s">
-        <v>976</v>
-      </c>
-      <c r="F57" s="387"/>
+      <c r="C57" s="388"/>
+      <c r="D57" s="382" t="s">
+        <v>963</v>
+      </c>
+      <c r="E57" s="389" t="s">
+        <v>970</v>
+      </c>
+      <c r="F57" s="384"/>
       <c r="H57" s="312"/>
       <c r="I57" s="305"/>
       <c r="J57" s="305"/>
@@ -18135,14 +18218,16 @@
     <row r="58" spans="1:10" ht="15.75" customHeight="1">
       <c r="A58" s="312"/>
       <c r="B58" s="304"/>
-      <c r="C58" s="380"/>
-      <c r="D58" s="381" t="s">
-        <v>977</v>
-      </c>
-      <c r="E58" s="380" t="s">
-        <v>978</v>
-      </c>
-      <c r="F58" s="387"/>
+      <c r="C58" s="385" t="s">
+        <v>971</v>
+      </c>
+      <c r="D58" s="378" t="s">
+        <v>972</v>
+      </c>
+      <c r="E58" s="386" t="s">
+        <v>973</v>
+      </c>
+      <c r="F58" s="384"/>
       <c r="H58" s="312"/>
       <c r="I58" s="305"/>
       <c r="J58" s="305"/>
@@ -18150,14 +18235,14 @@
     <row r="59" spans="1:10" ht="15.75" customHeight="1">
       <c r="A59" s="312"/>
       <c r="B59" s="304"/>
-      <c r="C59" s="380"/>
-      <c r="D59" s="381" t="s">
-        <v>979</v>
-      </c>
-      <c r="E59" s="390" t="s">
-        <v>980</v>
-      </c>
-      <c r="F59" s="387"/>
+      <c r="C59" s="377"/>
+      <c r="D59" s="387" t="s">
+        <v>974</v>
+      </c>
+      <c r="E59" s="389" t="s">
+        <v>975</v>
+      </c>
+      <c r="F59" s="384"/>
       <c r="H59" s="312"/>
       <c r="I59" s="305"/>
       <c r="J59" s="305"/>
@@ -18165,14 +18250,14 @@
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="312"/>
       <c r="B60" s="304"/>
-      <c r="C60" s="384"/>
-      <c r="D60" s="381" t="s">
-        <v>717</v>
-      </c>
-      <c r="E60" s="389" t="s">
-        <v>981</v>
-      </c>
-      <c r="F60" s="383"/>
+      <c r="C60" s="377"/>
+      <c r="D60" s="378" t="s">
+        <v>976</v>
+      </c>
+      <c r="E60" s="377" t="s">
+        <v>977</v>
+      </c>
+      <c r="F60" s="384"/>
       <c r="H60" s="312"/>
       <c r="I60" s="305"/>
       <c r="J60" s="305"/>
@@ -18180,16 +18265,14 @@
     <row r="61" spans="1:10" ht="15.75" customHeight="1">
       <c r="A61" s="312"/>
       <c r="B61" s="304"/>
-      <c r="C61" s="388" t="s">
-        <v>982</v>
-      </c>
-      <c r="D61" s="393" t="s">
-        <v>983</v>
-      </c>
-      <c r="E61" s="394" t="s">
-        <v>984</v>
-      </c>
-      <c r="F61" s="387"/>
+      <c r="C61" s="377"/>
+      <c r="D61" s="378" t="s">
+        <v>978</v>
+      </c>
+      <c r="E61" s="387" t="s">
+        <v>979</v>
+      </c>
+      <c r="F61" s="384"/>
       <c r="H61" s="312"/>
       <c r="I61" s="305"/>
       <c r="J61" s="305"/>
@@ -18197,14 +18280,14 @@
     <row r="62" spans="1:10" ht="15.75" customHeight="1">
       <c r="A62" s="312"/>
       <c r="B62" s="304"/>
-      <c r="C62" s="380"/>
-      <c r="D62" s="385" t="s">
-        <v>985</v>
-      </c>
-      <c r="E62" s="395" t="s">
-        <v>986</v>
-      </c>
-      <c r="F62" s="387"/>
+      <c r="C62" s="381"/>
+      <c r="D62" s="378" t="s">
+        <v>716</v>
+      </c>
+      <c r="E62" s="386" t="s">
+        <v>980</v>
+      </c>
+      <c r="F62" s="380"/>
       <c r="H62" s="312"/>
       <c r="I62" s="305"/>
       <c r="J62" s="305"/>
@@ -18212,14 +18295,16 @@
     <row r="63" spans="1:10" ht="15.75" customHeight="1">
       <c r="A63" s="312"/>
       <c r="B63" s="304"/>
-      <c r="C63" s="396"/>
-      <c r="D63" s="397" t="s">
-        <v>987</v>
-      </c>
-      <c r="E63" s="398" t="s">
-        <v>978</v>
-      </c>
-      <c r="F63" s="387"/>
+      <c r="C63" s="385" t="s">
+        <v>981</v>
+      </c>
+      <c r="D63" s="390" t="s">
+        <v>982</v>
+      </c>
+      <c r="E63" s="391" t="s">
+        <v>983</v>
+      </c>
+      <c r="F63" s="384"/>
       <c r="H63" s="312"/>
       <c r="I63" s="305"/>
       <c r="J63" s="305"/>
@@ -18227,14 +18312,14 @@
     <row r="64" spans="1:10" ht="15.75" customHeight="1">
       <c r="A64" s="312"/>
       <c r="B64" s="304"/>
-      <c r="C64" s="399"/>
-      <c r="D64" s="385" t="s">
-        <v>988</v>
-      </c>
-      <c r="E64" s="400" t="s">
-        <v>980</v>
-      </c>
-      <c r="F64" s="387"/>
+      <c r="C64" s="377"/>
+      <c r="D64" s="382" t="s">
+        <v>984</v>
+      </c>
+      <c r="E64" s="392" t="s">
+        <v>985</v>
+      </c>
+      <c r="F64" s="384"/>
       <c r="H64" s="312"/>
       <c r="I64" s="305"/>
       <c r="J64" s="305"/>
@@ -18242,14 +18327,14 @@
     <row r="65" spans="1:10" ht="15.75" customHeight="1">
       <c r="A65" s="312"/>
       <c r="B65" s="304"/>
-      <c r="C65" s="401"/>
-      <c r="D65" s="381" t="s">
-        <v>717</v>
-      </c>
-      <c r="E65" s="381" t="s">
-        <v>981</v>
-      </c>
-      <c r="F65" s="402"/>
+      <c r="C65" s="393"/>
+      <c r="D65" s="394" t="s">
+        <v>986</v>
+      </c>
+      <c r="E65" s="395" t="s">
+        <v>977</v>
+      </c>
+      <c r="F65" s="384"/>
       <c r="H65" s="312"/>
       <c r="I65" s="305"/>
       <c r="J65" s="305"/>
@@ -18257,16 +18342,14 @@
     <row r="66" spans="1:10" ht="15.75" customHeight="1">
       <c r="A66" s="312"/>
       <c r="B66" s="304"/>
-      <c r="C66" s="403" t="s">
-        <v>989</v>
-      </c>
-      <c r="D66" s="404" t="s">
-        <v>990</v>
-      </c>
-      <c r="E66" s="404" t="s">
-        <v>991</v>
-      </c>
-      <c r="F66" s="402"/>
+      <c r="C66" s="396"/>
+      <c r="D66" s="382" t="s">
+        <v>987</v>
+      </c>
+      <c r="E66" s="397" t="s">
+        <v>979</v>
+      </c>
+      <c r="F66" s="384"/>
       <c r="H66" s="312"/>
       <c r="I66" s="305"/>
       <c r="J66" s="305"/>
@@ -18274,14 +18357,14 @@
     <row r="67" spans="1:10" ht="15.75" customHeight="1">
       <c r="A67" s="312"/>
       <c r="B67" s="304"/>
-      <c r="C67" s="399"/>
-      <c r="D67" s="404" t="s">
-        <v>992</v>
-      </c>
-      <c r="E67" s="404" t="s">
-        <v>993</v>
-      </c>
-      <c r="F67" s="402"/>
+      <c r="C67" s="398"/>
+      <c r="D67" s="378" t="s">
+        <v>716</v>
+      </c>
+      <c r="E67" s="378" t="s">
+        <v>980</v>
+      </c>
+      <c r="F67" s="399"/>
       <c r="H67" s="312"/>
       <c r="I67" s="305"/>
       <c r="J67" s="305"/>
@@ -18289,14 +18372,16 @@
     <row r="68" spans="1:10" ht="15.75" customHeight="1">
       <c r="A68" s="312"/>
       <c r="B68" s="304"/>
-      <c r="C68" s="399"/>
-      <c r="D68" s="404" t="s">
-        <v>994</v>
-      </c>
-      <c r="E68" s="404" t="s">
-        <v>995</v>
-      </c>
-      <c r="F68" s="402"/>
+      <c r="C68" s="400" t="s">
+        <v>988</v>
+      </c>
+      <c r="D68" s="401" t="s">
+        <v>989</v>
+      </c>
+      <c r="E68" s="401" t="s">
+        <v>990</v>
+      </c>
+      <c r="F68" s="399"/>
       <c r="H68" s="312"/>
       <c r="I68" s="305"/>
       <c r="J68" s="305"/>
@@ -18304,14 +18389,14 @@
     <row r="69" spans="1:10" ht="15.75" customHeight="1">
       <c r="A69" s="312"/>
       <c r="B69" s="304"/>
-      <c r="C69" s="399"/>
-      <c r="D69" s="404" t="s">
-        <v>996</v>
-      </c>
-      <c r="E69" s="404" t="s">
+      <c r="C69" s="396"/>
+      <c r="D69" s="401" t="s">
         <v>991</v>
       </c>
-      <c r="F69" s="402"/>
+      <c r="E69" s="401" t="s">
+        <v>992</v>
+      </c>
+      <c r="F69" s="399"/>
       <c r="H69" s="312"/>
       <c r="I69" s="305"/>
       <c r="J69" s="305"/>
@@ -18319,99 +18404,129 @@
     <row r="70" spans="1:10" ht="15.75" customHeight="1">
       <c r="A70" s="312"/>
       <c r="B70" s="304"/>
-      <c r="C70" s="399"/>
-      <c r="D70" s="405" t="s">
-        <v>997</v>
-      </c>
-      <c r="E70" s="405" t="s">
-        <v>998</v>
-      </c>
-      <c r="F70" s="402"/>
+      <c r="C70" s="396"/>
+      <c r="D70" s="401" t="s">
+        <v>993</v>
+      </c>
+      <c r="E70" s="401" t="s">
+        <v>994</v>
+      </c>
+      <c r="F70" s="399"/>
       <c r="H70" s="312"/>
       <c r="I70" s="305"/>
       <c r="J70" s="305"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A71" s="305"/>
-      <c r="B71" s="305"/>
-      <c r="C71" s="406" t="s">
-        <v>999</v>
-      </c>
-      <c r="D71" s="407" t="s">
-        <v>992</v>
-      </c>
-      <c r="E71" s="408" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F71" s="402"/>
-      <c r="G71" s="305"/>
-      <c r="H71" s="305"/>
+      <c r="A71" s="312"/>
+      <c r="B71" s="304"/>
+      <c r="C71" s="396"/>
+      <c r="D71" s="401" t="s">
+        <v>995</v>
+      </c>
+      <c r="E71" s="401" t="s">
+        <v>990</v>
+      </c>
+      <c r="F71" s="399"/>
+      <c r="H71" s="312"/>
       <c r="I71" s="305"/>
       <c r="J71" s="305"/>
     </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1">
-      <c r="C72" s="409"/>
-      <c r="D72" s="410" t="s">
+    <row r="72" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A72" s="312"/>
+      <c r="B72" s="304"/>
+      <c r="C72" s="396"/>
+      <c r="D72" s="402" t="s">
+        <v>996</v>
+      </c>
+      <c r="E72" s="402" t="s">
+        <v>997</v>
+      </c>
+      <c r="F72" s="399"/>
+      <c r="H72" s="312"/>
+      <c r="I72" s="305"/>
+      <c r="J72" s="305"/>
+    </row>
+    <row r="73" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A73" s="305"/>
+      <c r="B73" s="305"/>
+      <c r="C73" s="403" t="s">
+        <v>998</v>
+      </c>
+      <c r="D73" s="404" t="s">
+        <v>991</v>
+      </c>
+      <c r="E73" s="405" t="s">
+        <v>999</v>
+      </c>
+      <c r="F73" s="399"/>
+      <c r="G73" s="305"/>
+      <c r="H73" s="305"/>
+      <c r="I73" s="305"/>
+      <c r="J73" s="305"/>
+    </row>
+    <row r="74" spans="1:10" ht="15" customHeight="1">
+      <c r="C74" s="406"/>
+      <c r="D74" s="407" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E74" s="408" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="15" customHeight="1">
+      <c r="C75" s="406"/>
+      <c r="D75" s="407" t="s">
         <v>1001</v>
       </c>
-      <c r="E72" s="411" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1">
-      <c r="C73" s="409"/>
-      <c r="D73" s="410" t="s">
+      <c r="E75" s="408" t="s">
         <v>1002</v>
-      </c>
-      <c r="E73" s="411" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1">
-      <c r="C74" s="412"/>
-      <c r="D74" s="410" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E74" s="408" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1">
-      <c r="C75" s="406" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D75" s="407" t="s">
-        <v>992</v>
-      </c>
-      <c r="E75" s="408" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1">
       <c r="C76" s="409"/>
-      <c r="D76" s="410" t="s">
+      <c r="D76" s="407" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E76" s="405" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15" customHeight="1">
+      <c r="C77" s="403" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D77" s="404" t="s">
+        <v>991</v>
+      </c>
+      <c r="E77" s="405" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15" customHeight="1">
+      <c r="C78" s="406"/>
+      <c r="D78" s="407" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E78" s="408" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="15" customHeight="1">
+      <c r="C79" s="406"/>
+      <c r="D79" s="407" t="s">
         <v>1001</v>
       </c>
-      <c r="E76" s="411" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1">
-      <c r="C77" s="409"/>
-      <c r="D77" s="410" t="s">
+      <c r="E79" s="408" t="s">
         <v>1002</v>
       </c>
-      <c r="E77" s="411" t="s">
+    </row>
+    <row r="80" spans="1:10" ht="15" customHeight="1">
+      <c r="C80" s="409"/>
+      <c r="D80" s="407" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1">
-      <c r="C78" s="412"/>
-      <c r="D78" s="410" t="s">
+      <c r="E80" s="405" t="s">
         <v>1004</v>
-      </c>
-      <c r="E78" s="408" t="s">
-        <v>1005</v>
       </c>
     </row>
   </sheetData>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1AA5C0-11B8-B74A-A77B-B4746B60B74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9056FD1-7624-5E4A-A15B-515B1C7FE24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ターム内容" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1059">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -4399,29 +4399,11 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>Admin.php</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>管理者用テーブル</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャユーズ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t xml:space="preserve">ヨウ </t>
-    </rPh>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>AttendanceRecord.php</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
     <t>勤怠情報用テーブル</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>Break.php</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -4443,10 +4425,6 @@
     <rPh sb="0" eb="5">
       <t>シュウセイ</t>
     </rPh>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>Newbreak.php</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -5096,10 +5074,6 @@
     <t>varchar(100)</t>
   </si>
   <si>
-    <t>adminsテーブル</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>attendance_recordsテーブル</t>
     <phoneticPr fontId="80"/>
   </si>
@@ -5129,10 +5103,6 @@
   </si>
   <si>
     <t>user_id, date</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>breaksテーブル</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -5235,8 +5205,193 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
+    <t>application_id</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>applications.id</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>new_break_in</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>new_break_out</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>メール認証誘導画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>redirect</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>一般ユーザーのログイン時、メール認証を誘導する画面</t>
+    <rPh sb="0" eb="2">
+      <t>イッパンユ-</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガメn</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>会員登録画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>勤怠一覧画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>勤怠詳細画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>申請一覧画面（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>ログイン画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>勤怠一覧画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>勤怠詳細画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>スタッフ一覧画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>スタッフ別勤怠一覧画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>申請一覧画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>修正申請承認画面（管理者）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>verify-email.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>break_timesテーブル</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>BreakTime.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>admin_status</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>boolean</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
     <r>
-      <t>newbreaks</t>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>デフォルト：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>false</t>
+    </r>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>attendance_status</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>選択肢：「勤務外」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>デフォルト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>, 「出勤中」, 「休憩中」,「退勤済」</t>
+    </r>
+    <rPh sb="0" eb="3">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>application_date</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <t>proposal_breaks</t>
     </r>
     <r>
       <rPr>
@@ -5252,88 +5407,7 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>application_id</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>applications.id</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>new_break_in</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>new_break_out</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>メール認証誘導画面（一般ユーザー）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>redirect</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>一般ユーザーのログイン時、メール認証を誘導する画面</t>
-    <rPh sb="0" eb="2">
-      <t>イッパンユ-</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ユウドウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ガメn</t>
-    </rPh>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>会員登録画面（一般ユーザー）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>勤怠一覧画面（一般ユーザー）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>勤怠詳細画面（一般ユーザー）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>申請一覧画面（一般ユーザー）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>ログイン画面（管理者）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>勤怠一覧画面（管理者）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>勤怠詳細画面（管理者）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>スタッフ一覧画面（管理者）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>スタッフ別勤怠一覧画面（管理者）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>申請一覧画面（管理者）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>修正申請承認画面（管理者）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>verify-email.blade.php</t>
+    <t>ProposalBreak.php</t>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -5956,7 +6030,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6045,6 +6119,24 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FFCFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -7005,7 +7097,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="470">
+  <cellXfs count="472">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8015,7 +8107,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -8128,7 +8219,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="63" fillId="13" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -8155,6 +8245,22 @@
     <xf numFmtId="0" fontId="63" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="85" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="2" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8190,20 +8296,8 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="85" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="2" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="2" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -8297,63 +8391,25 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="133350" cy="200025"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image1.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{525D372D-6CD5-6C46-A440-B6292532340D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7861300" y="1943100"/>
-          <a:ext cx="133350" cy="200025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>407797</xdr:colOff>
+      <xdr:colOff>512658</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>139816</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>6571376</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>94177</xdr:rowOff>
+      <xdr:colOff>5487797</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>184961</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D56158-9E33-E34A-AB78-6B457E2F1901}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5081EB4E-F90D-CAD1-BCD5-A940EEFEDF6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8362,15 +8418,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8269097" y="1320916"/>
-          <a:ext cx="6163579" cy="9263461"/>
+          <a:off x="8377337" y="1304954"/>
+          <a:ext cx="4975139" cy="10158539"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8719,7 +8775,7 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="2.1640625" style="306" customWidth="1"/>
@@ -8763,7 +8819,7 @@
     <row r="3" spans="1:12" ht="36.75" customHeight="1">
       <c r="A3" s="303"/>
       <c r="B3" s="303"/>
-      <c r="C3" s="410" t="s">
+      <c r="C3" s="409" t="s">
         <v>654</v>
       </c>
       <c r="D3" s="305"/>
@@ -8778,1502 +8834,1414 @@
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
       <c r="A4" s="303"/>
       <c r="B4" s="303"/>
-      <c r="C4" s="375" t="s">
+      <c r="C4" s="374" t="s">
         <v>659</v>
       </c>
-      <c r="D4" s="411"/>
-      <c r="E4" s="412"/>
-      <c r="F4" s="412"/>
-      <c r="G4" s="412"/>
-      <c r="H4" s="412"/>
-      <c r="I4" s="412"/>
-      <c r="J4" s="412"/>
-      <c r="K4" s="412"/>
+      <c r="D4" s="410"/>
+      <c r="E4" s="411"/>
+      <c r="F4" s="411"/>
+      <c r="G4" s="411"/>
+      <c r="H4" s="411"/>
+      <c r="I4" s="411"/>
+      <c r="J4" s="411"/>
+      <c r="K4" s="411"/>
       <c r="L4" s="305"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="303"/>
       <c r="B5" s="303"/>
-      <c r="C5" s="413" t="s">
+      <c r="C5" s="412" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="414" t="s">
+      <c r="D5" s="413" t="s">
         <v>671</v>
       </c>
-      <c r="E5" s="415" t="s">
+      <c r="E5" s="414" t="s">
         <v>675</v>
       </c>
-      <c r="F5" s="415" t="s">
+      <c r="F5" s="414" t="s">
         <v>438</v>
       </c>
-      <c r="G5" s="415" t="s">
+      <c r="G5" s="414" t="s">
         <v>676</v>
       </c>
-      <c r="H5" s="415" t="s">
+      <c r="H5" s="414" t="s">
         <v>677</v>
       </c>
-      <c r="I5" s="415" t="s">
+      <c r="I5" s="414" t="s">
         <v>678</v>
       </c>
-      <c r="J5" s="415" t="s">
+      <c r="J5" s="414" t="s">
         <v>679</v>
       </c>
-      <c r="K5" s="416" t="s">
+      <c r="K5" s="415" t="s">
         <v>681</v>
       </c>
       <c r="L5" s="305"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="368"/>
-      <c r="B6" s="368"/>
-      <c r="C6" s="417">
+      <c r="A6" s="367"/>
+      <c r="B6" s="367"/>
+      <c r="C6" s="416">
         <v>1</v>
       </c>
-      <c r="D6" s="418" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E6" s="419"/>
-      <c r="F6" s="419"/>
-      <c r="G6" s="419"/>
-      <c r="H6" s="419"/>
-      <c r="I6" s="419"/>
-      <c r="J6" s="420"/>
-      <c r="K6" s="421"/>
+      <c r="D6" s="417" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E6" s="418"/>
+      <c r="F6" s="418"/>
+      <c r="G6" s="418"/>
+      <c r="H6" s="418"/>
+      <c r="I6" s="418"/>
+      <c r="J6" s="419"/>
+      <c r="K6" s="420"/>
       <c r="L6" s="305"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="303"/>
       <c r="B7" s="303"/>
-      <c r="C7" s="422"/>
-      <c r="E7" s="395" t="s">
+      <c r="C7" s="421"/>
+      <c r="E7" s="394" t="s">
         <v>701</v>
       </c>
-      <c r="F7" s="423" t="s">
+      <c r="F7" s="422" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G7" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="H7" s="394"/>
+      <c r="I7" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J7" s="423"/>
+      <c r="K7" s="420"/>
+      <c r="L7" s="305"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A8" s="375"/>
+      <c r="B8" s="375"/>
+      <c r="C8" s="424"/>
+      <c r="D8" s="304"/>
+      <c r="E8" s="394" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F8" s="394" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G8" s="394"/>
+      <c r="H8" s="394"/>
+      <c r="I8" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J8" s="423"/>
+      <c r="K8" s="420"/>
+      <c r="L8" s="305"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A9" s="367"/>
+      <c r="B9" s="367"/>
+      <c r="C9" s="421"/>
+      <c r="E9" s="394" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F9" s="394" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G9" s="394"/>
+      <c r="H9" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="I9" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J9" s="423"/>
+      <c r="K9" s="425" t="s">
+        <v>764</v>
+      </c>
+      <c r="L9" s="305"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A10" s="367"/>
+      <c r="B10" s="367"/>
+      <c r="C10" s="421"/>
+      <c r="E10" s="394" t="s">
         <v>1008</v>
       </c>
-      <c r="G7" s="423" t="s">
+      <c r="F10" s="394" t="s">
+        <v>731</v>
+      </c>
+      <c r="G10" s="394"/>
+      <c r="H10" s="394"/>
+      <c r="I10" s="422"/>
+      <c r="J10" s="423"/>
+      <c r="K10" s="420"/>
+      <c r="L10" s="305"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A11" s="367"/>
+      <c r="B11" s="367"/>
+      <c r="C11" s="421"/>
+      <c r="E11" s="394" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F11" s="394" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G11" s="394"/>
+      <c r="H11" s="394"/>
+      <c r="I11" s="422" t="s">
         <v>710</v>
       </c>
-      <c r="H7" s="395"/>
-      <c r="I7" s="423" t="s">
+      <c r="J11" s="423"/>
+      <c r="K11" s="420"/>
+      <c r="L11" s="305"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A12" s="367"/>
+      <c r="B12" s="367"/>
+      <c r="C12" s="421"/>
+      <c r="E12" s="394" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F12" s="394" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G12" s="394"/>
+      <c r="H12" s="394"/>
+      <c r="I12" s="394"/>
+      <c r="J12" s="423"/>
+      <c r="K12" s="420"/>
+      <c r="L12" s="305"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A13" s="367"/>
+      <c r="B13" s="367"/>
+      <c r="C13" s="421"/>
+      <c r="D13" s="440" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E13" s="451" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F13" s="451" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G13" s="394"/>
+      <c r="H13" s="394"/>
+      <c r="I13" s="452" t="s">
         <v>710</v>
       </c>
-      <c r="J7" s="424"/>
-      <c r="K7" s="421"/>
-      <c r="L7" s="305"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="376"/>
-      <c r="B8" s="376"/>
-      <c r="C8" s="425"/>
-      <c r="D8" s="304"/>
-      <c r="E8" s="395" t="s">
-        <v>1009</v>
-      </c>
-      <c r="F8" s="395" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G8" s="395"/>
-      <c r="H8" s="395"/>
-      <c r="I8" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J8" s="424"/>
-      <c r="K8" s="421"/>
-      <c r="L8" s="305"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="368"/>
-      <c r="B9" s="368"/>
-      <c r="C9" s="422"/>
-      <c r="E9" s="395" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F9" s="395" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G9" s="395"/>
-      <c r="H9" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="I9" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J9" s="424"/>
-      <c r="K9" s="426" t="s">
-        <v>764</v>
-      </c>
-      <c r="L9" s="305"/>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="368"/>
-      <c r="B10" s="368"/>
-      <c r="C10" s="422"/>
-      <c r="E10" s="395" t="s">
+      <c r="J13" s="423"/>
+      <c r="K13" s="420"/>
+      <c r="L13" s="305"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A14" s="367"/>
+      <c r="B14" s="367"/>
+      <c r="C14" s="421"/>
+      <c r="D14" s="440" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E14" s="394" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F14" s="394" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G14" s="394"/>
+      <c r="H14" s="394"/>
+      <c r="I14" s="394"/>
+      <c r="J14" s="423"/>
+      <c r="K14" s="420"/>
+      <c r="L14" s="305"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A15" s="367"/>
+      <c r="B15" s="367"/>
+      <c r="C15" s="421"/>
+      <c r="E15" s="394" t="s">
+        <v>730</v>
+      </c>
+      <c r="F15" s="394" t="s">
+        <v>731</v>
+      </c>
+      <c r="G15" s="394"/>
+      <c r="H15" s="394"/>
+      <c r="I15" s="394"/>
+      <c r="J15" s="423"/>
+      <c r="K15" s="420"/>
+      <c r="L15" s="305"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A16" s="367"/>
+      <c r="B16" s="367"/>
+      <c r="C16" s="421"/>
+      <c r="E16" s="394" t="s">
+        <v>739</v>
+      </c>
+      <c r="F16" s="394" t="s">
+        <v>731</v>
+      </c>
+      <c r="G16" s="394"/>
+      <c r="H16" s="394"/>
+      <c r="I16" s="394"/>
+      <c r="J16" s="423"/>
+      <c r="K16" s="420"/>
+      <c r="L16" s="305"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A17" s="398"/>
+      <c r="B17" s="398"/>
+      <c r="C17" s="428">
+        <v>2</v>
+      </c>
+      <c r="D17" s="426" t="s">
         <v>1012</v>
       </c>
-      <c r="F10" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G10" s="395"/>
-      <c r="H10" s="395"/>
-      <c r="I10" s="423"/>
-      <c r="J10" s="424"/>
-      <c r="K10" s="421"/>
-      <c r="L10" s="305"/>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="368"/>
-      <c r="B11" s="368"/>
-      <c r="C11" s="422"/>
-      <c r="E11" s="395" t="s">
+      <c r="E17" s="418"/>
+      <c r="F17" s="418"/>
+      <c r="G17" s="418"/>
+      <c r="H17" s="418"/>
+      <c r="I17" s="418"/>
+      <c r="J17" s="419"/>
+      <c r="K17" s="305"/>
+      <c r="L17" s="305"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A18" s="398"/>
+      <c r="B18" s="398"/>
+      <c r="C18" s="427"/>
+      <c r="E18" s="394" t="s">
         <v>1013</v>
       </c>
-      <c r="F11" s="395" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G11" s="395"/>
-      <c r="H11" s="395"/>
-      <c r="I11" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J11" s="424"/>
-      <c r="K11" s="421"/>
-      <c r="L11" s="305"/>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="368"/>
-      <c r="B12" s="368"/>
-      <c r="C12" s="422"/>
-      <c r="E12" s="395" t="s">
+      <c r="F18" s="363" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G18" s="422" t="s">
+        <v>905</v>
+      </c>
+      <c r="H18" s="394"/>
+      <c r="I18" s="422" t="s">
+        <v>905</v>
+      </c>
+      <c r="J18" s="423"/>
+      <c r="K18" s="305"/>
+      <c r="L18" s="305"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A19" s="398"/>
+      <c r="B19" s="398"/>
+      <c r="C19" s="427"/>
+      <c r="D19" s="312" t="s">
         <v>1014</v>
       </c>
-      <c r="F12" s="395" t="s">
+      <c r="E19" s="394" t="s">
+        <v>985</v>
+      </c>
+      <c r="F19" s="363" t="s">
         <v>1015</v>
       </c>
-      <c r="G12" s="395"/>
-      <c r="H12" s="395"/>
-      <c r="I12" s="395"/>
-      <c r="J12" s="424"/>
-      <c r="K12" s="421"/>
-      <c r="L12" s="305"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" s="368"/>
-      <c r="B13" s="368"/>
-      <c r="C13" s="422"/>
-      <c r="E13" s="395" t="s">
-        <v>730</v>
-      </c>
-      <c r="F13" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G13" s="395"/>
-      <c r="H13" s="395"/>
-      <c r="I13" s="395"/>
-      <c r="J13" s="424"/>
-      <c r="K13" s="421"/>
-      <c r="L13" s="305"/>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A14" s="368"/>
-      <c r="B14" s="368"/>
-      <c r="C14" s="422"/>
-      <c r="E14" s="395" t="s">
-        <v>739</v>
-      </c>
-      <c r="F14" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G14" s="395"/>
-      <c r="H14" s="395"/>
-      <c r="I14" s="395"/>
-      <c r="J14" s="424"/>
-      <c r="K14" s="421"/>
-      <c r="L14" s="305"/>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="368"/>
-      <c r="B15" s="368"/>
-      <c r="C15" s="417">
-        <v>2</v>
-      </c>
-      <c r="D15" s="427" t="s">
+      <c r="G19" s="422"/>
+      <c r="H19" s="394" t="s">
+        <v>905</v>
+      </c>
+      <c r="I19" s="422" t="s">
+        <v>905</v>
+      </c>
+      <c r="J19" s="423" t="s">
         <v>1016</v>
       </c>
-      <c r="E15" s="419"/>
-      <c r="F15" s="419"/>
-      <c r="G15" s="419"/>
-      <c r="H15" s="419"/>
-      <c r="I15" s="419"/>
-      <c r="J15" s="420"/>
-      <c r="K15" s="421"/>
-      <c r="L15" s="305"/>
-    </row>
-    <row r="16" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A16" s="368"/>
-      <c r="B16" s="368"/>
-      <c r="C16" s="422"/>
-      <c r="E16" s="395" t="s">
-        <v>701</v>
-      </c>
-      <c r="F16" s="363" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G16" s="423" t="s">
+      <c r="K19" s="305"/>
+      <c r="L19" s="305"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A20" s="398"/>
+      <c r="B20" s="398"/>
+      <c r="C20" s="427"/>
+      <c r="D20" s="312"/>
+      <c r="E20" s="394" t="s">
+        <v>987</v>
+      </c>
+      <c r="F20" s="363" t="s">
+        <v>987</v>
+      </c>
+      <c r="G20" s="422"/>
+      <c r="H20" s="394" t="s">
         <v>905</v>
       </c>
-      <c r="H16" s="395"/>
-      <c r="I16" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J16" s="424"/>
-      <c r="K16" s="421"/>
-      <c r="L16" s="305"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A17" s="368"/>
-      <c r="B17" s="368"/>
-      <c r="C17" s="422"/>
-      <c r="D17" s="304"/>
-      <c r="E17" s="395" t="s">
-        <v>1009</v>
-      </c>
-      <c r="F17" s="306" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G17" s="395"/>
-      <c r="H17" s="395"/>
-      <c r="I17" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J17" s="424"/>
-      <c r="K17" s="421"/>
-      <c r="L17" s="305"/>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A18" s="368"/>
-      <c r="B18" s="368"/>
-      <c r="C18" s="422"/>
-      <c r="E18" s="395" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F18" s="395" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G18" s="395"/>
-      <c r="H18" s="395" t="s">
+      <c r="I20" s="422"/>
+      <c r="J20" s="423"/>
+      <c r="K20" s="305"/>
+      <c r="L20" s="305"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A21" s="398"/>
+      <c r="B21" s="398"/>
+      <c r="C21" s="427"/>
+      <c r="D21" s="304"/>
+      <c r="E21" s="394" t="s">
+        <v>996</v>
+      </c>
+      <c r="F21" s="363" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G21" s="394"/>
+      <c r="H21" s="394"/>
+      <c r="I21" s="422" t="s">
         <v>905</v>
       </c>
-      <c r="I18" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J18" s="424"/>
-      <c r="K18" s="421"/>
-      <c r="L18" s="305"/>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A19" s="368"/>
-      <c r="B19" s="368"/>
-      <c r="C19" s="422"/>
-      <c r="E19" s="395" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F19" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G19" s="395"/>
-      <c r="H19" s="395"/>
-      <c r="I19" s="395"/>
-      <c r="J19" s="424"/>
-      <c r="K19" s="421"/>
-      <c r="L19" s="305"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A20" s="368"/>
-      <c r="B20" s="368"/>
-      <c r="C20" s="422"/>
-      <c r="E20" s="395" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F20" s="395" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G20" s="395"/>
-      <c r="H20" s="395"/>
-      <c r="I20" s="395" t="s">
-        <v>710</v>
-      </c>
-      <c r="J20" s="424"/>
-      <c r="K20" s="421"/>
-      <c r="L20" s="305"/>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A21" s="368"/>
-      <c r="B21" s="368"/>
-      <c r="C21" s="422"/>
-      <c r="E21" s="395" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F21" s="306" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G21" s="395"/>
-      <c r="H21" s="395"/>
-      <c r="I21" s="395"/>
-      <c r="J21" s="424"/>
-      <c r="K21" s="428"/>
+      <c r="J21" s="423"/>
+      <c r="K21" s="305"/>
       <c r="L21" s="305"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A22" s="399"/>
-      <c r="B22" s="399"/>
-      <c r="C22" s="429"/>
-      <c r="E22" s="395" t="s">
-        <v>730</v>
-      </c>
-      <c r="F22" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G22" s="395"/>
-      <c r="H22" s="395"/>
-      <c r="I22" s="395"/>
-      <c r="J22" s="424"/>
+      <c r="A22" s="398"/>
+      <c r="B22" s="398"/>
+      <c r="C22" s="427"/>
+      <c r="E22" s="394" t="s">
+        <v>997</v>
+      </c>
+      <c r="F22" s="363" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G22" s="394"/>
+      <c r="H22" s="394"/>
+      <c r="I22" s="422"/>
+      <c r="J22" s="423"/>
       <c r="K22" s="305"/>
       <c r="L22" s="305"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A23" s="399"/>
-      <c r="B23" s="399"/>
-      <c r="C23" s="429"/>
-      <c r="E23" s="395" t="s">
-        <v>739</v>
-      </c>
-      <c r="F23" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G23" s="395"/>
-      <c r="H23" s="395"/>
-      <c r="I23" s="395"/>
-      <c r="J23" s="424"/>
+      <c r="A23" s="398"/>
+      <c r="B23" s="398"/>
+      <c r="C23" s="427"/>
+      <c r="E23" s="451" t="s">
+        <v>999</v>
+      </c>
+      <c r="F23" s="451" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G23" s="394"/>
+      <c r="H23" s="394"/>
+      <c r="I23" s="422"/>
+      <c r="J23" s="423"/>
       <c r="K23" s="305"/>
       <c r="L23" s="305"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A24" s="399"/>
-      <c r="B24" s="399"/>
-      <c r="C24" s="430">
-        <v>3</v>
-      </c>
-      <c r="D24" s="427" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E24" s="419"/>
-      <c r="F24" s="419"/>
-      <c r="G24" s="419"/>
-      <c r="H24" s="419"/>
-      <c r="I24" s="419"/>
-      <c r="J24" s="420"/>
+      <c r="A24" s="398"/>
+      <c r="B24" s="398"/>
+      <c r="C24" s="427"/>
+      <c r="D24" s="429"/>
+      <c r="E24" s="430" t="s">
+        <v>730</v>
+      </c>
+      <c r="F24" s="430" t="s">
+        <v>731</v>
+      </c>
+      <c r="G24" s="430"/>
+      <c r="H24" s="430"/>
+      <c r="I24" s="430"/>
+      <c r="J24" s="431"/>
       <c r="K24" s="305"/>
       <c r="L24" s="305"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A25" s="399"/>
-      <c r="B25" s="399"/>
-      <c r="C25" s="429"/>
-      <c r="E25" s="395" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F25" s="363" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G25" s="423" t="s">
-        <v>905</v>
-      </c>
-      <c r="H25" s="395"/>
-      <c r="I25" s="423" t="s">
-        <v>905</v>
-      </c>
-      <c r="J25" s="424"/>
+      <c r="A25" s="398"/>
+      <c r="B25" s="398"/>
+      <c r="C25" s="427"/>
+      <c r="D25" s="432"/>
+      <c r="E25" s="430" t="s">
+        <v>739</v>
+      </c>
+      <c r="F25" s="430" t="s">
+        <v>731</v>
+      </c>
+      <c r="G25" s="430"/>
+      <c r="H25" s="430"/>
+      <c r="I25" s="430"/>
+      <c r="J25" s="431"/>
       <c r="K25" s="305"/>
       <c r="L25" s="305"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A26" s="399"/>
-      <c r="B26" s="399"/>
-      <c r="C26" s="429"/>
-      <c r="D26" s="312" t="s">
+      <c r="A26" s="398"/>
+      <c r="B26" s="398"/>
+      <c r="C26" s="427"/>
+      <c r="D26" s="433"/>
+      <c r="E26" s="434" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F26" s="435"/>
+      <c r="G26" s="436"/>
+      <c r="H26" s="435" t="s">
         <v>1019</v>
       </c>
-      <c r="E26" s="395" t="s">
-        <v>989</v>
-      </c>
-      <c r="F26" s="363" t="s">
-        <v>1020</v>
-      </c>
-      <c r="G26" s="423"/>
-      <c r="H26" s="395" t="s">
-        <v>905</v>
-      </c>
-      <c r="I26" s="423" t="s">
-        <v>905</v>
-      </c>
-      <c r="J26" s="424" t="s">
-        <v>1021</v>
-      </c>
+      <c r="I26" s="435"/>
+      <c r="J26" s="437"/>
       <c r="K26" s="305"/>
       <c r="L26" s="305"/>
     </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A27" s="399"/>
-      <c r="B27" s="399"/>
-      <c r="C27" s="429"/>
-      <c r="D27" s="312"/>
-      <c r="E27" s="395" t="s">
-        <v>991</v>
-      </c>
-      <c r="F27" s="363" t="s">
-        <v>991</v>
-      </c>
-      <c r="G27" s="423"/>
-      <c r="H27" s="395" t="s">
-        <v>905</v>
-      </c>
-      <c r="I27" s="423"/>
-      <c r="J27" s="424"/>
+    <row r="27" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A27" s="398"/>
+      <c r="B27" s="398"/>
+      <c r="C27" s="428">
+        <v>3</v>
+      </c>
+      <c r="D27" s="426" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E27" s="418"/>
+      <c r="F27" s="418"/>
+      <c r="G27" s="418"/>
+      <c r="H27" s="418"/>
+      <c r="I27" s="418"/>
+      <c r="J27" s="419"/>
       <c r="K27" s="305"/>
       <c r="L27" s="305"/>
     </row>
-    <row r="28" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A28" s="399"/>
-      <c r="B28" s="399"/>
-      <c r="C28" s="429"/>
-      <c r="D28" s="304"/>
-      <c r="E28" s="395" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F28" s="363" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G28" s="395"/>
-      <c r="H28" s="395"/>
-      <c r="I28" s="423" t="s">
-        <v>905</v>
-      </c>
-      <c r="J28" s="424"/>
+    <row r="28" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A28" s="398"/>
+      <c r="B28" s="398"/>
+      <c r="C28" s="427"/>
+      <c r="E28" s="394" t="s">
+        <v>701</v>
+      </c>
+      <c r="F28" s="394" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G28" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="H28" s="394"/>
+      <c r="I28" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J28" s="423"/>
       <c r="K28" s="305"/>
       <c r="L28" s="305"/>
     </row>
-    <row r="29" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A29" s="399"/>
-      <c r="B29" s="399"/>
-      <c r="C29" s="429"/>
-      <c r="E29" s="395" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F29" s="363" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G29" s="395"/>
-      <c r="H29" s="395"/>
-      <c r="I29" s="423"/>
-      <c r="J29" s="424"/>
+    <row r="29" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A29" s="398"/>
+      <c r="B29" s="398"/>
+      <c r="C29" s="427"/>
+      <c r="D29" s="312" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E29" s="394" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F29" s="394" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G29" s="422"/>
+      <c r="H29" s="394"/>
+      <c r="I29" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J29" s="423" t="s">
+        <v>1021</v>
+      </c>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
     </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A30" s="399"/>
-      <c r="B30" s="399"/>
-      <c r="C30" s="429"/>
-      <c r="D30" s="431"/>
-      <c r="E30" s="432" t="s">
-        <v>730</v>
-      </c>
-      <c r="F30" s="432" t="s">
-        <v>731</v>
-      </c>
-      <c r="G30" s="432"/>
-      <c r="H30" s="432"/>
-      <c r="I30" s="432"/>
-      <c r="J30" s="433"/>
+    <row r="30" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A30" s="398"/>
+      <c r="B30" s="398"/>
+      <c r="C30" s="427"/>
+      <c r="D30" s="304"/>
+      <c r="E30" s="394" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F30" s="394" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G30" s="394"/>
+      <c r="H30" s="394"/>
+      <c r="I30" s="422"/>
+      <c r="J30" s="438"/>
       <c r="K30" s="305"/>
       <c r="L30" s="305"/>
     </row>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A31" s="399"/>
-      <c r="B31" s="399"/>
-      <c r="C31" s="429"/>
-      <c r="D31" s="434"/>
-      <c r="E31" s="432" t="s">
-        <v>739</v>
-      </c>
-      <c r="F31" s="432" t="s">
-        <v>731</v>
-      </c>
-      <c r="G31" s="432"/>
-      <c r="H31" s="432"/>
-      <c r="I31" s="432"/>
-      <c r="J31" s="433"/>
+    <row r="31" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A31" s="398"/>
+      <c r="B31" s="398"/>
+      <c r="C31" s="427"/>
+      <c r="E31" s="394" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F31" s="394" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G31" s="394"/>
+      <c r="H31" s="394"/>
+      <c r="I31" s="422"/>
+      <c r="J31" s="423"/>
       <c r="K31" s="305"/>
       <c r="L31" s="305"/>
     </row>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A32" s="399"/>
-      <c r="B32" s="399"/>
-      <c r="C32" s="429"/>
-      <c r="D32" s="435"/>
-      <c r="E32" s="436" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F32" s="437"/>
-      <c r="G32" s="438"/>
-      <c r="H32" s="437" t="s">
-        <v>1024</v>
-      </c>
-      <c r="I32" s="437"/>
-      <c r="J32" s="439"/>
+    <row r="32" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A32" s="398"/>
+      <c r="B32" s="398"/>
+      <c r="C32" s="427"/>
+      <c r="E32" s="394" t="s">
+        <v>730</v>
+      </c>
+      <c r="F32" s="394" t="s">
+        <v>731</v>
+      </c>
+      <c r="G32" s="394"/>
+      <c r="H32" s="394"/>
+      <c r="I32" s="394"/>
+      <c r="J32" s="423"/>
       <c r="K32" s="305"/>
       <c r="L32" s="305"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A33" s="399"/>
-      <c r="B33" s="399"/>
-      <c r="C33" s="430">
-        <v>4</v>
-      </c>
-      <c r="D33" s="427" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E33" s="419"/>
-      <c r="F33" s="419"/>
-      <c r="G33" s="419"/>
-      <c r="H33" s="419"/>
-      <c r="I33" s="419"/>
-      <c r="J33" s="420"/>
+      <c r="A33" s="398"/>
+      <c r="B33" s="398"/>
+      <c r="C33" s="427"/>
+      <c r="E33" s="394" t="s">
+        <v>739</v>
+      </c>
+      <c r="F33" s="394" t="s">
+        <v>731</v>
+      </c>
+      <c r="G33" s="394"/>
+      <c r="H33" s="394"/>
+      <c r="I33" s="394"/>
+      <c r="J33" s="423"/>
       <c r="K33" s="305"/>
       <c r="L33" s="305"/>
     </row>
     <row r="34" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A34" s="399"/>
-      <c r="B34" s="399"/>
-      <c r="C34" s="429"/>
-      <c r="E34" s="395" t="s">
-        <v>701</v>
-      </c>
-      <c r="F34" s="395" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G34" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="H34" s="395"/>
-      <c r="I34" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J34" s="424"/>
+      <c r="A34" s="398"/>
+      <c r="B34" s="398"/>
+      <c r="C34" s="428">
+        <v>4</v>
+      </c>
+      <c r="D34" s="468" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E34" s="469"/>
+      <c r="F34" s="469"/>
+      <c r="G34" s="469"/>
+      <c r="H34" s="469"/>
+      <c r="I34" s="418"/>
+      <c r="J34" s="419"/>
       <c r="K34" s="305"/>
       <c r="L34" s="305"/>
     </row>
-    <row r="35" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A35" s="399"/>
-      <c r="B35" s="399"/>
-      <c r="C35" s="429"/>
-      <c r="D35" s="312" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E35" s="395" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F35" s="395" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G35" s="423"/>
-      <c r="H35" s="395"/>
-      <c r="I35" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J35" s="424" t="s">
-        <v>1027</v>
-      </c>
+    <row r="35" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A35" s="398"/>
+      <c r="B35" s="398"/>
+      <c r="C35" s="427"/>
+      <c r="E35" s="394" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F35" s="363" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G35" s="422" t="s">
+        <v>905</v>
+      </c>
+      <c r="H35" s="394"/>
+      <c r="I35" s="422" t="s">
+        <v>905</v>
+      </c>
+      <c r="J35" s="423"/>
       <c r="K35" s="305"/>
       <c r="L35" s="305"/>
     </row>
-    <row r="36" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A36" s="399"/>
-      <c r="B36" s="399"/>
-      <c r="C36" s="429"/>
-      <c r="D36" s="304"/>
-      <c r="E36" s="395" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F36" s="395" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G36" s="395"/>
-      <c r="H36" s="395"/>
-      <c r="I36" s="423"/>
-      <c r="J36" s="440"/>
+    <row r="36" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A36" s="398"/>
+      <c r="B36" s="398"/>
+      <c r="C36" s="427"/>
+      <c r="D36" s="306" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E36" s="394" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F36" s="363" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G36" s="422"/>
+      <c r="H36" s="394"/>
+      <c r="I36" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J36" s="423" t="s">
+        <v>1021</v>
+      </c>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
     </row>
-    <row r="37" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A37" s="399"/>
-      <c r="B37" s="399"/>
-      <c r="C37" s="429"/>
-      <c r="E37" s="395" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F37" s="395" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G37" s="395"/>
-      <c r="H37" s="395"/>
-      <c r="I37" s="423"/>
-      <c r="J37" s="424"/>
+    <row r="37" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A37" s="398"/>
+      <c r="B37" s="398"/>
+      <c r="C37" s="427"/>
+      <c r="E37" s="394" t="s">
+        <v>968</v>
+      </c>
+      <c r="F37" s="394" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G37" s="394"/>
+      <c r="H37" s="394"/>
+      <c r="I37" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J37" s="423"/>
       <c r="K37" s="305"/>
       <c r="L37" s="305"/>
     </row>
-    <row r="38" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A38" s="399"/>
-      <c r="B38" s="399"/>
-      <c r="C38" s="429"/>
-      <c r="E38" s="395" t="s">
-        <v>730</v>
-      </c>
-      <c r="F38" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G38" s="395"/>
-      <c r="H38" s="395"/>
-      <c r="I38" s="395"/>
-      <c r="J38" s="424"/>
+    <row r="38" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A38" s="398"/>
+      <c r="B38" s="398"/>
+      <c r="C38" s="427"/>
+      <c r="E38" s="394" t="s">
+        <v>970</v>
+      </c>
+      <c r="F38" s="439" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G38" s="394"/>
+      <c r="H38" s="394"/>
+      <c r="I38" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J38" s="423"/>
       <c r="K38" s="305"/>
       <c r="L38" s="305"/>
     </row>
     <row r="39" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A39" s="399"/>
-      <c r="B39" s="399"/>
-      <c r="C39" s="429"/>
-      <c r="E39" s="395" t="s">
-        <v>739</v>
-      </c>
-      <c r="F39" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G39" s="395"/>
-      <c r="H39" s="395"/>
-      <c r="I39" s="395"/>
-      <c r="J39" s="424"/>
+      <c r="A39" s="398"/>
+      <c r="B39" s="398"/>
+      <c r="C39" s="427"/>
+      <c r="E39" s="394" t="s">
+        <v>999</v>
+      </c>
+      <c r="F39" s="394" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G39" s="394"/>
+      <c r="H39" s="394"/>
+      <c r="I39" s="422" t="s">
+        <v>710</v>
+      </c>
+      <c r="J39" s="423"/>
       <c r="K39" s="305"/>
       <c r="L39" s="305"/>
     </row>
     <row r="40" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A40" s="399"/>
-      <c r="B40" s="399"/>
-      <c r="C40" s="430">
-        <v>5</v>
-      </c>
-      <c r="D40" s="462" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-      <c r="G40" s="463"/>
-      <c r="H40" s="463"/>
-      <c r="I40" s="419"/>
-      <c r="J40" s="420"/>
+      <c r="A40" s="398"/>
+      <c r="B40" s="398"/>
+      <c r="C40" s="427"/>
+      <c r="D40" s="440" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E40" s="394" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F40" s="394" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G40" s="394"/>
+      <c r="H40" s="394"/>
+      <c r="I40" s="394" t="s">
+        <v>905</v>
+      </c>
+      <c r="J40" s="423"/>
       <c r="K40" s="305"/>
       <c r="L40" s="305"/>
     </row>
-    <row r="41" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A41" s="399"/>
-      <c r="B41" s="399"/>
-      <c r="C41" s="429"/>
-      <c r="E41" s="395" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F41" s="363" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G41" s="423" t="s">
+    <row r="41" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A41" s="398"/>
+      <c r="B41" s="398"/>
+      <c r="C41" s="427"/>
+      <c r="D41" s="440"/>
+      <c r="E41" s="451" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F41" s="451" t="s">
+        <v>987</v>
+      </c>
+      <c r="G41" s="394"/>
+      <c r="H41" s="394"/>
+      <c r="I41" s="451" t="s">
         <v>905</v>
       </c>
-      <c r="H41" s="395"/>
-      <c r="I41" s="423" t="s">
-        <v>905</v>
-      </c>
-      <c r="J41" s="424"/>
+      <c r="J41" s="423"/>
       <c r="K41" s="305"/>
       <c r="L41" s="305"/>
     </row>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A42" s="399"/>
-      <c r="B42" s="399"/>
-      <c r="C42" s="429"/>
-      <c r="D42" s="306" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E42" s="395" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F42" s="363" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G42" s="423"/>
-      <c r="H42" s="395"/>
-      <c r="I42" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J42" s="424" t="s">
-        <v>1027</v>
-      </c>
+    <row r="42" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A42" s="398"/>
+      <c r="B42" s="398"/>
+      <c r="C42" s="427"/>
+      <c r="D42" s="429"/>
+      <c r="E42" s="430" t="s">
+        <v>730</v>
+      </c>
+      <c r="F42" s="430" t="s">
+        <v>731</v>
+      </c>
+      <c r="G42" s="430"/>
+      <c r="H42" s="430"/>
+      <c r="I42" s="430"/>
+      <c r="J42" s="431"/>
       <c r="K42" s="305"/>
       <c r="L42" s="305"/>
     </row>
-    <row r="43" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A43" s="399"/>
-      <c r="B43" s="399"/>
-      <c r="C43" s="429"/>
-      <c r="E43" s="395" t="s">
-        <v>972</v>
-      </c>
-      <c r="F43" s="395" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G43" s="395"/>
-      <c r="H43" s="395"/>
-      <c r="I43" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J43" s="424"/>
+    <row r="43" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A43" s="398"/>
+      <c r="B43" s="398"/>
+      <c r="C43" s="441"/>
+      <c r="D43" s="433"/>
+      <c r="E43" s="430" t="s">
+        <v>739</v>
+      </c>
+      <c r="F43" s="430" t="s">
+        <v>731</v>
+      </c>
+      <c r="G43" s="430"/>
+      <c r="H43" s="430"/>
+      <c r="I43" s="430"/>
+      <c r="J43" s="431"/>
       <c r="K43" s="305"/>
       <c r="L43" s="305"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A44" s="399"/>
-      <c r="B44" s="399"/>
-      <c r="C44" s="429"/>
-      <c r="E44" s="395" t="s">
-        <v>974</v>
-      </c>
-      <c r="F44" s="441" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G44" s="395"/>
-      <c r="H44" s="395"/>
-      <c r="I44" s="423" t="s">
-        <v>710</v>
-      </c>
-      <c r="J44" s="424"/>
+      <c r="A44" s="398"/>
+      <c r="B44" s="398"/>
+      <c r="C44" s="428">
+        <v>5</v>
+      </c>
+      <c r="D44" s="470" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E44" s="418"/>
+      <c r="F44" s="418"/>
+      <c r="G44" s="418"/>
+      <c r="H44" s="418"/>
+      <c r="I44" s="418"/>
+      <c r="J44" s="419"/>
       <c r="K44" s="305"/>
       <c r="L44" s="305"/>
     </row>
-    <row r="45" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A45" s="399"/>
-      <c r="B45" s="399"/>
-      <c r="C45" s="429"/>
-      <c r="E45" s="395" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F45" s="395" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G45" s="395"/>
-      <c r="H45" s="395"/>
-      <c r="I45" s="423" t="s">
+    <row r="45" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A45" s="398"/>
+      <c r="B45" s="398"/>
+      <c r="C45" s="427"/>
+      <c r="E45" s="394" t="s">
+        <v>701</v>
+      </c>
+      <c r="F45" s="394" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G45" s="394" t="s">
         <v>710</v>
       </c>
-      <c r="J45" s="424"/>
+      <c r="H45" s="394"/>
+      <c r="I45" s="394" t="s">
+        <v>710</v>
+      </c>
+      <c r="J45" s="423"/>
       <c r="K45" s="305"/>
       <c r="L45" s="305"/>
     </row>
-    <row r="46" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A46" s="399"/>
-      <c r="B46" s="399"/>
-      <c r="C46" s="429"/>
-      <c r="D46" s="442" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E46" s="395" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F46" s="395" t="s">
-        <v>1035</v>
-      </c>
-      <c r="G46" s="395"/>
-      <c r="H46" s="395"/>
-      <c r="I46" s="395" t="s">
+    <row r="46" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A46" s="398"/>
+      <c r="B46" s="398"/>
+      <c r="C46" s="427"/>
+      <c r="D46" s="312" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E46" s="394" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F46" s="394" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G46" s="394"/>
+      <c r="H46" s="394"/>
+      <c r="I46" s="394" t="s">
         <v>905</v>
       </c>
-      <c r="J46" s="424"/>
+      <c r="J46" s="423" t="s">
+        <v>1031</v>
+      </c>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
     </row>
-    <row r="47" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A47" s="399"/>
-      <c r="B47" s="399"/>
-      <c r="C47" s="429"/>
-      <c r="D47" s="431"/>
-      <c r="E47" s="432" t="s">
-        <v>730</v>
-      </c>
-      <c r="F47" s="432" t="s">
-        <v>731</v>
-      </c>
-      <c r="G47" s="432"/>
-      <c r="H47" s="432"/>
-      <c r="I47" s="432"/>
-      <c r="J47" s="433"/>
+    <row r="47" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A47" s="398"/>
+      <c r="B47" s="398"/>
+      <c r="C47" s="427"/>
+      <c r="E47" s="394" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F47" s="394" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G47" s="394"/>
+      <c r="H47" s="394"/>
+      <c r="I47" s="394"/>
+      <c r="J47" s="423"/>
       <c r="K47" s="305"/>
       <c r="L47" s="305"/>
     </row>
-    <row r="48" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A48" s="399"/>
-      <c r="B48" s="399"/>
-      <c r="C48" s="443"/>
-      <c r="D48" s="435"/>
-      <c r="E48" s="432" t="s">
-        <v>739</v>
-      </c>
-      <c r="F48" s="432" t="s">
-        <v>731</v>
-      </c>
-      <c r="G48" s="432"/>
-      <c r="H48" s="432"/>
-      <c r="I48" s="432"/>
-      <c r="J48" s="433"/>
+    <row r="48" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A48" s="398"/>
+      <c r="B48" s="398"/>
+      <c r="C48" s="427"/>
+      <c r="E48" s="394" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F48" s="394" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G48" s="394"/>
+      <c r="H48" s="394"/>
+      <c r="I48" s="394"/>
+      <c r="J48" s="423"/>
       <c r="K48" s="305"/>
       <c r="L48" s="305"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A49" s="399"/>
-      <c r="B49" s="399"/>
-      <c r="C49" s="430">
-        <v>6</v>
-      </c>
-      <c r="D49" s="418" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E49" s="419"/>
-      <c r="F49" s="419"/>
-      <c r="G49" s="419"/>
-      <c r="H49" s="419"/>
-      <c r="I49" s="419"/>
-      <c r="J49" s="420"/>
+      <c r="A49" s="398"/>
+      <c r="B49" s="398"/>
+      <c r="C49" s="427"/>
+      <c r="E49" s="394" t="s">
+        <v>730</v>
+      </c>
+      <c r="F49" s="394" t="s">
+        <v>731</v>
+      </c>
+      <c r="G49" s="394"/>
+      <c r="H49" s="394"/>
+      <c r="I49" s="394"/>
+      <c r="J49" s="423"/>
       <c r="K49" s="305"/>
       <c r="L49" s="305"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A50" s="399"/>
-      <c r="B50" s="399"/>
-      <c r="C50" s="429"/>
-      <c r="E50" s="395" t="s">
-        <v>701</v>
-      </c>
-      <c r="F50" s="395" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G50" s="395" t="s">
-        <v>710</v>
-      </c>
-      <c r="H50" s="395"/>
-      <c r="I50" s="395" t="s">
-        <v>710</v>
-      </c>
-      <c r="J50" s="424"/>
+      <c r="A50" s="398"/>
+      <c r="B50" s="398"/>
+      <c r="C50" s="427"/>
+      <c r="E50" s="394" t="s">
+        <v>739</v>
+      </c>
+      <c r="F50" s="394" t="s">
+        <v>731</v>
+      </c>
+      <c r="G50" s="394"/>
+      <c r="H50" s="394"/>
+      <c r="I50" s="394"/>
+      <c r="J50" s="423"/>
       <c r="K50" s="305"/>
       <c r="L50" s="305"/>
     </row>
-    <row r="51" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A51" s="399"/>
-      <c r="B51" s="399"/>
-      <c r="C51" s="429"/>
-      <c r="D51" s="312" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E51" s="395" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F51" s="395" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G51" s="395"/>
-      <c r="H51" s="395"/>
-      <c r="I51" s="395" t="s">
-        <v>905</v>
-      </c>
-      <c r="J51" s="424" t="s">
-        <v>1038</v>
-      </c>
+    <row r="51" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A51" s="398"/>
+      <c r="B51" s="398"/>
+      <c r="C51" s="428">
+        <v>6</v>
+      </c>
+      <c r="D51" s="417" t="s">
+        <v>748</v>
+      </c>
+      <c r="E51" s="418"/>
+      <c r="F51" s="418"/>
+      <c r="G51" s="418"/>
+      <c r="H51" s="418"/>
+      <c r="I51" s="418"/>
+      <c r="J51" s="419"/>
       <c r="K51" s="305"/>
       <c r="L51" s="305"/>
     </row>
-    <row r="52" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A52" s="399"/>
-      <c r="B52" s="399"/>
-      <c r="C52" s="429"/>
-      <c r="E52" s="395" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F52" s="395" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G52" s="395"/>
-      <c r="H52" s="395"/>
-      <c r="I52" s="395"/>
-      <c r="J52" s="424"/>
+    <row r="52" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A52" s="398"/>
+      <c r="B52" s="398"/>
+      <c r="C52" s="427"/>
+      <c r="E52" s="394"/>
+      <c r="F52" s="363"/>
+      <c r="G52" s="422"/>
+      <c r="H52" s="394"/>
+      <c r="I52" s="422"/>
+      <c r="J52" s="423"/>
       <c r="K52" s="305"/>
       <c r="L52" s="305"/>
     </row>
-    <row r="53" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A53" s="399"/>
-      <c r="B53" s="399"/>
-      <c r="C53" s="429"/>
-      <c r="E53" s="395" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F53" s="395" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G53" s="395"/>
-      <c r="H53" s="395"/>
-      <c r="I53" s="395"/>
-      <c r="J53" s="424"/>
+    <row r="53" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A53" s="398"/>
+      <c r="B53" s="398"/>
+      <c r="C53" s="427"/>
+      <c r="E53" s="394"/>
+      <c r="F53" s="363"/>
+      <c r="G53" s="394"/>
+      <c r="H53" s="394"/>
+      <c r="I53" s="422"/>
+      <c r="J53" s="423"/>
       <c r="K53" s="305"/>
       <c r="L53" s="305"/>
     </row>
-    <row r="54" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A54" s="399"/>
-      <c r="B54" s="399"/>
-      <c r="C54" s="429"/>
-      <c r="E54" s="395" t="s">
-        <v>730</v>
-      </c>
-      <c r="F54" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G54" s="395"/>
-      <c r="H54" s="395"/>
-      <c r="I54" s="395"/>
-      <c r="J54" s="424"/>
+    <row r="54" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A54" s="398"/>
+      <c r="B54" s="398"/>
+      <c r="C54" s="427"/>
+      <c r="D54" s="312"/>
+      <c r="E54" s="394"/>
+      <c r="F54" s="363"/>
+      <c r="G54" s="394"/>
+      <c r="H54" s="422"/>
+      <c r="I54" s="422"/>
+      <c r="J54" s="423"/>
       <c r="K54" s="305"/>
       <c r="L54" s="305"/>
     </row>
-    <row r="55" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A55" s="399"/>
-      <c r="B55" s="399"/>
-      <c r="C55" s="429"/>
-      <c r="E55" s="395" t="s">
-        <v>739</v>
-      </c>
-      <c r="F55" s="395" t="s">
-        <v>731</v>
-      </c>
-      <c r="G55" s="395"/>
-      <c r="H55" s="395"/>
-      <c r="I55" s="395"/>
-      <c r="J55" s="424"/>
+    <row r="55" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A55" s="398"/>
+      <c r="B55" s="398"/>
+      <c r="C55" s="427"/>
+      <c r="E55" s="394"/>
+      <c r="F55" s="394"/>
+      <c r="G55" s="394"/>
+      <c r="H55" s="394"/>
+      <c r="I55" s="394"/>
+      <c r="J55" s="423"/>
       <c r="K55" s="305"/>
       <c r="L55" s="305"/>
     </row>
     <row r="56" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A56" s="399"/>
-      <c r="B56" s="399"/>
-      <c r="C56" s="430">
-        <v>7</v>
-      </c>
-      <c r="D56" s="418" t="s">
-        <v>748</v>
-      </c>
-      <c r="E56" s="419"/>
-      <c r="F56" s="419"/>
-      <c r="G56" s="419"/>
-      <c r="H56" s="419"/>
-      <c r="I56" s="419"/>
-      <c r="J56" s="420"/>
+      <c r="A56" s="398"/>
+      <c r="B56" s="398"/>
+      <c r="C56" s="427"/>
+      <c r="E56" s="394"/>
+      <c r="F56" s="394"/>
+      <c r="G56" s="394"/>
+      <c r="H56" s="394"/>
+      <c r="I56" s="394"/>
+      <c r="J56" s="423"/>
       <c r="K56" s="305"/>
       <c r="L56" s="305"/>
     </row>
     <row r="57" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A57" s="399"/>
-      <c r="B57" s="399"/>
-      <c r="C57" s="429"/>
-      <c r="E57" s="395"/>
-      <c r="F57" s="363"/>
-      <c r="G57" s="423"/>
-      <c r="H57" s="395"/>
-      <c r="I57" s="423"/>
-      <c r="J57" s="424"/>
+      <c r="A57" s="398"/>
+      <c r="B57" s="398"/>
+      <c r="C57" s="427"/>
+      <c r="E57" s="364"/>
+      <c r="F57" s="394"/>
+      <c r="G57" s="394"/>
+      <c r="H57" s="394"/>
+      <c r="I57" s="394"/>
+      <c r="J57" s="423"/>
       <c r="K57" s="305"/>
       <c r="L57" s="305"/>
     </row>
-    <row r="58" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A58" s="399"/>
-      <c r="B58" s="399"/>
-      <c r="C58" s="429"/>
-      <c r="E58" s="395"/>
-      <c r="F58" s="363"/>
-      <c r="G58" s="395"/>
-      <c r="H58" s="395"/>
-      <c r="I58" s="423"/>
-      <c r="J58" s="424"/>
+    <row r="58" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A58" s="398"/>
+      <c r="B58" s="398"/>
+      <c r="C58" s="428">
+        <v>7</v>
+      </c>
+      <c r="D58" s="417" t="s">
+        <v>748</v>
+      </c>
+      <c r="E58" s="418"/>
+      <c r="F58" s="418"/>
+      <c r="G58" s="418"/>
+      <c r="H58" s="418"/>
+      <c r="I58" s="418"/>
+      <c r="J58" s="419"/>
       <c r="K58" s="305"/>
       <c r="L58" s="305"/>
     </row>
-    <row r="59" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A59" s="399"/>
-      <c r="B59" s="399"/>
-      <c r="C59" s="429"/>
-      <c r="D59" s="312"/>
-      <c r="E59" s="395"/>
-      <c r="F59" s="363"/>
-      <c r="G59" s="395"/>
-      <c r="H59" s="423"/>
-      <c r="I59" s="423"/>
-      <c r="J59" s="424"/>
+    <row r="59" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A59" s="398"/>
+      <c r="B59" s="398"/>
+      <c r="C59" s="427"/>
+      <c r="E59" s="394"/>
+      <c r="F59" s="394"/>
+      <c r="G59" s="394"/>
+      <c r="H59" s="394"/>
+      <c r="I59" s="394"/>
+      <c r="J59" s="423"/>
       <c r="K59" s="305"/>
       <c r="L59" s="305"/>
     </row>
-    <row r="60" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A60" s="399"/>
-      <c r="B60" s="399"/>
-      <c r="C60" s="429"/>
-      <c r="E60" s="395"/>
-      <c r="F60" s="395"/>
-      <c r="G60" s="395"/>
-      <c r="H60" s="395"/>
-      <c r="I60" s="395"/>
-      <c r="J60" s="424"/>
+    <row r="60" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A60" s="398"/>
+      <c r="B60" s="398"/>
+      <c r="C60" s="427"/>
+      <c r="D60" s="304"/>
+      <c r="E60" s="394"/>
+      <c r="F60" s="394"/>
+      <c r="G60" s="394"/>
+      <c r="H60" s="394"/>
+      <c r="I60" s="394"/>
+      <c r="J60" s="423"/>
       <c r="K60" s="305"/>
       <c r="L60" s="305"/>
     </row>
-    <row r="61" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A61" s="399"/>
-      <c r="B61" s="399"/>
-      <c r="C61" s="429"/>
-      <c r="E61" s="395"/>
-      <c r="F61" s="395"/>
-      <c r="G61" s="395"/>
-      <c r="H61" s="395"/>
-      <c r="I61" s="395"/>
-      <c r="J61" s="424"/>
+    <row r="61" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A61" s="398"/>
+      <c r="B61" s="398"/>
+      <c r="C61" s="427"/>
+      <c r="E61" s="394"/>
+      <c r="F61" s="394"/>
+      <c r="G61" s="394"/>
+      <c r="H61" s="394"/>
+      <c r="I61" s="394"/>
+      <c r="J61" s="423"/>
       <c r="K61" s="305"/>
       <c r="L61" s="305"/>
     </row>
-    <row r="62" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A62" s="399"/>
-      <c r="B62" s="399"/>
-      <c r="C62" s="429"/>
-      <c r="E62" s="364"/>
-      <c r="F62" s="395"/>
-      <c r="G62" s="395"/>
-      <c r="H62" s="395"/>
-      <c r="I62" s="395"/>
-      <c r="J62" s="424"/>
+    <row r="62" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A62" s="398"/>
+      <c r="B62" s="398"/>
+      <c r="C62" s="427"/>
+      <c r="E62" s="394"/>
+      <c r="F62" s="394"/>
+      <c r="G62" s="394"/>
+      <c r="H62" s="394"/>
+      <c r="I62" s="394"/>
+      <c r="J62" s="423"/>
       <c r="K62" s="305"/>
       <c r="L62" s="305"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A63" s="399"/>
-      <c r="B63" s="399"/>
-      <c r="C63" s="430">
-        <v>8</v>
-      </c>
-      <c r="D63" s="418" t="s">
-        <v>748</v>
-      </c>
-      <c r="E63" s="419"/>
-      <c r="F63" s="419"/>
-      <c r="G63" s="419"/>
-      <c r="H63" s="419"/>
-      <c r="I63" s="419"/>
-      <c r="J63" s="420"/>
+      <c r="A63" s="398"/>
+      <c r="B63" s="398"/>
+      <c r="C63" s="427"/>
+      <c r="E63" s="394"/>
+      <c r="F63" s="394"/>
+      <c r="G63" s="394"/>
+      <c r="H63" s="394"/>
+      <c r="I63" s="394"/>
+      <c r="J63" s="423"/>
       <c r="K63" s="305"/>
       <c r="L63" s="305"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A64" s="399"/>
-      <c r="B64" s="399"/>
-      <c r="C64" s="429"/>
-      <c r="E64" s="395"/>
-      <c r="F64" s="395"/>
-      <c r="G64" s="395"/>
-      <c r="H64" s="395"/>
-      <c r="I64" s="395"/>
-      <c r="J64" s="424"/>
+      <c r="A64" s="398"/>
+      <c r="B64" s="398"/>
+      <c r="C64" s="427"/>
+      <c r="E64" s="394"/>
+      <c r="F64" s="394"/>
+      <c r="G64" s="394"/>
+      <c r="H64" s="394"/>
+      <c r="I64" s="394"/>
+      <c r="J64" s="423"/>
       <c r="K64" s="305"/>
       <c r="L64" s="305"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A65" s="399"/>
-      <c r="B65" s="399"/>
-      <c r="C65" s="429"/>
-      <c r="D65" s="304"/>
-      <c r="E65" s="395"/>
-      <c r="F65" s="395"/>
-      <c r="G65" s="395"/>
-      <c r="H65" s="395"/>
-      <c r="I65" s="395"/>
-      <c r="J65" s="424"/>
+      <c r="A65" s="398"/>
+      <c r="B65" s="398"/>
+      <c r="C65" s="427"/>
+      <c r="E65" s="394"/>
+      <c r="F65" s="394"/>
+      <c r="G65" s="394"/>
+      <c r="H65" s="394"/>
+      <c r="I65" s="394"/>
+      <c r="J65" s="423"/>
       <c r="K65" s="305"/>
       <c r="L65" s="305"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A66" s="399"/>
-      <c r="B66" s="399"/>
-      <c r="C66" s="429"/>
-      <c r="E66" s="395"/>
-      <c r="F66" s="395"/>
-      <c r="G66" s="395"/>
-      <c r="H66" s="395"/>
-      <c r="I66" s="395"/>
-      <c r="J66" s="424"/>
+      <c r="A66" s="398"/>
+      <c r="B66" s="398"/>
+      <c r="C66" s="427"/>
+      <c r="E66" s="394"/>
+      <c r="F66" s="394"/>
+      <c r="G66" s="394"/>
+      <c r="H66" s="394"/>
+      <c r="I66" s="394"/>
+      <c r="J66" s="423"/>
       <c r="K66" s="305"/>
       <c r="L66" s="305"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A67" s="399"/>
-      <c r="B67" s="399"/>
-      <c r="C67" s="429"/>
-      <c r="E67" s="395"/>
-      <c r="F67" s="395"/>
-      <c r="G67" s="395"/>
-      <c r="H67" s="395"/>
-      <c r="I67" s="395"/>
-      <c r="J67" s="424"/>
+      <c r="A67" s="398"/>
+      <c r="B67" s="398"/>
+      <c r="C67" s="427"/>
+      <c r="E67" s="394"/>
+      <c r="F67" s="394"/>
+      <c r="G67" s="394"/>
+      <c r="H67" s="394"/>
+      <c r="I67" s="394"/>
+      <c r="J67" s="423"/>
       <c r="K67" s="305"/>
       <c r="L67" s="305"/>
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A68" s="399"/>
-      <c r="B68" s="399"/>
-      <c r="C68" s="429"/>
-      <c r="E68" s="395"/>
-      <c r="F68" s="395"/>
-      <c r="G68" s="395"/>
-      <c r="H68" s="395"/>
-      <c r="I68" s="395"/>
-      <c r="J68" s="424"/>
+      <c r="A68" s="398"/>
+      <c r="B68" s="398"/>
+      <c r="C68" s="427"/>
+      <c r="D68" s="303"/>
+      <c r="E68" s="394"/>
+      <c r="F68" s="394"/>
+      <c r="G68" s="394"/>
+      <c r="H68" s="394"/>
+      <c r="I68" s="394"/>
+      <c r="J68" s="423"/>
       <c r="K68" s="305"/>
       <c r="L68" s="305"/>
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A69" s="399"/>
-      <c r="B69" s="399"/>
-      <c r="C69" s="429"/>
-      <c r="E69" s="395"/>
-      <c r="F69" s="395"/>
-      <c r="G69" s="395"/>
-      <c r="H69" s="395"/>
-      <c r="I69" s="395"/>
-      <c r="J69" s="424"/>
+      <c r="A69" s="398"/>
+      <c r="B69" s="398"/>
+      <c r="C69" s="427"/>
+      <c r="D69" s="429"/>
+      <c r="E69" s="442"/>
+      <c r="F69" s="442"/>
+      <c r="G69" s="442"/>
+      <c r="H69" s="442"/>
+      <c r="I69" s="442"/>
+      <c r="J69" s="443"/>
       <c r="K69" s="305"/>
       <c r="L69" s="305"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A70" s="399"/>
-      <c r="B70" s="399"/>
-      <c r="C70" s="429"/>
-      <c r="E70" s="395"/>
-      <c r="F70" s="395"/>
-      <c r="G70" s="395"/>
-      <c r="H70" s="395"/>
-      <c r="I70" s="395"/>
-      <c r="J70" s="424"/>
+      <c r="A70" s="398"/>
+      <c r="B70" s="398"/>
+      <c r="C70" s="427"/>
+      <c r="D70" s="429"/>
+      <c r="E70" s="430"/>
+      <c r="F70" s="430"/>
+      <c r="G70" s="430"/>
+      <c r="H70" s="430"/>
+      <c r="I70" s="430"/>
+      <c r="J70" s="431"/>
       <c r="K70" s="305"/>
       <c r="L70" s="305"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A71" s="399"/>
-      <c r="B71" s="399"/>
-      <c r="C71" s="429"/>
-      <c r="E71" s="395"/>
-      <c r="F71" s="395"/>
-      <c r="G71" s="395"/>
-      <c r="H71" s="395"/>
-      <c r="I71" s="395"/>
-      <c r="J71" s="424"/>
+      <c r="A71" s="398"/>
+      <c r="B71" s="398"/>
+      <c r="C71" s="441"/>
+      <c r="D71" s="433"/>
+      <c r="E71" s="430"/>
+      <c r="F71" s="430"/>
+      <c r="G71" s="430"/>
+      <c r="H71" s="430"/>
+      <c r="I71" s="430"/>
+      <c r="J71" s="431"/>
       <c r="K71" s="305"/>
       <c r="L71" s="305"/>
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A72" s="399"/>
-      <c r="B72" s="399"/>
-      <c r="C72" s="429"/>
-      <c r="E72" s="395"/>
-      <c r="F72" s="395"/>
-      <c r="G72" s="395"/>
-      <c r="H72" s="395"/>
-      <c r="I72" s="395"/>
-      <c r="J72" s="424"/>
+      <c r="A72" s="398"/>
+      <c r="B72" s="398"/>
+      <c r="C72" s="428">
+        <v>8</v>
+      </c>
+      <c r="D72" s="417" t="s">
+        <v>748</v>
+      </c>
+      <c r="E72" s="418"/>
+      <c r="F72" s="418"/>
+      <c r="G72" s="418"/>
+      <c r="H72" s="418"/>
+      <c r="I72" s="418"/>
+      <c r="J72" s="419"/>
       <c r="K72" s="305"/>
       <c r="L72" s="305"/>
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A73" s="399"/>
-      <c r="B73" s="399"/>
-      <c r="C73" s="429"/>
-      <c r="D73" s="303"/>
-      <c r="E73" s="395"/>
-      <c r="F73" s="395"/>
-      <c r="G73" s="395"/>
-      <c r="H73" s="395"/>
-      <c r="I73" s="395"/>
-      <c r="J73" s="424"/>
+      <c r="A73" s="398"/>
+      <c r="B73" s="398"/>
+      <c r="C73" s="427"/>
+      <c r="E73" s="394"/>
+      <c r="F73" s="394"/>
+      <c r="G73" s="394"/>
+      <c r="H73" s="394"/>
+      <c r="I73" s="394"/>
+      <c r="J73" s="423"/>
       <c r="K73" s="305"/>
       <c r="L73" s="305"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A74" s="399"/>
-      <c r="B74" s="399"/>
-      <c r="C74" s="429"/>
-      <c r="D74" s="431"/>
-      <c r="E74" s="444"/>
-      <c r="F74" s="444"/>
-      <c r="G74" s="444"/>
-      <c r="H74" s="444"/>
-      <c r="I74" s="444"/>
-      <c r="J74" s="445"/>
+      <c r="A74" s="398"/>
+      <c r="B74" s="398"/>
+      <c r="C74" s="427"/>
+      <c r="D74" s="304"/>
+      <c r="E74" s="394"/>
+      <c r="F74" s="394"/>
+      <c r="G74" s="394"/>
+      <c r="H74" s="394"/>
+      <c r="I74" s="394"/>
+      <c r="J74" s="423"/>
       <c r="K74" s="305"/>
       <c r="L74" s="305"/>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A75" s="399"/>
-      <c r="B75" s="399"/>
-      <c r="C75" s="429"/>
-      <c r="D75" s="431"/>
-      <c r="E75" s="432"/>
-      <c r="F75" s="432"/>
-      <c r="G75" s="432"/>
-      <c r="H75" s="432"/>
-      <c r="I75" s="432"/>
-      <c r="J75" s="433"/>
+      <c r="A75" s="398"/>
+      <c r="B75" s="398"/>
+      <c r="C75" s="427"/>
+      <c r="E75" s="394"/>
+      <c r="F75" s="394"/>
+      <c r="G75" s="394"/>
+      <c r="H75" s="394"/>
+      <c r="I75" s="394"/>
+      <c r="J75" s="423"/>
       <c r="K75" s="305"/>
       <c r="L75" s="305"/>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A76" s="399"/>
-      <c r="B76" s="399"/>
-      <c r="C76" s="443"/>
-      <c r="D76" s="435"/>
-      <c r="E76" s="432"/>
-      <c r="F76" s="432"/>
-      <c r="G76" s="432"/>
-      <c r="H76" s="432"/>
-      <c r="I76" s="432"/>
-      <c r="J76" s="433"/>
+      <c r="A76" s="398"/>
+      <c r="B76" s="398"/>
+      <c r="C76" s="427"/>
+      <c r="E76" s="394"/>
+      <c r="F76" s="394"/>
+      <c r="G76" s="394"/>
+      <c r="H76" s="394"/>
+      <c r="I76" s="394"/>
+      <c r="J76" s="423"/>
       <c r="K76" s="305"/>
       <c r="L76" s="305"/>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A77" s="399"/>
-      <c r="B77" s="399"/>
-      <c r="C77" s="430">
-        <v>9</v>
-      </c>
-      <c r="D77" s="418" t="s">
-        <v>748</v>
-      </c>
-      <c r="E77" s="419"/>
-      <c r="F77" s="419"/>
-      <c r="G77" s="419"/>
-      <c r="H77" s="419"/>
-      <c r="I77" s="419"/>
-      <c r="J77" s="420"/>
+      <c r="A77" s="398"/>
+      <c r="B77" s="398"/>
+      <c r="C77" s="427"/>
+      <c r="E77" s="394"/>
+      <c r="F77" s="394"/>
+      <c r="G77" s="394"/>
+      <c r="H77" s="394"/>
+      <c r="I77" s="394"/>
+      <c r="J77" s="423"/>
       <c r="K77" s="305"/>
       <c r="L77" s="305"/>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A78" s="399"/>
-      <c r="B78" s="399"/>
-      <c r="C78" s="429"/>
-      <c r="E78" s="395"/>
-      <c r="F78" s="395"/>
-      <c r="G78" s="395"/>
-      <c r="H78" s="395"/>
-      <c r="I78" s="395"/>
-      <c r="J78" s="424"/>
+      <c r="A78" s="398"/>
+      <c r="B78" s="398"/>
+      <c r="C78" s="427"/>
+      <c r="E78" s="394"/>
+      <c r="F78" s="394"/>
+      <c r="G78" s="394"/>
+      <c r="H78" s="394"/>
+      <c r="I78" s="394"/>
+      <c r="J78" s="423"/>
       <c r="K78" s="305"/>
       <c r="L78" s="305"/>
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A79" s="399"/>
-      <c r="B79" s="399"/>
-      <c r="C79" s="429"/>
-      <c r="D79" s="304"/>
-      <c r="E79" s="395"/>
-      <c r="F79" s="395"/>
-      <c r="G79" s="395"/>
-      <c r="H79" s="395"/>
-      <c r="I79" s="395"/>
-      <c r="J79" s="424"/>
+      <c r="A79" s="398"/>
+      <c r="B79" s="398"/>
+      <c r="C79" s="427"/>
+      <c r="E79" s="394"/>
+      <c r="F79" s="394"/>
+      <c r="G79" s="394"/>
+      <c r="H79" s="394"/>
+      <c r="I79" s="394"/>
+      <c r="J79" s="423"/>
       <c r="K79" s="305"/>
       <c r="L79" s="305"/>
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A80" s="399"/>
-      <c r="B80" s="399"/>
-      <c r="C80" s="429"/>
-      <c r="E80" s="395"/>
-      <c r="F80" s="395"/>
-      <c r="G80" s="395"/>
-      <c r="H80" s="395"/>
-      <c r="I80" s="395"/>
-      <c r="J80" s="424"/>
+      <c r="A80" s="398"/>
+      <c r="B80" s="398"/>
+      <c r="C80" s="427"/>
+      <c r="E80" s="394"/>
+      <c r="F80" s="394"/>
+      <c r="G80" s="394"/>
+      <c r="H80" s="394"/>
+      <c r="I80" s="394"/>
+      <c r="J80" s="423"/>
       <c r="K80" s="305"/>
       <c r="L80" s="305"/>
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A81" s="399"/>
-      <c r="B81" s="399"/>
-      <c r="C81" s="429"/>
-      <c r="E81" s="395"/>
-      <c r="F81" s="395"/>
-      <c r="G81" s="395"/>
-      <c r="H81" s="395"/>
-      <c r="I81" s="395"/>
-      <c r="J81" s="424"/>
+      <c r="A81" s="398"/>
+      <c r="B81" s="398"/>
+      <c r="C81" s="427"/>
+      <c r="E81" s="394"/>
+      <c r="F81" s="394"/>
+      <c r="G81" s="394"/>
+      <c r="H81" s="394"/>
+      <c r="I81" s="394"/>
+      <c r="J81" s="423"/>
       <c r="K81" s="305"/>
       <c r="L81" s="305"/>
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A82" s="399"/>
-      <c r="B82" s="399"/>
-      <c r="C82" s="429"/>
-      <c r="E82" s="395"/>
-      <c r="F82" s="395"/>
-      <c r="G82" s="395"/>
-      <c r="H82" s="395"/>
-      <c r="I82" s="395"/>
-      <c r="J82" s="424"/>
+      <c r="A82" s="398"/>
+      <c r="B82" s="398"/>
+      <c r="C82" s="427"/>
+      <c r="D82" s="303"/>
+      <c r="E82" s="394"/>
+      <c r="F82" s="394"/>
+      <c r="G82" s="394"/>
+      <c r="H82" s="394"/>
+      <c r="I82" s="394"/>
+      <c r="J82" s="423"/>
       <c r="K82" s="305"/>
       <c r="L82" s="305"/>
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A83" s="399"/>
-      <c r="B83" s="399"/>
-      <c r="C83" s="429"/>
-      <c r="E83" s="395"/>
-      <c r="F83" s="395"/>
-      <c r="G83" s="395"/>
-      <c r="H83" s="395"/>
-      <c r="I83" s="395"/>
-      <c r="J83" s="424"/>
+      <c r="A83" s="398"/>
+      <c r="B83" s="398"/>
+      <c r="C83" s="427"/>
+      <c r="D83" s="429"/>
+      <c r="E83" s="442"/>
+      <c r="F83" s="442"/>
+      <c r="G83" s="442"/>
+      <c r="H83" s="442"/>
+      <c r="I83" s="442"/>
+      <c r="J83" s="443"/>
       <c r="K83" s="305"/>
       <c r="L83" s="305"/>
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A84" s="399"/>
-      <c r="B84" s="399"/>
-      <c r="C84" s="429"/>
-      <c r="E84" s="395"/>
-      <c r="F84" s="395"/>
-      <c r="G84" s="395"/>
-      <c r="H84" s="395"/>
-      <c r="I84" s="395"/>
-      <c r="J84" s="424"/>
+      <c r="A84" s="398"/>
+      <c r="B84" s="398"/>
+      <c r="C84" s="427"/>
+      <c r="D84" s="429"/>
+      <c r="E84" s="430"/>
+      <c r="F84" s="430"/>
+      <c r="G84" s="430"/>
+      <c r="H84" s="430"/>
+      <c r="I84" s="430"/>
+      <c r="J84" s="431"/>
       <c r="K84" s="305"/>
       <c r="L84" s="305"/>
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A85" s="399"/>
-      <c r="B85" s="399"/>
-      <c r="C85" s="429"/>
-      <c r="E85" s="395"/>
-      <c r="F85" s="395"/>
-      <c r="G85" s="395"/>
-      <c r="H85" s="395"/>
-      <c r="I85" s="395"/>
-      <c r="J85" s="424"/>
+      <c r="A85" s="398"/>
+      <c r="B85" s="398"/>
+      <c r="C85" s="441"/>
+      <c r="D85" s="433"/>
+      <c r="E85" s="430"/>
+      <c r="F85" s="430"/>
+      <c r="G85" s="430"/>
+      <c r="H85" s="430"/>
+      <c r="I85" s="430"/>
+      <c r="J85" s="431"/>
       <c r="K85" s="305"/>
       <c r="L85" s="305"/>
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A86" s="399"/>
-      <c r="B86" s="399"/>
-      <c r="C86" s="429"/>
-      <c r="E86" s="395"/>
-      <c r="F86" s="395"/>
-      <c r="G86" s="395"/>
-      <c r="H86" s="395"/>
-      <c r="I86" s="395"/>
-      <c r="J86" s="424"/>
+      <c r="A86" s="398"/>
+      <c r="B86" s="398"/>
+      <c r="C86" s="444"/>
+      <c r="D86" s="305"/>
+      <c r="E86" s="305"/>
+      <c r="F86" s="305"/>
+      <c r="G86" s="305"/>
+      <c r="H86" s="305"/>
+      <c r="I86" s="305"/>
+      <c r="J86" s="305"/>
       <c r="K86" s="305"/>
       <c r="L86" s="305"/>
     </row>
-    <row r="87" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A87" s="399"/>
-      <c r="B87" s="399"/>
-      <c r="C87" s="429"/>
-      <c r="D87" s="303"/>
-      <c r="E87" s="395"/>
-      <c r="F87" s="395"/>
-      <c r="G87" s="395"/>
-      <c r="H87" s="395"/>
-      <c r="I87" s="395"/>
-      <c r="J87" s="424"/>
-      <c r="K87" s="305"/>
-      <c r="L87" s="305"/>
-    </row>
-    <row r="88" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A88" s="399"/>
-      <c r="B88" s="399"/>
-      <c r="C88" s="429"/>
-      <c r="D88" s="431"/>
-      <c r="E88" s="444"/>
-      <c r="F88" s="444"/>
-      <c r="G88" s="444"/>
-      <c r="H88" s="444"/>
-      <c r="I88" s="444"/>
-      <c r="J88" s="445"/>
-      <c r="K88" s="305"/>
-      <c r="L88" s="305"/>
-    </row>
-    <row r="89" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A89" s="399"/>
-      <c r="B89" s="399"/>
-      <c r="C89" s="429"/>
-      <c r="D89" s="431"/>
-      <c r="E89" s="432"/>
-      <c r="F89" s="432"/>
-      <c r="G89" s="432"/>
-      <c r="H89" s="432"/>
-      <c r="I89" s="432"/>
-      <c r="J89" s="433"/>
-      <c r="K89" s="305"/>
-      <c r="L89" s="305"/>
-    </row>
-    <row r="90" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A90" s="399"/>
-      <c r="B90" s="399"/>
-      <c r="C90" s="443"/>
-      <c r="D90" s="435"/>
-      <c r="E90" s="432"/>
-      <c r="F90" s="432"/>
-      <c r="G90" s="432"/>
-      <c r="H90" s="432"/>
-      <c r="I90" s="432"/>
-      <c r="J90" s="433"/>
-      <c r="K90" s="305"/>
-      <c r="L90" s="305"/>
-    </row>
-    <row r="91" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A91" s="399"/>
-      <c r="B91" s="399"/>
-      <c r="C91" s="446"/>
-      <c r="D91" s="305"/>
-      <c r="E91" s="305"/>
-      <c r="F91" s="305"/>
-      <c r="G91" s="305"/>
-      <c r="H91" s="305"/>
-      <c r="I91" s="305"/>
-      <c r="J91" s="305"/>
-      <c r="K91" s="305"/>
-      <c r="L91" s="305"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D34:H34"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0" footer="0"/>
@@ -10329,11 +10297,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="450" t="s">
+      <c r="C4" s="456" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="451"/>
-      <c r="E4" s="451"/>
+      <c r="D4" s="457"/>
+      <c r="E4" s="457"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10342,13 +10310,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="456" t="s">
+      <c r="C5" s="462" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="452" t="s">
+      <c r="D5" s="458" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="453"/>
+      <c r="E5" s="459"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10357,11 +10325,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="449"/>
-      <c r="D6" s="454" t="s">
+      <c r="C6" s="455"/>
+      <c r="D6" s="460" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="455"/>
+      <c r="E6" s="461"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10370,11 +10338,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="449"/>
-      <c r="D7" s="454" t="s">
+      <c r="C7" s="455"/>
+      <c r="D7" s="460" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="455"/>
+      <c r="E7" s="461"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10383,11 +10351,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="449"/>
-      <c r="D8" s="454" t="s">
+      <c r="C8" s="455"/>
+      <c r="D8" s="460" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="455"/>
+      <c r="E8" s="461"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10396,11 +10364,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="449"/>
-      <c r="D9" s="454" t="s">
+      <c r="C9" s="455"/>
+      <c r="D9" s="460" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="455"/>
+      <c r="E9" s="461"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10409,11 +10377,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="448"/>
-      <c r="D10" s="454" t="s">
+      <c r="C10" s="454"/>
+      <c r="D10" s="460" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="455"/>
+      <c r="E10" s="461"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10422,13 +10390,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="447" t="s">
+      <c r="C11" s="453" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="454" t="s">
+      <c r="D11" s="460" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="455"/>
+      <c r="E11" s="461"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10437,11 +10405,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="448"/>
-      <c r="D12" s="454" t="s">
+      <c r="C12" s="454"/>
+      <c r="D12" s="460" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="455"/>
+      <c r="E12" s="461"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10450,13 +10418,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="447" t="s">
+      <c r="C13" s="453" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="454" t="s">
+      <c r="D13" s="460" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="455"/>
+      <c r="E13" s="461"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10465,11 +10433,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="449"/>
-      <c r="D14" s="454" t="s">
+      <c r="C14" s="455"/>
+      <c r="D14" s="460" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="455"/>
+      <c r="E14" s="461"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10478,11 +10446,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="448"/>
-      <c r="D15" s="454" t="s">
+      <c r="C15" s="454"/>
+      <c r="D15" s="460" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="455"/>
+      <c r="E15" s="461"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -10491,13 +10459,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="447" t="s">
+      <c r="C16" s="453" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="459" t="s">
+      <c r="D16" s="465" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="460"/>
+      <c r="E16" s="466"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -10506,8 +10474,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="449"/>
-      <c r="D17" s="458" t="s">
+      <c r="C17" s="455"/>
+      <c r="D17" s="464" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -10521,8 +10489,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="449"/>
-      <c r="D18" s="449"/>
+      <c r="C18" s="455"/>
+      <c r="D18" s="455"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -10534,8 +10502,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="449"/>
-      <c r="D19" s="449"/>
+      <c r="C19" s="455"/>
+      <c r="D19" s="455"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -10547,8 +10515,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="449"/>
-      <c r="D20" s="449"/>
+      <c r="C20" s="455"/>
+      <c r="D20" s="455"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -10560,8 +10528,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="449"/>
-      <c r="D21" s="448"/>
+      <c r="C21" s="455"/>
+      <c r="D21" s="454"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -10573,8 +10541,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="449"/>
-      <c r="D22" s="457" t="s">
+      <c r="C22" s="455"/>
+      <c r="D22" s="463" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -10588,8 +10556,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="449"/>
-      <c r="D23" s="449"/>
+      <c r="C23" s="455"/>
+      <c r="D23" s="455"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -10601,8 +10569,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="449"/>
-      <c r="D24" s="449"/>
+      <c r="C24" s="455"/>
+      <c r="D24" s="455"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -10614,8 +10582,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="449"/>
-      <c r="D25" s="449"/>
+      <c r="C25" s="455"/>
+      <c r="D25" s="455"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -10627,8 +10595,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="449"/>
-      <c r="D26" s="448"/>
+      <c r="C26" s="455"/>
+      <c r="D26" s="454"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -10640,7 +10608,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="449"/>
+      <c r="C27" s="455"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -10655,7 +10623,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="449"/>
+      <c r="C28" s="455"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -10670,8 +10638,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="449"/>
-      <c r="D29" s="458" t="s">
+      <c r="C29" s="455"/>
+      <c r="D29" s="464" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -10685,8 +10653,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="449"/>
-      <c r="D30" s="449"/>
+      <c r="C30" s="455"/>
+      <c r="D30" s="455"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -10698,8 +10666,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="448"/>
-      <c r="D31" s="448"/>
+      <c r="C31" s="454"/>
+      <c r="D31" s="454"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -10711,13 +10679,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="447" t="s">
+      <c r="C32" s="453" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="454" t="s">
+      <c r="D32" s="460" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="455"/>
+      <c r="E32" s="461"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -10725,11 +10693,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="449"/>
-      <c r="D33" s="454" t="s">
+      <c r="C33" s="455"/>
+      <c r="D33" s="460" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="455"/>
+      <c r="E33" s="461"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -10738,11 +10706,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="448"/>
-      <c r="D34" s="454" t="s">
+      <c r="C34" s="454"/>
+      <c r="D34" s="460" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="455"/>
+      <c r="E34" s="461"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -14095,7 +14063,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="461">
+      <c r="C71" s="467">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
@@ -14115,7 +14083,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="449"/>
+      <c r="C72" s="455"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14131,7 +14099,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="448"/>
+      <c r="C73" s="454"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17158,7 +17126,7 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="2.6640625" style="306" customWidth="1"/>
@@ -17619,10 +17587,10 @@
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
       <c r="C20" s="354" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="D20" s="355" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="E20" s="356" t="s">
         <v>897</v>
@@ -17637,7 +17605,7 @@
         <v>905</v>
       </c>
       <c r="I20" s="360" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="J20" s="305"/>
     </row>
@@ -17699,13 +17667,13 @@
       <c r="I24" s="305"/>
       <c r="J24" s="305"/>
     </row>
-    <row r="25" spans="1:10" ht="16.5" customHeight="1">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="312"/>
       <c r="B25" s="304"/>
-      <c r="C25" s="365" t="s">
+      <c r="C25" s="366" t="s">
         <v>935</v>
       </c>
-      <c r="D25" s="366" t="s">
+      <c r="D25" s="364" t="s">
         <v>936</v>
       </c>
       <c r="E25" s="312"/>
@@ -17715,14 +17683,14 @@
       <c r="I25" s="305"/>
       <c r="J25" s="305"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1">
+    <row r="26" spans="1:10" ht="16.5" customHeight="1">
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
-      <c r="C26" s="367" t="s">
+      <c r="C26" s="366" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D26" s="365" t="s">
         <v>937</v>
-      </c>
-      <c r="D26" s="364" t="s">
-        <v>938</v>
       </c>
       <c r="E26" s="312"/>
       <c r="F26" s="312"/>
@@ -17731,14 +17699,14 @@
       <c r="I26" s="305"/>
       <c r="J26" s="305"/>
     </row>
-    <row r="27" spans="1:10" ht="16.5" customHeight="1">
+    <row r="27" spans="1:10" ht="17.25" customHeight="1">
       <c r="A27" s="312"/>
       <c r="B27" s="304"/>
-      <c r="C27" s="367" t="s">
+      <c r="C27" s="366" t="s">
+        <v>938</v>
+      </c>
+      <c r="D27" s="365" t="s">
         <v>939</v>
-      </c>
-      <c r="D27" s="366" t="s">
-        <v>940</v>
       </c>
       <c r="E27" s="312"/>
       <c r="F27" s="312"/>
@@ -17747,14 +17715,14 @@
       <c r="I27" s="305"/>
       <c r="J27" s="305"/>
     </row>
-    <row r="28" spans="1:10" ht="17.25" customHeight="1">
+    <row r="28" spans="1:10" ht="14.25" customHeight="1">
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
-      <c r="C28" s="367" t="s">
-        <v>941</v>
-      </c>
-      <c r="D28" s="366" t="s">
-        <v>942</v>
+      <c r="C28" s="471" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D28" s="365" t="s">
+        <v>940</v>
       </c>
       <c r="E28" s="312"/>
       <c r="F28" s="312"/>
@@ -17763,15 +17731,11 @@
       <c r="I28" s="305"/>
       <c r="J28" s="305"/>
     </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1">
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="312"/>
       <c r="B29" s="304"/>
-      <c r="C29" s="367" t="s">
-        <v>943</v>
-      </c>
-      <c r="D29" s="366" t="s">
-        <v>944</v>
-      </c>
+      <c r="C29" s="312"/>
+      <c r="D29" s="312"/>
       <c r="E29" s="312"/>
       <c r="F29" s="312"/>
       <c r="G29" s="312"/>
@@ -17781,9 +17745,11 @@
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="312"/>
-      <c r="B30" s="304"/>
+      <c r="B30" s="304" t="s">
+        <v>670</v>
+      </c>
       <c r="C30" s="312"/>
-      <c r="D30" s="312"/>
+      <c r="D30" s="367"/>
       <c r="E30" s="312"/>
       <c r="F30" s="312"/>
       <c r="G30" s="312"/>
@@ -17793,11 +17759,13 @@
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="312"/>
-      <c r="B31" s="304" t="s">
-        <v>670</v>
-      </c>
-      <c r="C31" s="312"/>
-      <c r="D31" s="368"/>
+      <c r="B31" s="304"/>
+      <c r="C31" s="368" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="369" t="s">
+        <v>682</v>
+      </c>
       <c r="E31" s="312"/>
       <c r="F31" s="312"/>
       <c r="G31" s="312"/>
@@ -17808,11 +17776,11 @@
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
-      <c r="C32" s="369" t="s">
-        <v>21</v>
+      <c r="C32" s="445" t="s">
+        <v>1037</v>
       </c>
       <c r="D32" s="370" t="s">
-        <v>682</v>
+        <v>941</v>
       </c>
       <c r="E32" s="312"/>
       <c r="F32" s="312"/>
@@ -17824,11 +17792,11 @@
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="312"/>
       <c r="B33" s="304"/>
-      <c r="C33" s="464" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D33" s="371" t="s">
-        <v>945</v>
+      <c r="C33" s="371" t="s">
+        <v>942</v>
+      </c>
+      <c r="D33" s="370" t="s">
+        <v>943</v>
       </c>
       <c r="E33" s="312"/>
       <c r="F33" s="312"/>
@@ -17840,11 +17808,11 @@
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="312"/>
       <c r="B34" s="304"/>
-      <c r="C34" s="372" t="s">
-        <v>946</v>
-      </c>
-      <c r="D34" s="371" t="s">
-        <v>947</v>
+      <c r="C34" s="371" t="s">
+        <v>901</v>
+      </c>
+      <c r="D34" s="370" t="s">
+        <v>944</v>
       </c>
       <c r="E34" s="312"/>
       <c r="F34" s="312"/>
@@ -17856,11 +17824,11 @@
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
-      <c r="C35" s="372" t="s">
-        <v>901</v>
-      </c>
-      <c r="D35" s="371" t="s">
-        <v>948</v>
+      <c r="C35" s="371" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D35" s="370" t="s">
+        <v>945</v>
       </c>
       <c r="E35" s="312"/>
       <c r="F35" s="312"/>
@@ -17872,11 +17840,11 @@
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
-      <c r="C36" s="372" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D36" s="371" t="s">
-        <v>949</v>
+      <c r="C36" s="371" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D36" s="372" t="s">
+        <v>946</v>
       </c>
       <c r="E36" s="312"/>
       <c r="F36" s="312"/>
@@ -17888,11 +17856,11 @@
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
-      <c r="C37" s="372" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D37" s="373" t="s">
-        <v>950</v>
+      <c r="C37" s="371" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D37" s="370" t="s">
+        <v>947</v>
       </c>
       <c r="E37" s="312"/>
       <c r="F37" s="312"/>
@@ -17904,11 +17872,11 @@
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
-      <c r="C38" s="372" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D38" s="371" t="s">
-        <v>951</v>
+      <c r="C38" s="371" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D38" s="370" t="s">
+        <v>948</v>
       </c>
       <c r="E38" s="312"/>
       <c r="F38" s="312"/>
@@ -17920,11 +17888,11 @@
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
-      <c r="C39" s="372" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D39" s="371" t="s">
-        <v>952</v>
+      <c r="C39" s="446" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D39" s="370" t="s">
+        <v>949</v>
       </c>
       <c r="E39" s="312"/>
       <c r="F39" s="312"/>
@@ -17936,11 +17904,11 @@
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
-      <c r="C40" s="465" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D40" s="371" t="s">
-        <v>953</v>
+      <c r="C40" s="371" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D40" s="372" t="s">
+        <v>950</v>
       </c>
       <c r="E40" s="312"/>
       <c r="F40" s="312"/>
@@ -17952,11 +17920,11 @@
     <row r="41" spans="1:10" ht="15.75" customHeight="1">
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
-      <c r="C41" s="372" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D41" s="373" t="s">
-        <v>954</v>
+      <c r="C41" s="371" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D41" s="370" t="s">
+        <v>951</v>
       </c>
       <c r="E41" s="312"/>
       <c r="F41" s="312"/>
@@ -17968,11 +17936,11 @@
     <row r="42" spans="1:10" ht="15.75" customHeight="1">
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
-      <c r="C42" s="372" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D42" s="371" t="s">
-        <v>955</v>
+      <c r="C42" s="446" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D42" s="373" t="s">
+        <v>952</v>
       </c>
       <c r="E42" s="312"/>
       <c r="F42" s="312"/>
@@ -17984,11 +17952,11 @@
     <row r="43" spans="1:10" ht="15.75" customHeight="1">
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
-      <c r="C43" s="465" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D43" s="374" t="s">
-        <v>956</v>
+      <c r="C43" s="371" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D43" s="370" t="s">
+        <v>953</v>
       </c>
       <c r="E43" s="312"/>
       <c r="F43" s="312"/>
@@ -18000,11 +17968,11 @@
     <row r="44" spans="1:10" ht="15.75" customHeight="1">
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
-      <c r="C44" s="372" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D44" s="371" t="s">
-        <v>957</v>
+      <c r="C44" s="371" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D44" s="370" t="s">
+        <v>954</v>
       </c>
       <c r="E44" s="312"/>
       <c r="F44" s="312"/>
@@ -18016,11 +17984,11 @@
     <row r="45" spans="1:10" ht="15.75" customHeight="1">
       <c r="A45" s="312"/>
       <c r="B45" s="304"/>
-      <c r="C45" s="372" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D45" s="371" t="s">
-        <v>958</v>
+      <c r="C45" s="447" t="s">
+        <v>929</v>
+      </c>
+      <c r="D45" s="448" t="s">
+        <v>955</v>
       </c>
       <c r="E45" s="312"/>
       <c r="F45" s="312"/>
@@ -18032,11 +18000,11 @@
     <row r="46" spans="1:10" ht="15.75" customHeight="1">
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
-      <c r="C46" s="466" t="s">
-        <v>929</v>
-      </c>
-      <c r="D46" s="467" t="s">
-        <v>959</v>
+      <c r="C46" s="449" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D46" s="450" t="s">
+        <v>1048</v>
       </c>
       <c r="E46" s="312"/>
       <c r="F46" s="312"/>
@@ -18048,14 +18016,10 @@
     <row r="47" spans="1:10" ht="15.75" customHeight="1">
       <c r="A47" s="312"/>
       <c r="B47" s="304"/>
-      <c r="C47" s="468" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D47" s="469" t="s">
-        <v>1055</v>
-      </c>
+      <c r="C47" s="312"/>
+      <c r="D47" s="312"/>
       <c r="E47" s="312"/>
-      <c r="F47" s="312"/>
+      <c r="F47" s="367"/>
       <c r="G47" s="312"/>
       <c r="H47" s="312"/>
       <c r="I47" s="305"/>
@@ -18063,11 +18027,13 @@
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
       <c r="A48" s="312"/>
-      <c r="B48" s="304"/>
+      <c r="B48" s="304" t="s">
+        <v>113</v>
+      </c>
       <c r="C48" s="312"/>
       <c r="D48" s="312"/>
       <c r="E48" s="312"/>
-      <c r="F48" s="368"/>
+      <c r="F48" s="367"/>
       <c r="G48" s="312"/>
       <c r="H48" s="312"/>
       <c r="I48" s="305"/>
@@ -18075,14 +18041,17 @@
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1">
       <c r="A49" s="312"/>
-      <c r="B49" s="304" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="312"/>
-      <c r="D49" s="312"/>
-      <c r="E49" s="312"/>
-      <c r="F49" s="368"/>
-      <c r="G49" s="312"/>
+      <c r="B49" s="304"/>
+      <c r="C49" s="374" t="s">
+        <v>732</v>
+      </c>
+      <c r="D49" s="368" t="s">
+        <v>734</v>
+      </c>
+      <c r="E49" s="368" t="s">
+        <v>736</v>
+      </c>
+      <c r="F49" s="375"/>
       <c r="H49" s="312"/>
       <c r="I49" s="305"/>
       <c r="J49" s="305"/>
@@ -18090,16 +18059,16 @@
     <row r="50" spans="1:10" ht="15.75" customHeight="1">
       <c r="A50" s="312"/>
       <c r="B50" s="304"/>
-      <c r="C50" s="375" t="s">
-        <v>732</v>
-      </c>
-      <c r="D50" s="369" t="s">
-        <v>734</v>
-      </c>
-      <c r="E50" s="369" t="s">
-        <v>736</v>
-      </c>
-      <c r="F50" s="376"/>
+      <c r="C50" s="376" t="s">
+        <v>956</v>
+      </c>
+      <c r="D50" s="377" t="s">
+        <v>957</v>
+      </c>
+      <c r="E50" s="378" t="s">
+        <v>958</v>
+      </c>
+      <c r="F50" s="379"/>
       <c r="H50" s="312"/>
       <c r="I50" s="305"/>
       <c r="J50" s="305"/>
@@ -18107,16 +18076,14 @@
     <row r="51" spans="1:10" ht="15.75" customHeight="1">
       <c r="A51" s="312"/>
       <c r="B51" s="304"/>
-      <c r="C51" s="377" t="s">
+      <c r="C51" s="380"/>
+      <c r="D51" s="381" t="s">
+        <v>959</v>
+      </c>
+      <c r="E51" s="382" t="s">
         <v>960</v>
       </c>
-      <c r="D51" s="378" t="s">
-        <v>961</v>
-      </c>
-      <c r="E51" s="379" t="s">
-        <v>962</v>
-      </c>
-      <c r="F51" s="380"/>
+      <c r="F51" s="383"/>
       <c r="H51" s="312"/>
       <c r="I51" s="305"/>
       <c r="J51" s="305"/>
@@ -18124,14 +18091,16 @@
     <row r="52" spans="1:10" ht="15.75" customHeight="1">
       <c r="A52" s="312"/>
       <c r="B52" s="304"/>
-      <c r="C52" s="381"/>
-      <c r="D52" s="382" t="s">
-        <v>963</v>
-      </c>
-      <c r="E52" s="383" t="s">
-        <v>964</v>
-      </c>
-      <c r="F52" s="384"/>
+      <c r="C52" s="376" t="s">
+        <v>961</v>
+      </c>
+      <c r="D52" s="377" t="s">
+        <v>957</v>
+      </c>
+      <c r="E52" s="378" t="s">
+        <v>958</v>
+      </c>
+      <c r="F52" s="379"/>
       <c r="H52" s="312"/>
       <c r="I52" s="305"/>
       <c r="J52" s="305"/>
@@ -18139,16 +18108,14 @@
     <row r="53" spans="1:10" ht="15.75" customHeight="1">
       <c r="A53" s="312"/>
       <c r="B53" s="304"/>
-      <c r="C53" s="377" t="s">
-        <v>965</v>
-      </c>
-      <c r="D53" s="378" t="s">
-        <v>961</v>
-      </c>
-      <c r="E53" s="379" t="s">
-        <v>962</v>
-      </c>
-      <c r="F53" s="380"/>
+      <c r="C53" s="380"/>
+      <c r="D53" s="381" t="s">
+        <v>959</v>
+      </c>
+      <c r="E53" s="382" t="s">
+        <v>960</v>
+      </c>
+      <c r="F53" s="383"/>
       <c r="H53" s="312"/>
       <c r="I53" s="305"/>
       <c r="J53" s="305"/>
@@ -18156,14 +18123,16 @@
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
       <c r="A54" s="312"/>
       <c r="B54" s="304"/>
-      <c r="C54" s="381"/>
-      <c r="D54" s="382" t="s">
+      <c r="C54" s="384" t="s">
+        <v>962</v>
+      </c>
+      <c r="D54" s="381" t="s">
         <v>963</v>
       </c>
-      <c r="E54" s="383" t="s">
+      <c r="E54" s="385" t="s">
         <v>964</v>
       </c>
-      <c r="F54" s="384"/>
+      <c r="F54" s="383"/>
       <c r="H54" s="312"/>
       <c r="I54" s="305"/>
       <c r="J54" s="305"/>
@@ -18171,16 +18140,14 @@
     <row r="55" spans="1:10" ht="15.75" customHeight="1">
       <c r="A55" s="312"/>
       <c r="B55" s="304"/>
-      <c r="C55" s="385" t="s">
-        <v>966</v>
-      </c>
-      <c r="D55" s="382" t="s">
-        <v>967</v>
-      </c>
-      <c r="E55" s="386" t="s">
-        <v>968</v>
-      </c>
-      <c r="F55" s="384"/>
+      <c r="C55" s="376"/>
+      <c r="D55" s="386" t="s">
+        <v>957</v>
+      </c>
+      <c r="E55" s="385" t="s">
+        <v>965</v>
+      </c>
+      <c r="F55" s="383"/>
       <c r="H55" s="312"/>
       <c r="I55" s="305"/>
       <c r="J55" s="305"/>
@@ -18188,14 +18155,14 @@
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
       <c r="A56" s="312"/>
       <c r="B56" s="304"/>
-      <c r="C56" s="377"/>
-      <c r="D56" s="387" t="s">
-        <v>961</v>
-      </c>
-      <c r="E56" s="386" t="s">
-        <v>969</v>
-      </c>
-      <c r="F56" s="384"/>
+      <c r="C56" s="387"/>
+      <c r="D56" s="381" t="s">
+        <v>959</v>
+      </c>
+      <c r="E56" s="388" t="s">
+        <v>966</v>
+      </c>
+      <c r="F56" s="383"/>
       <c r="H56" s="312"/>
       <c r="I56" s="305"/>
       <c r="J56" s="305"/>
@@ -18203,14 +18170,16 @@
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
       <c r="A57" s="312"/>
       <c r="B57" s="304"/>
-      <c r="C57" s="388"/>
-      <c r="D57" s="382" t="s">
-        <v>963</v>
-      </c>
-      <c r="E57" s="389" t="s">
-        <v>970</v>
-      </c>
-      <c r="F57" s="384"/>
+      <c r="C57" s="384" t="s">
+        <v>967</v>
+      </c>
+      <c r="D57" s="377" t="s">
+        <v>968</v>
+      </c>
+      <c r="E57" s="385" t="s">
+        <v>969</v>
+      </c>
+      <c r="F57" s="383"/>
       <c r="H57" s="312"/>
       <c r="I57" s="305"/>
       <c r="J57" s="305"/>
@@ -18218,16 +18187,14 @@
     <row r="58" spans="1:10" ht="15.75" customHeight="1">
       <c r="A58" s="312"/>
       <c r="B58" s="304"/>
-      <c r="C58" s="385" t="s">
+      <c r="C58" s="376"/>
+      <c r="D58" s="386" t="s">
+        <v>970</v>
+      </c>
+      <c r="E58" s="388" t="s">
         <v>971</v>
       </c>
-      <c r="D58" s="378" t="s">
-        <v>972</v>
-      </c>
-      <c r="E58" s="386" t="s">
-        <v>973</v>
-      </c>
-      <c r="F58" s="384"/>
+      <c r="F58" s="383"/>
       <c r="H58" s="312"/>
       <c r="I58" s="305"/>
       <c r="J58" s="305"/>
@@ -18235,14 +18202,14 @@
     <row r="59" spans="1:10" ht="15.75" customHeight="1">
       <c r="A59" s="312"/>
       <c r="B59" s="304"/>
-      <c r="C59" s="377"/>
-      <c r="D59" s="387" t="s">
-        <v>974</v>
-      </c>
-      <c r="E59" s="389" t="s">
-        <v>975</v>
-      </c>
-      <c r="F59" s="384"/>
+      <c r="C59" s="376"/>
+      <c r="D59" s="377" t="s">
+        <v>972</v>
+      </c>
+      <c r="E59" s="376" t="s">
+        <v>973</v>
+      </c>
+      <c r="F59" s="383"/>
       <c r="H59" s="312"/>
       <c r="I59" s="305"/>
       <c r="J59" s="305"/>
@@ -18250,14 +18217,14 @@
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="312"/>
       <c r="B60" s="304"/>
-      <c r="C60" s="377"/>
-      <c r="D60" s="378" t="s">
-        <v>976</v>
-      </c>
-      <c r="E60" s="377" t="s">
-        <v>977</v>
-      </c>
-      <c r="F60" s="384"/>
+      <c r="C60" s="376"/>
+      <c r="D60" s="377" t="s">
+        <v>974</v>
+      </c>
+      <c r="E60" s="386" t="s">
+        <v>975</v>
+      </c>
+      <c r="F60" s="383"/>
       <c r="H60" s="312"/>
       <c r="I60" s="305"/>
       <c r="J60" s="305"/>
@@ -18265,14 +18232,14 @@
     <row r="61" spans="1:10" ht="15.75" customHeight="1">
       <c r="A61" s="312"/>
       <c r="B61" s="304"/>
-      <c r="C61" s="377"/>
-      <c r="D61" s="378" t="s">
-        <v>978</v>
-      </c>
-      <c r="E61" s="387" t="s">
-        <v>979</v>
-      </c>
-      <c r="F61" s="384"/>
+      <c r="C61" s="380"/>
+      <c r="D61" s="377" t="s">
+        <v>716</v>
+      </c>
+      <c r="E61" s="385" t="s">
+        <v>976</v>
+      </c>
+      <c r="F61" s="379"/>
       <c r="H61" s="312"/>
       <c r="I61" s="305"/>
       <c r="J61" s="305"/>
@@ -18280,14 +18247,16 @@
     <row r="62" spans="1:10" ht="15.75" customHeight="1">
       <c r="A62" s="312"/>
       <c r="B62" s="304"/>
-      <c r="C62" s="381"/>
-      <c r="D62" s="378" t="s">
-        <v>716</v>
-      </c>
-      <c r="E62" s="386" t="s">
-        <v>980</v>
-      </c>
-      <c r="F62" s="380"/>
+      <c r="C62" s="384" t="s">
+        <v>977</v>
+      </c>
+      <c r="D62" s="389" t="s">
+        <v>978</v>
+      </c>
+      <c r="E62" s="390" t="s">
+        <v>979</v>
+      </c>
+      <c r="F62" s="383"/>
       <c r="H62" s="312"/>
       <c r="I62" s="305"/>
       <c r="J62" s="305"/>
@@ -18295,16 +18264,14 @@
     <row r="63" spans="1:10" ht="15.75" customHeight="1">
       <c r="A63" s="312"/>
       <c r="B63" s="304"/>
-      <c r="C63" s="385" t="s">
+      <c r="C63" s="376"/>
+      <c r="D63" s="381" t="s">
+        <v>980</v>
+      </c>
+      <c r="E63" s="391" t="s">
         <v>981</v>
       </c>
-      <c r="D63" s="390" t="s">
-        <v>982</v>
-      </c>
-      <c r="E63" s="391" t="s">
-        <v>983</v>
-      </c>
-      <c r="F63" s="384"/>
+      <c r="F63" s="383"/>
       <c r="H63" s="312"/>
       <c r="I63" s="305"/>
       <c r="J63" s="305"/>
@@ -18312,14 +18279,14 @@
     <row r="64" spans="1:10" ht="15.75" customHeight="1">
       <c r="A64" s="312"/>
       <c r="B64" s="304"/>
-      <c r="C64" s="377"/>
-      <c r="D64" s="382" t="s">
-        <v>984</v>
-      </c>
-      <c r="E64" s="392" t="s">
-        <v>985</v>
-      </c>
-      <c r="F64" s="384"/>
+      <c r="C64" s="392"/>
+      <c r="D64" s="393" t="s">
+        <v>982</v>
+      </c>
+      <c r="E64" s="394" t="s">
+        <v>973</v>
+      </c>
+      <c r="F64" s="383"/>
       <c r="H64" s="312"/>
       <c r="I64" s="305"/>
       <c r="J64" s="305"/>
@@ -18327,14 +18294,14 @@
     <row r="65" spans="1:10" ht="15.75" customHeight="1">
       <c r="A65" s="312"/>
       <c r="B65" s="304"/>
-      <c r="C65" s="393"/>
-      <c r="D65" s="394" t="s">
-        <v>986</v>
-      </c>
-      <c r="E65" s="395" t="s">
-        <v>977</v>
-      </c>
-      <c r="F65" s="384"/>
+      <c r="C65" s="395"/>
+      <c r="D65" s="381" t="s">
+        <v>983</v>
+      </c>
+      <c r="E65" s="396" t="s">
+        <v>975</v>
+      </c>
+      <c r="F65" s="383"/>
       <c r="H65" s="312"/>
       <c r="I65" s="305"/>
       <c r="J65" s="305"/>
@@ -18342,14 +18309,14 @@
     <row r="66" spans="1:10" ht="15.75" customHeight="1">
       <c r="A66" s="312"/>
       <c r="B66" s="304"/>
-      <c r="C66" s="396"/>
-      <c r="D66" s="382" t="s">
-        <v>987</v>
-      </c>
-      <c r="E66" s="397" t="s">
-        <v>979</v>
-      </c>
-      <c r="F66" s="384"/>
+      <c r="C66" s="397"/>
+      <c r="D66" s="377" t="s">
+        <v>716</v>
+      </c>
+      <c r="E66" s="377" t="s">
+        <v>976</v>
+      </c>
+      <c r="F66" s="398"/>
       <c r="H66" s="312"/>
       <c r="I66" s="305"/>
       <c r="J66" s="305"/>
@@ -18357,14 +18324,16 @@
     <row r="67" spans="1:10" ht="15.75" customHeight="1">
       <c r="A67" s="312"/>
       <c r="B67" s="304"/>
-      <c r="C67" s="398"/>
-      <c r="D67" s="378" t="s">
-        <v>716</v>
-      </c>
-      <c r="E67" s="378" t="s">
-        <v>980</v>
-      </c>
-      <c r="F67" s="399"/>
+      <c r="C67" s="399" t="s">
+        <v>984</v>
+      </c>
+      <c r="D67" s="400" t="s">
+        <v>985</v>
+      </c>
+      <c r="E67" s="400" t="s">
+        <v>986</v>
+      </c>
+      <c r="F67" s="398"/>
       <c r="H67" s="312"/>
       <c r="I67" s="305"/>
       <c r="J67" s="305"/>
@@ -18372,16 +18341,14 @@
     <row r="68" spans="1:10" ht="15.75" customHeight="1">
       <c r="A68" s="312"/>
       <c r="B68" s="304"/>
-      <c r="C68" s="400" t="s">
+      <c r="C68" s="395"/>
+      <c r="D68" s="400" t="s">
+        <v>987</v>
+      </c>
+      <c r="E68" s="400" t="s">
         <v>988</v>
       </c>
-      <c r="D68" s="401" t="s">
-        <v>989</v>
-      </c>
-      <c r="E68" s="401" t="s">
-        <v>990</v>
-      </c>
-      <c r="F68" s="399"/>
+      <c r="F68" s="398"/>
       <c r="H68" s="312"/>
       <c r="I68" s="305"/>
       <c r="J68" s="305"/>
@@ -18389,14 +18356,14 @@
     <row r="69" spans="1:10" ht="15.75" customHeight="1">
       <c r="A69" s="312"/>
       <c r="B69" s="304"/>
-      <c r="C69" s="396"/>
-      <c r="D69" s="401" t="s">
-        <v>991</v>
-      </c>
-      <c r="E69" s="401" t="s">
-        <v>992</v>
-      </c>
-      <c r="F69" s="399"/>
+      <c r="C69" s="395"/>
+      <c r="D69" s="400" t="s">
+        <v>989</v>
+      </c>
+      <c r="E69" s="400" t="s">
+        <v>990</v>
+      </c>
+      <c r="F69" s="398"/>
       <c r="H69" s="312"/>
       <c r="I69" s="305"/>
       <c r="J69" s="305"/>
@@ -18404,14 +18371,14 @@
     <row r="70" spans="1:10" ht="15.75" customHeight="1">
       <c r="A70" s="312"/>
       <c r="B70" s="304"/>
-      <c r="C70" s="396"/>
-      <c r="D70" s="401" t="s">
-        <v>993</v>
-      </c>
-      <c r="E70" s="401" t="s">
-        <v>994</v>
-      </c>
-      <c r="F70" s="399"/>
+      <c r="C70" s="395"/>
+      <c r="D70" s="400" t="s">
+        <v>991</v>
+      </c>
+      <c r="E70" s="400" t="s">
+        <v>986</v>
+      </c>
+      <c r="F70" s="398"/>
       <c r="H70" s="312"/>
       <c r="I70" s="305"/>
       <c r="J70" s="305"/>
@@ -18419,114 +18386,99 @@
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
       <c r="A71" s="312"/>
       <c r="B71" s="304"/>
-      <c r="C71" s="396"/>
+      <c r="C71" s="395"/>
       <c r="D71" s="401" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E71" s="401" t="s">
-        <v>990</v>
-      </c>
-      <c r="F71" s="399"/>
+        <v>993</v>
+      </c>
+      <c r="F71" s="398"/>
       <c r="H71" s="312"/>
       <c r="I71" s="305"/>
       <c r="J71" s="305"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A72" s="312"/>
-      <c r="B72" s="304"/>
-      <c r="C72" s="396"/>
-      <c r="D72" s="402" t="s">
-        <v>996</v>
-      </c>
-      <c r="E72" s="402" t="s">
-        <v>997</v>
-      </c>
-      <c r="F72" s="399"/>
-      <c r="H72" s="312"/>
+      <c r="A72" s="305"/>
+      <c r="B72" s="305"/>
+      <c r="C72" s="402" t="s">
+        <v>994</v>
+      </c>
+      <c r="D72" s="403" t="s">
+        <v>987</v>
+      </c>
+      <c r="E72" s="404" t="s">
+        <v>995</v>
+      </c>
+      <c r="F72" s="398"/>
+      <c r="G72" s="305"/>
+      <c r="H72" s="305"/>
       <c r="I72" s="305"/>
       <c r="J72" s="305"/>
     </row>
-    <row r="73" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A73" s="305"/>
-      <c r="B73" s="305"/>
-      <c r="C73" s="403" t="s">
+    <row r="73" spans="1:10" ht="15" customHeight="1">
+      <c r="C73" s="405"/>
+      <c r="D73" s="406" t="s">
+        <v>996</v>
+      </c>
+      <c r="E73" s="407" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="15" customHeight="1">
+      <c r="C74" s="405"/>
+      <c r="D74" s="406" t="s">
+        <v>997</v>
+      </c>
+      <c r="E74" s="407" t="s">
         <v>998</v>
       </c>
-      <c r="D73" s="404" t="s">
-        <v>991</v>
-      </c>
-      <c r="E73" s="405" t="s">
+    </row>
+    <row r="75" spans="1:10" ht="15" customHeight="1">
+      <c r="C75" s="408"/>
+      <c r="D75" s="406" t="s">
         <v>999</v>
       </c>
-      <c r="F73" s="399"/>
-      <c r="G73" s="305"/>
-      <c r="H73" s="305"/>
-      <c r="I73" s="305"/>
-      <c r="J73" s="305"/>
-    </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1">
-      <c r="C74" s="406"/>
-      <c r="D74" s="407" t="s">
+      <c r="E75" s="404" t="s">
         <v>1000</v>
       </c>
-      <c r="E74" s="408" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1">
-      <c r="C75" s="406"/>
-      <c r="D75" s="407" t="s">
+    </row>
+    <row r="76" spans="1:10" ht="15" customHeight="1">
+      <c r="C76" s="402" t="s">
         <v>1001</v>
       </c>
-      <c r="E75" s="408" t="s">
+      <c r="D76" s="403" t="s">
+        <v>987</v>
+      </c>
+      <c r="E76" s="404" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1">
-      <c r="C76" s="409"/>
-      <c r="D76" s="407" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E76" s="405" t="s">
-        <v>1004</v>
-      </c>
-    </row>
     <row r="77" spans="1:10" ht="15" customHeight="1">
-      <c r="C77" s="403" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D77" s="404" t="s">
-        <v>991</v>
-      </c>
-      <c r="E77" s="405" t="s">
-        <v>1006</v>
+      <c r="C77" s="405"/>
+      <c r="D77" s="406" t="s">
+        <v>996</v>
+      </c>
+      <c r="E77" s="407" t="s">
+        <v>979</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1">
-      <c r="C78" s="406"/>
-      <c r="D78" s="407" t="s">
+      <c r="C78" s="405"/>
+      <c r="D78" s="406" t="s">
+        <v>997</v>
+      </c>
+      <c r="E78" s="407" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="15" customHeight="1">
+      <c r="C79" s="408"/>
+      <c r="D79" s="406" t="s">
+        <v>999</v>
+      </c>
+      <c r="E79" s="404" t="s">
         <v>1000</v>
-      </c>
-      <c r="E78" s="408" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1">
-      <c r="C79" s="406"/>
-      <c r="D79" s="407" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E79" s="408" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1">
-      <c r="C80" s="409"/>
-      <c r="D80" s="407" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E80" s="405" t="s">
-        <v>1004</v>
       </c>
     </row>
   </sheetData>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9056FD1-7624-5E4A-A15B-515B1C7FE24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ED9D55-303E-9943-8759-B5073D7306B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ターム内容" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="1059">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -5106,9 +5106,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>attendance_id</t>
-  </si>
-  <si>
     <t>attendance_records.id</t>
     <phoneticPr fontId="80"/>
   </si>
@@ -5408,6 +5405,10 @@
   </si>
   <si>
     <t>ProposalBreak.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>attendance_record_id</t>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -6030,7 +6031,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6130,12 +6131,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
         <bgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC0504D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7097,7 +7104,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="472">
+  <cellXfs count="474">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8261,11 +8268,25 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8274,30 +8295,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -8305,6 +8314,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC0504D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -8394,22 +8408,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>512658</xdr:colOff>
+      <xdr:colOff>815596</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>139816</xdr:rowOff>
+      <xdr:rowOff>116514</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>5487797</xdr:colOff>
+      <xdr:colOff>5790064</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>184961</xdr:rowOff>
+      <xdr:rowOff>61520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5081EB4E-F90D-CAD1-BCD5-A940EEFEDF6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A673AACF-707B-82A1-DC6C-D6EA2855192B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8425,8 +8439,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8377337" y="1304954"/>
-          <a:ext cx="4975139" cy="10158539"/>
+          <a:off x="8680275" y="1281652"/>
+          <a:ext cx="4974468" cy="10058400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9019,13 +9033,13 @@
       <c r="B13" s="367"/>
       <c r="C13" s="421"/>
       <c r="D13" s="440" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E13" s="451" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F13" s="451" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G13" s="394"/>
       <c r="H13" s="394"/>
@@ -9041,13 +9055,13 @@
       <c r="B14" s="367"/>
       <c r="C14" s="421"/>
       <c r="D14" s="440" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E14" s="394" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F14" s="394" t="s">
         <v>1051</v>
-      </c>
-      <c r="F14" s="394" t="s">
-        <v>1052</v>
       </c>
       <c r="G14" s="394"/>
       <c r="H14" s="394"/>
@@ -9220,7 +9234,7 @@
         <v>999</v>
       </c>
       <c r="F23" s="451" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G23" s="394"/>
       <c r="H23" s="394"/>
@@ -9290,7 +9304,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="426" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E27" s="418"/>
       <c r="F27" s="418"/>
@@ -9329,8 +9343,8 @@
       <c r="D29" s="312" t="s">
         <v>1014</v>
       </c>
-      <c r="E29" s="394" t="s">
-        <v>1020</v>
+      <c r="E29" s="472" t="s">
+        <v>1058</v>
       </c>
       <c r="F29" s="394" t="s">
         <v>1004</v>
@@ -9341,7 +9355,7 @@
         <v>710</v>
       </c>
       <c r="J29" s="423" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
@@ -9352,7 +9366,7 @@
       <c r="C30" s="427"/>
       <c r="D30" s="304"/>
       <c r="E30" s="394" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F30" s="394" t="s">
         <v>1017</v>
@@ -9369,7 +9383,7 @@
       <c r="B31" s="398"/>
       <c r="C31" s="427"/>
       <c r="E31" s="394" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F31" s="394" t="s">
         <v>1017</v>
@@ -9421,13 +9435,13 @@
       <c r="C34" s="428">
         <v>4</v>
       </c>
-      <c r="D34" s="468" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E34" s="469"/>
-      <c r="F34" s="469"/>
-      <c r="G34" s="469"/>
-      <c r="H34" s="469"/>
+      <c r="D34" s="454" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E34" s="455"/>
+      <c r="F34" s="455"/>
+      <c r="G34" s="455"/>
+      <c r="H34" s="455"/>
       <c r="I34" s="418"/>
       <c r="J34" s="419"/>
       <c r="K34" s="305"/>
@@ -9459,10 +9473,10 @@
       <c r="B36" s="398"/>
       <c r="C36" s="427"/>
       <c r="D36" s="306" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E36" s="394" t="s">
-        <v>1020</v>
+        <v>1024</v>
+      </c>
+      <c r="E36" s="472" t="s">
+        <v>1058</v>
       </c>
       <c r="F36" s="363" t="s">
         <v>1004</v>
@@ -9473,7 +9487,7 @@
         <v>710</v>
       </c>
       <c r="J36" s="423" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
@@ -9509,9 +9523,7 @@
       </c>
       <c r="G38" s="394"/>
       <c r="H38" s="394"/>
-      <c r="I38" s="422" t="s">
-        <v>710</v>
-      </c>
+      <c r="I38" s="473"/>
       <c r="J38" s="423"/>
       <c r="K38" s="305"/>
       <c r="L38" s="305"/>
@@ -9524,7 +9536,7 @@
         <v>999</v>
       </c>
       <c r="F39" s="394" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G39" s="394"/>
       <c r="H39" s="394"/>
@@ -9540,13 +9552,13 @@
       <c r="B40" s="398"/>
       <c r="C40" s="427"/>
       <c r="D40" s="440" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E40" s="394" t="s">
         <v>1027</v>
       </c>
-      <c r="E40" s="394" t="s">
+      <c r="F40" s="394" t="s">
         <v>1028</v>
-      </c>
-      <c r="F40" s="394" t="s">
-        <v>1029</v>
       </c>
       <c r="G40" s="394"/>
       <c r="H40" s="394"/>
@@ -9563,7 +9575,7 @@
       <c r="C41" s="427"/>
       <c r="D41" s="440"/>
       <c r="E41" s="451" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F41" s="451" t="s">
         <v>987</v>
@@ -9619,8 +9631,8 @@
       <c r="C44" s="428">
         <v>5</v>
       </c>
-      <c r="D44" s="470" t="s">
-        <v>1057</v>
+      <c r="D44" s="471" t="s">
+        <v>1056</v>
       </c>
       <c r="E44" s="418"/>
       <c r="F44" s="418"/>
@@ -9657,10 +9669,10 @@
       <c r="B46" s="398"/>
       <c r="C46" s="427"/>
       <c r="D46" s="312" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E46" s="394" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="F46" s="394" t="s">
         <v>1004</v>
@@ -9671,7 +9683,7 @@
         <v>905</v>
       </c>
       <c r="J46" s="423" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
@@ -9681,7 +9693,7 @@
       <c r="B47" s="398"/>
       <c r="C47" s="427"/>
       <c r="E47" s="394" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F47" s="394" t="s">
         <v>1017</v>
@@ -9698,7 +9710,7 @@
       <c r="B48" s="398"/>
       <c r="C48" s="427"/>
       <c r="E48" s="394" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F48" s="394" t="s">
         <v>1017</v>
@@ -10297,11 +10309,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="456" t="s">
+      <c r="C4" s="464" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="457"/>
-      <c r="E4" s="457"/>
+      <c r="D4" s="465"/>
+      <c r="E4" s="465"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10310,13 +10322,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="462" t="s">
+      <c r="C5" s="468" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="458" t="s">
+      <c r="D5" s="466" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="459"/>
+      <c r="E5" s="467"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10325,11 +10337,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="455"/>
-      <c r="D6" s="460" t="s">
+      <c r="C6" s="461"/>
+      <c r="D6" s="456" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="461"/>
+      <c r="E6" s="457"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10338,11 +10350,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="455"/>
-      <c r="D7" s="460" t="s">
+      <c r="C7" s="461"/>
+      <c r="D7" s="456" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="461"/>
+      <c r="E7" s="457"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10351,11 +10363,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="455"/>
-      <c r="D8" s="460" t="s">
+      <c r="C8" s="461"/>
+      <c r="D8" s="456" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="461"/>
+      <c r="E8" s="457"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10364,11 +10376,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="455"/>
-      <c r="D9" s="460" t="s">
+      <c r="C9" s="461"/>
+      <c r="D9" s="456" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="461"/>
+      <c r="E9" s="457"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10377,11 +10389,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="454"/>
-      <c r="D10" s="460" t="s">
+      <c r="C10" s="462"/>
+      <c r="D10" s="456" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="461"/>
+      <c r="E10" s="457"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10390,13 +10402,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="453" t="s">
+      <c r="C11" s="463" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="460" t="s">
+      <c r="D11" s="456" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="461"/>
+      <c r="E11" s="457"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10405,11 +10417,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="454"/>
-      <c r="D12" s="460" t="s">
+      <c r="C12" s="462"/>
+      <c r="D12" s="456" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="461"/>
+      <c r="E12" s="457"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10418,13 +10430,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="453" t="s">
+      <c r="C13" s="463" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="460" t="s">
+      <c r="D13" s="456" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="461"/>
+      <c r="E13" s="457"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10433,11 +10445,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="455"/>
-      <c r="D14" s="460" t="s">
+      <c r="C14" s="461"/>
+      <c r="D14" s="456" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="461"/>
+      <c r="E14" s="457"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10446,11 +10458,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="454"/>
-      <c r="D15" s="460" t="s">
+      <c r="C15" s="462"/>
+      <c r="D15" s="456" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="461"/>
+      <c r="E15" s="457"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -10459,13 +10471,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="453" t="s">
+      <c r="C16" s="463" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="465" t="s">
+      <c r="D16" s="458" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="466"/>
+      <c r="E16" s="459"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -10474,8 +10486,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="455"/>
-      <c r="D17" s="464" t="s">
+      <c r="C17" s="461"/>
+      <c r="D17" s="460" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -10489,8 +10501,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="455"/>
-      <c r="D18" s="455"/>
+      <c r="C18" s="461"/>
+      <c r="D18" s="461"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -10502,8 +10514,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="455"/>
-      <c r="D19" s="455"/>
+      <c r="C19" s="461"/>
+      <c r="D19" s="461"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -10515,8 +10527,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="455"/>
-      <c r="D20" s="455"/>
+      <c r="C20" s="461"/>
+      <c r="D20" s="461"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -10528,8 +10540,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="455"/>
-      <c r="D21" s="454"/>
+      <c r="C21" s="461"/>
+      <c r="D21" s="462"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -10541,8 +10553,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="455"/>
-      <c r="D22" s="463" t="s">
+      <c r="C22" s="461"/>
+      <c r="D22" s="469" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -10556,8 +10568,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="455"/>
-      <c r="D23" s="455"/>
+      <c r="C23" s="461"/>
+      <c r="D23" s="461"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -10569,8 +10581,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="455"/>
-      <c r="D24" s="455"/>
+      <c r="C24" s="461"/>
+      <c r="D24" s="461"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -10582,8 +10594,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="455"/>
-      <c r="D25" s="455"/>
+      <c r="C25" s="461"/>
+      <c r="D25" s="461"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -10595,8 +10607,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="455"/>
-      <c r="D26" s="454"/>
+      <c r="C26" s="461"/>
+      <c r="D26" s="462"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -10608,7 +10620,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="455"/>
+      <c r="C27" s="461"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -10623,7 +10635,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="455"/>
+      <c r="C28" s="461"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -10638,8 +10650,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="455"/>
-      <c r="D29" s="464" t="s">
+      <c r="C29" s="461"/>
+      <c r="D29" s="460" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -10653,8 +10665,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="455"/>
-      <c r="D30" s="455"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -10666,8 +10678,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="454"/>
-      <c r="D31" s="454"/>
+      <c r="C31" s="462"/>
+      <c r="D31" s="462"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -10679,13 +10691,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="453" t="s">
+      <c r="C32" s="463" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="460" t="s">
+      <c r="D32" s="456" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="461"/>
+      <c r="E32" s="457"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -10693,11 +10705,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="455"/>
-      <c r="D33" s="460" t="s">
+      <c r="C33" s="461"/>
+      <c r="D33" s="456" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="461"/>
+      <c r="E33" s="457"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -10706,11 +10718,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="454"/>
-      <c r="D34" s="460" t="s">
+      <c r="C34" s="462"/>
+      <c r="D34" s="456" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="461"/>
+      <c r="E34" s="457"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -10727,14 +10739,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -10751,6 +10755,14 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -14063,7 +14075,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="467">
+      <c r="C71" s="470">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
@@ -14083,7 +14095,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="455"/>
+      <c r="C72" s="461"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14099,7 +14111,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="454"/>
+      <c r="C73" s="462"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17587,10 +17599,10 @@
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
       <c r="C20" s="354" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D20" s="355" t="s">
         <v>1034</v>
-      </c>
-      <c r="D20" s="355" t="s">
-        <v>1035</v>
       </c>
       <c r="E20" s="356" t="s">
         <v>897</v>
@@ -17605,7 +17617,7 @@
         <v>905</v>
       </c>
       <c r="I20" s="360" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="J20" s="305"/>
     </row>
@@ -17687,7 +17699,7 @@
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
       <c r="C26" s="366" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D26" s="365" t="s">
         <v>937</v>
@@ -17718,8 +17730,8 @@
     <row r="28" spans="1:10" ht="14.25" customHeight="1">
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
-      <c r="C28" s="471" t="s">
-        <v>1058</v>
+      <c r="C28" s="453" t="s">
+        <v>1057</v>
       </c>
       <c r="D28" s="365" t="s">
         <v>940</v>
@@ -17777,7 +17789,7 @@
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
       <c r="C32" s="445" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D32" s="370" t="s">
         <v>941</v>
@@ -17825,7 +17837,7 @@
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
       <c r="C35" s="371" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D35" s="370" t="s">
         <v>945</v>
@@ -17841,7 +17853,7 @@
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
       <c r="C36" s="371" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D36" s="372" t="s">
         <v>946</v>
@@ -17857,7 +17869,7 @@
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
       <c r="C37" s="371" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D37" s="370" t="s">
         <v>947</v>
@@ -17873,7 +17885,7 @@
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
       <c r="C38" s="371" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D38" s="370" t="s">
         <v>948</v>
@@ -17889,7 +17901,7 @@
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
       <c r="C39" s="446" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D39" s="370" t="s">
         <v>949</v>
@@ -17905,7 +17917,7 @@
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
       <c r="C40" s="371" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D40" s="372" t="s">
         <v>950</v>
@@ -17921,7 +17933,7 @@
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
       <c r="C41" s="371" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D41" s="370" t="s">
         <v>951</v>
@@ -17937,7 +17949,7 @@
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
       <c r="C42" s="446" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D42" s="373" t="s">
         <v>952</v>
@@ -17953,7 +17965,7 @@
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
       <c r="C43" s="371" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D43" s="370" t="s">
         <v>953</v>
@@ -17969,7 +17981,7 @@
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
       <c r="C44" s="371" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D44" s="370" t="s">
         <v>954</v>
@@ -18001,10 +18013,10 @@
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
       <c r="C46" s="449" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D46" s="450" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E46" s="312"/>
       <c r="F46" s="312"/>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ED9D55-303E-9943-8759-B5073D7306B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F8A432-959D-FD4A-9D01-81F7FCE6E8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1060">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -5409,6 +5409,44 @@
   </si>
   <si>
     <t>attendance_record_id</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <t>/admin/login</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>web.php</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>に直接記載</t>
+    </r>
+    <rPh sb="21" eb="25">
+      <t>チョク</t>
+    </rPh>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -7104,7 +7142,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="474">
+  <cellXfs count="477">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8269,24 +8307,14 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8295,18 +8323,37 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9343,7 +9390,7 @@
       <c r="D29" s="312" t="s">
         <v>1014</v>
       </c>
-      <c r="E29" s="472" t="s">
+      <c r="E29" s="455" t="s">
         <v>1058</v>
       </c>
       <c r="F29" s="394" t="s">
@@ -9435,13 +9482,13 @@
       <c r="C34" s="428">
         <v>4</v>
       </c>
-      <c r="D34" s="454" t="s">
+      <c r="D34" s="472" t="s">
         <v>1023</v>
       </c>
-      <c r="E34" s="455"/>
-      <c r="F34" s="455"/>
-      <c r="G34" s="455"/>
-      <c r="H34" s="455"/>
+      <c r="E34" s="473"/>
+      <c r="F34" s="473"/>
+      <c r="G34" s="473"/>
+      <c r="H34" s="473"/>
       <c r="I34" s="418"/>
       <c r="J34" s="419"/>
       <c r="K34" s="305"/>
@@ -9475,7 +9522,7 @@
       <c r="D36" s="306" t="s">
         <v>1024</v>
       </c>
-      <c r="E36" s="472" t="s">
+      <c r="E36" s="455" t="s">
         <v>1058</v>
       </c>
       <c r="F36" s="363" t="s">
@@ -9523,7 +9570,7 @@
       </c>
       <c r="G38" s="394"/>
       <c r="H38" s="394"/>
-      <c r="I38" s="473"/>
+      <c r="I38" s="456"/>
       <c r="J38" s="423"/>
       <c r="K38" s="305"/>
       <c r="L38" s="305"/>
@@ -9631,7 +9678,7 @@
       <c r="C44" s="428">
         <v>5</v>
       </c>
-      <c r="D44" s="471" t="s">
+      <c r="D44" s="454" t="s">
         <v>1056</v>
       </c>
       <c r="E44" s="418"/>
@@ -10309,11 +10356,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="464" t="s">
+      <c r="C4" s="460" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="465"/>
-      <c r="E4" s="465"/>
+      <c r="D4" s="461"/>
+      <c r="E4" s="461"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10322,13 +10369,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="468" t="s">
+      <c r="C5" s="466" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="466" t="s">
+      <c r="D5" s="462" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="467"/>
+      <c r="E5" s="463"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10337,11 +10384,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="461"/>
-      <c r="D6" s="456" t="s">
+      <c r="C6" s="459"/>
+      <c r="D6" s="464" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="457"/>
+      <c r="E6" s="465"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10350,11 +10397,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="461"/>
-      <c r="D7" s="456" t="s">
+      <c r="C7" s="459"/>
+      <c r="D7" s="464" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="457"/>
+      <c r="E7" s="465"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10363,11 +10410,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="461"/>
-      <c r="D8" s="456" t="s">
+      <c r="C8" s="459"/>
+      <c r="D8" s="464" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="457"/>
+      <c r="E8" s="465"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10376,11 +10423,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="461"/>
-      <c r="D9" s="456" t="s">
+      <c r="C9" s="459"/>
+      <c r="D9" s="464" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="457"/>
+      <c r="E9" s="465"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10389,11 +10436,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="462"/>
-      <c r="D10" s="456" t="s">
+      <c r="C10" s="458"/>
+      <c r="D10" s="464" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="457"/>
+      <c r="E10" s="465"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10402,13 +10449,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="463" t="s">
+      <c r="C11" s="457" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="456" t="s">
+      <c r="D11" s="464" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="457"/>
+      <c r="E11" s="465"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10417,11 +10464,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="462"/>
-      <c r="D12" s="456" t="s">
+      <c r="C12" s="458"/>
+      <c r="D12" s="464" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="457"/>
+      <c r="E12" s="465"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10430,13 +10477,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="463" t="s">
+      <c r="C13" s="457" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="456" t="s">
+      <c r="D13" s="464" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="457"/>
+      <c r="E13" s="465"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10445,11 +10492,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="461"/>
-      <c r="D14" s="456" t="s">
+      <c r="C14" s="459"/>
+      <c r="D14" s="464" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="457"/>
+      <c r="E14" s="465"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10458,11 +10505,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="462"/>
-      <c r="D15" s="456" t="s">
+      <c r="C15" s="458"/>
+      <c r="D15" s="464" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="457"/>
+      <c r="E15" s="465"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -10471,13 +10518,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="463" t="s">
+      <c r="C16" s="457" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="458" t="s">
+      <c r="D16" s="469" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="459"/>
+      <c r="E16" s="470"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -10486,8 +10533,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="461"/>
-      <c r="D17" s="460" t="s">
+      <c r="C17" s="459"/>
+      <c r="D17" s="468" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -10501,8 +10548,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="461"/>
-      <c r="D18" s="461"/>
+      <c r="C18" s="459"/>
+      <c r="D18" s="459"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -10514,8 +10561,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="461"/>
-      <c r="D19" s="461"/>
+      <c r="C19" s="459"/>
+      <c r="D19" s="459"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -10527,8 +10574,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="461"/>
-      <c r="D20" s="461"/>
+      <c r="C20" s="459"/>
+      <c r="D20" s="459"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -10540,8 +10587,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="461"/>
-      <c r="D21" s="462"/>
+      <c r="C21" s="459"/>
+      <c r="D21" s="458"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -10553,8 +10600,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="461"/>
-      <c r="D22" s="469" t="s">
+      <c r="C22" s="459"/>
+      <c r="D22" s="467" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -10568,8 +10615,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="461"/>
-      <c r="D23" s="461"/>
+      <c r="C23" s="459"/>
+      <c r="D23" s="459"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -10581,8 +10628,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="461"/>
-      <c r="D24" s="461"/>
+      <c r="C24" s="459"/>
+      <c r="D24" s="459"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -10594,8 +10641,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="461"/>
-      <c r="D25" s="461"/>
+      <c r="C25" s="459"/>
+      <c r="D25" s="459"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -10607,8 +10654,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="461"/>
-      <c r="D26" s="462"/>
+      <c r="C26" s="459"/>
+      <c r="D26" s="458"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -10620,7 +10667,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="461"/>
+      <c r="C27" s="459"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -10635,7 +10682,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="461"/>
+      <c r="C28" s="459"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -10650,8 +10697,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="461"/>
-      <c r="D29" s="460" t="s">
+      <c r="C29" s="459"/>
+      <c r="D29" s="468" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -10665,8 +10712,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
+      <c r="C30" s="459"/>
+      <c r="D30" s="459"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -10678,8 +10725,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="462"/>
-      <c r="D31" s="462"/>
+      <c r="C31" s="458"/>
+      <c r="D31" s="458"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -10691,13 +10738,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="463" t="s">
+      <c r="C32" s="457" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="456" t="s">
+      <c r="D32" s="464" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="457"/>
+      <c r="E32" s="465"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -10705,11 +10752,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="461"/>
-      <c r="D33" s="456" t="s">
+      <c r="C33" s="459"/>
+      <c r="D33" s="464" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="457"/>
+      <c r="E33" s="465"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -10718,11 +10765,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="462"/>
-      <c r="D34" s="456" t="s">
+      <c r="C34" s="458"/>
+      <c r="D34" s="464" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="457"/>
+      <c r="E34" s="465"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -10739,6 +10786,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -10755,14 +10810,6 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -14075,7 +14122,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="470">
+      <c r="C71" s="471">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
@@ -14095,7 +14142,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="461"/>
+      <c r="C72" s="459"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14111,7 +14158,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="462"/>
+      <c r="C73" s="458"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17149,7 +17196,7 @@
     <col min="7" max="7" width="13.1640625" style="306" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" style="306" customWidth="1"/>
     <col min="9" max="9" width="19.83203125" style="306" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="306" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="476" customWidth="1"/>
     <col min="11" max="16384" width="12.6640625" style="306"/>
   </cols>
   <sheetData>
@@ -17163,7 +17210,7 @@
       <c r="G1" s="305"/>
       <c r="H1" s="305"/>
       <c r="I1" s="305"/>
-      <c r="J1" s="305"/>
+      <c r="J1" s="474"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="303"/>
@@ -17175,7 +17222,7 @@
       <c r="G2" s="305"/>
       <c r="H2" s="305"/>
       <c r="I2" s="305"/>
-      <c r="J2" s="305"/>
+      <c r="J2" s="474"/>
     </row>
     <row r="3" spans="1:10" ht="27.75" customHeight="1" thickBot="1">
       <c r="A3" s="308"/>
@@ -17189,7 +17236,7 @@
       <c r="G3" s="310"/>
       <c r="H3" s="310"/>
       <c r="I3" s="310"/>
-      <c r="J3" s="310"/>
+      <c r="J3" s="475"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
       <c r="A4" s="312"/>
@@ -17203,7 +17250,7 @@
       <c r="G4" s="312"/>
       <c r="H4" s="312"/>
       <c r="I4" s="305"/>
-      <c r="J4" s="305"/>
+      <c r="J4" s="474"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="312"/>
@@ -17229,7 +17276,7 @@
       <c r="I5" s="315" t="s">
         <v>349</v>
       </c>
-      <c r="J5" s="305"/>
+      <c r="J5" s="474"/>
     </row>
     <row r="6" spans="1:10" ht="56">
       <c r="A6" s="312"/>
@@ -17255,7 +17302,7 @@
       <c r="I6" s="322" t="s">
         <v>898</v>
       </c>
-      <c r="J6" s="305"/>
+      <c r="J6" s="474"/>
     </row>
     <row r="7" spans="1:10" ht="56">
       <c r="A7" s="312"/>
@@ -17281,7 +17328,7 @@
       <c r="I7" s="329" t="s">
         <v>900</v>
       </c>
-      <c r="J7" s="305"/>
+      <c r="J7" s="474"/>
     </row>
     <row r="8" spans="1:10" ht="28">
       <c r="A8" s="312"/>
@@ -17307,7 +17354,7 @@
       <c r="I8" s="334" t="s">
         <v>906</v>
       </c>
-      <c r="J8" s="305"/>
+      <c r="J8" s="474"/>
     </row>
     <row r="9" spans="1:10" ht="45">
       <c r="A9" s="312"/>
@@ -17333,7 +17380,7 @@
       <c r="I9" s="336" t="s">
         <v>908</v>
       </c>
-      <c r="J9" s="305"/>
+      <c r="J9" s="474"/>
     </row>
     <row r="10" spans="1:10" ht="45">
       <c r="A10" s="312"/>
@@ -17359,7 +17406,7 @@
       <c r="I10" s="336" t="s">
         <v>911</v>
       </c>
-      <c r="J10" s="305"/>
+      <c r="J10" s="474"/>
     </row>
     <row r="11" spans="1:10" ht="45">
       <c r="A11" s="312"/>
@@ -17385,7 +17432,7 @@
       <c r="I11" s="336" t="s">
         <v>913</v>
       </c>
-      <c r="J11" s="305"/>
+      <c r="J11" s="474"/>
     </row>
     <row r="12" spans="1:10" ht="42">
       <c r="A12" s="312"/>
@@ -17397,7 +17444,7 @@
         <v>70</v>
       </c>
       <c r="E12" s="338" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="F12" s="331" t="s">
         <v>896</v>
@@ -17411,7 +17458,9 @@
       <c r="I12" s="340" t="s">
         <v>914</v>
       </c>
-      <c r="J12" s="305"/>
+      <c r="J12" s="474" t="s">
+        <v>1059</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="56">
       <c r="A13" s="312"/>
@@ -17437,7 +17486,7 @@
       <c r="I13" s="334" t="s">
         <v>916</v>
       </c>
-      <c r="J13" s="305"/>
+      <c r="J13" s="474"/>
     </row>
     <row r="14" spans="1:10" ht="56">
       <c r="A14" s="312"/>
@@ -17463,7 +17512,7 @@
       <c r="I14" s="334" t="s">
         <v>919</v>
       </c>
-      <c r="J14" s="305"/>
+      <c r="J14" s="474"/>
     </row>
     <row r="15" spans="1:10" ht="42">
       <c r="A15" s="312"/>
@@ -17489,7 +17538,7 @@
       <c r="I15" s="334" t="s">
         <v>921</v>
       </c>
-      <c r="J15" s="305"/>
+      <c r="J15" s="474"/>
     </row>
     <row r="16" spans="1:10" ht="42">
       <c r="A16" s="312"/>
@@ -17515,7 +17564,7 @@
       <c r="I16" s="334" t="s">
         <v>922</v>
       </c>
-      <c r="J16" s="305"/>
+      <c r="J16" s="474"/>
     </row>
     <row r="17" spans="1:10" ht="45">
       <c r="A17" s="312"/>
@@ -17541,7 +17590,7 @@
       <c r="I17" s="336" t="s">
         <v>925</v>
       </c>
-      <c r="J17" s="305"/>
+      <c r="J17" s="474"/>
     </row>
     <row r="18" spans="1:10" ht="60">
       <c r="A18" s="312"/>
@@ -17567,7 +17616,7 @@
       <c r="I18" s="353" t="s">
         <v>928</v>
       </c>
-      <c r="J18" s="305"/>
+      <c r="J18" s="474"/>
     </row>
     <row r="19" spans="1:10" ht="45">
       <c r="A19" s="312"/>
@@ -17593,7 +17642,7 @@
       <c r="I19" s="360" t="s">
         <v>932</v>
       </c>
-      <c r="J19" s="305"/>
+      <c r="J19" s="474"/>
     </row>
     <row r="20" spans="1:10" ht="45">
       <c r="A20" s="312"/>
@@ -17619,7 +17668,7 @@
       <c r="I20" s="360" t="s">
         <v>1035</v>
       </c>
-      <c r="J20" s="305"/>
+      <c r="J20" s="474"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="312"/>
@@ -17631,7 +17680,7 @@
       <c r="G21" s="312"/>
       <c r="H21" s="312"/>
       <c r="I21" s="305"/>
-      <c r="J21" s="305"/>
+      <c r="J21" s="474"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="312"/>
@@ -17645,7 +17694,7 @@
       <c r="G22" s="312"/>
       <c r="H22" s="312"/>
       <c r="I22" s="305"/>
-      <c r="J22" s="305"/>
+      <c r="J22" s="474"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="312"/>
@@ -17661,7 +17710,7 @@
       <c r="G23" s="312"/>
       <c r="H23" s="312"/>
       <c r="I23" s="305"/>
-      <c r="J23" s="305"/>
+      <c r="J23" s="474"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="312"/>
@@ -17677,7 +17726,7 @@
       <c r="G24" s="312"/>
       <c r="H24" s="312"/>
       <c r="I24" s="305"/>
-      <c r="J24" s="305"/>
+      <c r="J24" s="474"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="312"/>
@@ -17693,7 +17742,7 @@
       <c r="G25" s="312"/>
       <c r="H25" s="312"/>
       <c r="I25" s="305"/>
-      <c r="J25" s="305"/>
+      <c r="J25" s="474"/>
     </row>
     <row r="26" spans="1:10" ht="16.5" customHeight="1">
       <c r="A26" s="312"/>
@@ -17709,7 +17758,7 @@
       <c r="G26" s="312"/>
       <c r="H26" s="312"/>
       <c r="I26" s="305"/>
-      <c r="J26" s="305"/>
+      <c r="J26" s="474"/>
     </row>
     <row r="27" spans="1:10" ht="17.25" customHeight="1">
       <c r="A27" s="312"/>
@@ -17725,7 +17774,7 @@
       <c r="G27" s="312"/>
       <c r="H27" s="312"/>
       <c r="I27" s="305"/>
-      <c r="J27" s="305"/>
+      <c r="J27" s="474"/>
     </row>
     <row r="28" spans="1:10" ht="14.25" customHeight="1">
       <c r="A28" s="312"/>
@@ -17741,7 +17790,7 @@
       <c r="G28" s="312"/>
       <c r="H28" s="312"/>
       <c r="I28" s="305"/>
-      <c r="J28" s="305"/>
+      <c r="J28" s="474"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="312"/>
@@ -17753,7 +17802,7 @@
       <c r="G29" s="312"/>
       <c r="H29" s="312"/>
       <c r="I29" s="305"/>
-      <c r="J29" s="305"/>
+      <c r="J29" s="474"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="312"/>
@@ -17767,7 +17816,7 @@
       <c r="G30" s="312"/>
       <c r="H30" s="312"/>
       <c r="I30" s="305"/>
-      <c r="J30" s="305"/>
+      <c r="J30" s="474"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="312"/>
@@ -17783,7 +17832,7 @@
       <c r="G31" s="312"/>
       <c r="H31" s="312"/>
       <c r="I31" s="305"/>
-      <c r="J31" s="305"/>
+      <c r="J31" s="474"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="312"/>
@@ -17799,7 +17848,7 @@
       <c r="G32" s="312"/>
       <c r="H32" s="312"/>
       <c r="I32" s="305"/>
-      <c r="J32" s="305"/>
+      <c r="J32" s="474"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="312"/>
@@ -17815,7 +17864,7 @@
       <c r="G33" s="312"/>
       <c r="H33" s="312"/>
       <c r="I33" s="305"/>
-      <c r="J33" s="305"/>
+      <c r="J33" s="474"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="312"/>
@@ -17831,7 +17880,7 @@
       <c r="G34" s="312"/>
       <c r="H34" s="312"/>
       <c r="I34" s="305"/>
-      <c r="J34" s="305"/>
+      <c r="J34" s="474"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="312"/>
@@ -17847,7 +17896,7 @@
       <c r="G35" s="312"/>
       <c r="H35" s="312"/>
       <c r="I35" s="305"/>
-      <c r="J35" s="305"/>
+      <c r="J35" s="474"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
       <c r="A36" s="312"/>
@@ -17863,7 +17912,7 @@
       <c r="G36" s="312"/>
       <c r="H36" s="312"/>
       <c r="I36" s="305"/>
-      <c r="J36" s="305"/>
+      <c r="J36" s="474"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="312"/>
@@ -17879,7 +17928,7 @@
       <c r="G37" s="312"/>
       <c r="H37" s="312"/>
       <c r="I37" s="305"/>
-      <c r="J37" s="305"/>
+      <c r="J37" s="474"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
       <c r="A38" s="312"/>
@@ -17895,7 +17944,7 @@
       <c r="G38" s="312"/>
       <c r="H38" s="312"/>
       <c r="I38" s="305"/>
-      <c r="J38" s="305"/>
+      <c r="J38" s="474"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
       <c r="A39" s="312"/>
@@ -17911,7 +17960,7 @@
       <c r="G39" s="312"/>
       <c r="H39" s="312"/>
       <c r="I39" s="305"/>
-      <c r="J39" s="305"/>
+      <c r="J39" s="474"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="312"/>
@@ -17927,7 +17976,7 @@
       <c r="G40" s="312"/>
       <c r="H40" s="312"/>
       <c r="I40" s="305"/>
-      <c r="J40" s="305"/>
+      <c r="J40" s="474"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1">
       <c r="A41" s="312"/>
@@ -17943,7 +17992,7 @@
       <c r="G41" s="312"/>
       <c r="H41" s="312"/>
       <c r="I41" s="305"/>
-      <c r="J41" s="305"/>
+      <c r="J41" s="474"/>
     </row>
     <row r="42" spans="1:10" ht="15.75" customHeight="1">
       <c r="A42" s="312"/>
@@ -17959,7 +18008,7 @@
       <c r="G42" s="312"/>
       <c r="H42" s="312"/>
       <c r="I42" s="305"/>
-      <c r="J42" s="305"/>
+      <c r="J42" s="474"/>
     </row>
     <row r="43" spans="1:10" ht="15.75" customHeight="1">
       <c r="A43" s="312"/>
@@ -17975,7 +18024,7 @@
       <c r="G43" s="312"/>
       <c r="H43" s="312"/>
       <c r="I43" s="305"/>
-      <c r="J43" s="305"/>
+      <c r="J43" s="474"/>
     </row>
     <row r="44" spans="1:10" ht="15.75" customHeight="1">
       <c r="A44" s="312"/>
@@ -17991,7 +18040,7 @@
       <c r="G44" s="312"/>
       <c r="H44" s="312"/>
       <c r="I44" s="305"/>
-      <c r="J44" s="305"/>
+      <c r="J44" s="474"/>
     </row>
     <row r="45" spans="1:10" ht="15.75" customHeight="1">
       <c r="A45" s="312"/>
@@ -18007,7 +18056,7 @@
       <c r="G45" s="312"/>
       <c r="H45" s="312"/>
       <c r="I45" s="305"/>
-      <c r="J45" s="305"/>
+      <c r="J45" s="474"/>
     </row>
     <row r="46" spans="1:10" ht="15.75" customHeight="1">
       <c r="A46" s="312"/>
@@ -18023,7 +18072,7 @@
       <c r="G46" s="312"/>
       <c r="H46" s="312"/>
       <c r="I46" s="305"/>
-      <c r="J46" s="305"/>
+      <c r="J46" s="474"/>
     </row>
     <row r="47" spans="1:10" ht="15.75" customHeight="1">
       <c r="A47" s="312"/>
@@ -18035,7 +18084,7 @@
       <c r="G47" s="312"/>
       <c r="H47" s="312"/>
       <c r="I47" s="305"/>
-      <c r="J47" s="305"/>
+      <c r="J47" s="474"/>
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
       <c r="A48" s="312"/>
@@ -18049,7 +18098,7 @@
       <c r="G48" s="312"/>
       <c r="H48" s="312"/>
       <c r="I48" s="305"/>
-      <c r="J48" s="305"/>
+      <c r="J48" s="474"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1">
       <c r="A49" s="312"/>
@@ -18066,7 +18115,7 @@
       <c r="F49" s="375"/>
       <c r="H49" s="312"/>
       <c r="I49" s="305"/>
-      <c r="J49" s="305"/>
+      <c r="J49" s="474"/>
     </row>
     <row r="50" spans="1:10" ht="15.75" customHeight="1">
       <c r="A50" s="312"/>
@@ -18083,7 +18132,7 @@
       <c r="F50" s="379"/>
       <c r="H50" s="312"/>
       <c r="I50" s="305"/>
-      <c r="J50" s="305"/>
+      <c r="J50" s="474"/>
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1">
       <c r="A51" s="312"/>
@@ -18098,7 +18147,7 @@
       <c r="F51" s="383"/>
       <c r="H51" s="312"/>
       <c r="I51" s="305"/>
-      <c r="J51" s="305"/>
+      <c r="J51" s="474"/>
     </row>
     <row r="52" spans="1:10" ht="15.75" customHeight="1">
       <c r="A52" s="312"/>
@@ -18115,7 +18164,7 @@
       <c r="F52" s="379"/>
       <c r="H52" s="312"/>
       <c r="I52" s="305"/>
-      <c r="J52" s="305"/>
+      <c r="J52" s="474"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" customHeight="1">
       <c r="A53" s="312"/>
@@ -18130,7 +18179,7 @@
       <c r="F53" s="383"/>
       <c r="H53" s="312"/>
       <c r="I53" s="305"/>
-      <c r="J53" s="305"/>
+      <c r="J53" s="474"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
       <c r="A54" s="312"/>
@@ -18147,7 +18196,7 @@
       <c r="F54" s="383"/>
       <c r="H54" s="312"/>
       <c r="I54" s="305"/>
-      <c r="J54" s="305"/>
+      <c r="J54" s="474"/>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1">
       <c r="A55" s="312"/>
@@ -18162,7 +18211,7 @@
       <c r="F55" s="383"/>
       <c r="H55" s="312"/>
       <c r="I55" s="305"/>
-      <c r="J55" s="305"/>
+      <c r="J55" s="474"/>
     </row>
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
       <c r="A56" s="312"/>
@@ -18177,7 +18226,7 @@
       <c r="F56" s="383"/>
       <c r="H56" s="312"/>
       <c r="I56" s="305"/>
-      <c r="J56" s="305"/>
+      <c r="J56" s="474"/>
     </row>
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
       <c r="A57" s="312"/>
@@ -18194,7 +18243,7 @@
       <c r="F57" s="383"/>
       <c r="H57" s="312"/>
       <c r="I57" s="305"/>
-      <c r="J57" s="305"/>
+      <c r="J57" s="474"/>
     </row>
     <row r="58" spans="1:10" ht="15.75" customHeight="1">
       <c r="A58" s="312"/>
@@ -18209,7 +18258,7 @@
       <c r="F58" s="383"/>
       <c r="H58" s="312"/>
       <c r="I58" s="305"/>
-      <c r="J58" s="305"/>
+      <c r="J58" s="474"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1">
       <c r="A59" s="312"/>
@@ -18224,7 +18273,7 @@
       <c r="F59" s="383"/>
       <c r="H59" s="312"/>
       <c r="I59" s="305"/>
-      <c r="J59" s="305"/>
+      <c r="J59" s="474"/>
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="312"/>
@@ -18239,7 +18288,7 @@
       <c r="F60" s="383"/>
       <c r="H60" s="312"/>
       <c r="I60" s="305"/>
-      <c r="J60" s="305"/>
+      <c r="J60" s="474"/>
     </row>
     <row r="61" spans="1:10" ht="15.75" customHeight="1">
       <c r="A61" s="312"/>
@@ -18254,7 +18303,7 @@
       <c r="F61" s="379"/>
       <c r="H61" s="312"/>
       <c r="I61" s="305"/>
-      <c r="J61" s="305"/>
+      <c r="J61" s="474"/>
     </row>
     <row r="62" spans="1:10" ht="15.75" customHeight="1">
       <c r="A62" s="312"/>
@@ -18271,7 +18320,7 @@
       <c r="F62" s="383"/>
       <c r="H62" s="312"/>
       <c r="I62" s="305"/>
-      <c r="J62" s="305"/>
+      <c r="J62" s="474"/>
     </row>
     <row r="63" spans="1:10" ht="15.75" customHeight="1">
       <c r="A63" s="312"/>
@@ -18286,7 +18335,7 @@
       <c r="F63" s="383"/>
       <c r="H63" s="312"/>
       <c r="I63" s="305"/>
-      <c r="J63" s="305"/>
+      <c r="J63" s="474"/>
     </row>
     <row r="64" spans="1:10" ht="15.75" customHeight="1">
       <c r="A64" s="312"/>
@@ -18301,7 +18350,7 @@
       <c r="F64" s="383"/>
       <c r="H64" s="312"/>
       <c r="I64" s="305"/>
-      <c r="J64" s="305"/>
+      <c r="J64" s="474"/>
     </row>
     <row r="65" spans="1:10" ht="15.75" customHeight="1">
       <c r="A65" s="312"/>
@@ -18316,7 +18365,7 @@
       <c r="F65" s="383"/>
       <c r="H65" s="312"/>
       <c r="I65" s="305"/>
-      <c r="J65" s="305"/>
+      <c r="J65" s="474"/>
     </row>
     <row r="66" spans="1:10" ht="15.75" customHeight="1">
       <c r="A66" s="312"/>
@@ -18331,7 +18380,7 @@
       <c r="F66" s="398"/>
       <c r="H66" s="312"/>
       <c r="I66" s="305"/>
-      <c r="J66" s="305"/>
+      <c r="J66" s="474"/>
     </row>
     <row r="67" spans="1:10" ht="15.75" customHeight="1">
       <c r="A67" s="312"/>
@@ -18348,7 +18397,7 @@
       <c r="F67" s="398"/>
       <c r="H67" s="312"/>
       <c r="I67" s="305"/>
-      <c r="J67" s="305"/>
+      <c r="J67" s="474"/>
     </row>
     <row r="68" spans="1:10" ht="15.75" customHeight="1">
       <c r="A68" s="312"/>
@@ -18363,7 +18412,7 @@
       <c r="F68" s="398"/>
       <c r="H68" s="312"/>
       <c r="I68" s="305"/>
-      <c r="J68" s="305"/>
+      <c r="J68" s="474"/>
     </row>
     <row r="69" spans="1:10" ht="15.75" customHeight="1">
       <c r="A69" s="312"/>
@@ -18378,7 +18427,7 @@
       <c r="F69" s="398"/>
       <c r="H69" s="312"/>
       <c r="I69" s="305"/>
-      <c r="J69" s="305"/>
+      <c r="J69" s="474"/>
     </row>
     <row r="70" spans="1:10" ht="15.75" customHeight="1">
       <c r="A70" s="312"/>
@@ -18393,7 +18442,7 @@
       <c r="F70" s="398"/>
       <c r="H70" s="312"/>
       <c r="I70" s="305"/>
-      <c r="J70" s="305"/>
+      <c r="J70" s="474"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
       <c r="A71" s="312"/>
@@ -18408,7 +18457,7 @@
       <c r="F71" s="398"/>
       <c r="H71" s="312"/>
       <c r="I71" s="305"/>
-      <c r="J71" s="305"/>
+      <c r="J71" s="474"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1">
       <c r="A72" s="305"/>
@@ -18426,7 +18475,7 @@
       <c r="G72" s="305"/>
       <c r="H72" s="305"/>
       <c r="I72" s="305"/>
-      <c r="J72" s="305"/>
+      <c r="J72" s="474"/>
     </row>
     <row r="73" spans="1:10" ht="15" customHeight="1">
       <c r="C73" s="405"/>
